--- a/artfynd/A 13030-2025 artfynd.xlsx
+++ b/artfynd/A 13030-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128933955</v>
       </c>
       <c r="B2" t="n">
-        <v>92174</v>
+        <v>92178</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -790,7 +790,7 @@
         <v>128933901</v>
       </c>
       <c r="B3" t="n">
-        <v>75205</v>
+        <v>75209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,17 +892,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128933958</v>
+        <v>128933126</v>
       </c>
       <c r="B4" t="n">
-        <v>80225</v>
+        <v>78881</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,37 +910,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544871</v>
+        <v>545150</v>
       </c>
       <c r="R4" t="n">
-        <v>7198612</v>
+        <v>7198391</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,27 +968,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>Kolad granved</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,22 +1003,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128933126</v>
+        <v>128933958</v>
       </c>
       <c r="B5" t="n">
-        <v>78877</v>
+        <v>80229</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,41 +1026,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545150</v>
+        <v>544871</v>
       </c>
       <c r="R5" t="n">
-        <v>7198391</v>
+        <v>7198612</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,27 +1080,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Kolad granved</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,22 +1115,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128933902</v>
+        <v>128933155</v>
       </c>
       <c r="B6" t="n">
-        <v>57716</v>
+        <v>79124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,37 +1138,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545147</v>
+        <v>544955</v>
       </c>
       <c r="R6" t="n">
-        <v>7198430</v>
+        <v>7198720</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1192,27 +1196,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:51</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gamla ringbarkningar på tall</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1227,22 +1226,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128933155</v>
+        <v>128933902</v>
       </c>
       <c r="B7" t="n">
-        <v>79120</v>
+        <v>57720</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1250,41 +1249,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544955</v>
+        <v>545147</v>
       </c>
       <c r="R7" t="n">
-        <v>7198720</v>
+        <v>7198430</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1308,22 +1303,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gamla ringbarkningar på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1338,22 +1338,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128933127</v>
+        <v>128933159</v>
       </c>
       <c r="B8" t="n">
-        <v>78877</v>
+        <v>91804</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1361,21 +1361,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545155</v>
+        <v>544907</v>
       </c>
       <c r="R8" t="n">
-        <v>7198397</v>
+        <v>7198585</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1419,22 +1419,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,22 +1449,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128933159</v>
+        <v>128933127</v>
       </c>
       <c r="B9" t="n">
-        <v>91800</v>
+        <v>78881</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544907</v>
+        <v>545155</v>
       </c>
       <c r="R9" t="n">
-        <v>7198585</v>
+        <v>7198397</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1530,22 +1530,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1560,12 +1560,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1575,7 +1575,7 @@
         <v>128933131</v>
       </c>
       <c r="B10" t="n">
-        <v>80253</v>
+        <v>80257</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,22 +1671,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128933999</v>
+        <v>128933125</v>
       </c>
       <c r="B11" t="n">
-        <v>80225</v>
+        <v>88908</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,37 +1694,41 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544807</v>
+        <v>545148</v>
       </c>
       <c r="R11" t="n">
-        <v>7198677</v>
+        <v>7198360</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1748,27 +1752,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På gammal sälg i sluttning</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1783,22 +1782,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128933125</v>
+        <v>128933891</v>
       </c>
       <c r="B12" t="n">
-        <v>88904</v>
+        <v>78881</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,41 +1805,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>510</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545148</v>
+        <v>545149</v>
       </c>
       <c r="R12" t="n">
-        <v>7198360</v>
+        <v>7198384</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1869,7 +1864,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1879,7 +1874,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På död naken gran med brandljud. På kol.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1894,22 +1894,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128933891</v>
+        <v>128933999</v>
       </c>
       <c r="B13" t="n">
-        <v>78877</v>
+        <v>80229</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1917,21 +1917,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1941,10 +1941,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545149</v>
+        <v>544807</v>
       </c>
       <c r="R13" t="n">
-        <v>7198384</v>
+        <v>7198677</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -1971,27 +1971,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På död naken gran med brandljud. På kol.</t>
+          <t>På gammal sälg i sluttning</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2021,7 +2021,7 @@
         <v>128933172</v>
       </c>
       <c r="B14" t="n">
-        <v>80261</v>
+        <v>80265</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2117,22 +2117,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128933970</v>
+        <v>128933904</v>
       </c>
       <c r="B15" t="n">
-        <v>91800</v>
+        <v>78527</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2140,21 +2140,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>6437</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2164,13 +2164,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544900</v>
+        <v>545138</v>
       </c>
       <c r="R15" t="n">
-        <v>7198605</v>
+        <v>7198414</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2194,27 +2194,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På gammal granlåga</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2234,17 +2229,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128933904</v>
+        <v>128933970</v>
       </c>
       <c r="B16" t="n">
-        <v>78523</v>
+        <v>91804</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2252,21 +2247,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6437</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2276,13 +2271,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>545138</v>
+        <v>544900</v>
       </c>
       <c r="R16" t="n">
-        <v>7198414</v>
+        <v>7198605</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2306,22 +2301,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2351,7 +2351,7 @@
         <v>128933968</v>
       </c>
       <c r="B17" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2453,17 +2453,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128933896</v>
+        <v>128933161</v>
       </c>
       <c r="B18" t="n">
-        <v>78877</v>
+        <v>91522</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2471,37 +2471,41 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>1204</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545160</v>
+        <v>544891</v>
       </c>
       <c r="R18" t="n">
-        <v>7198394</v>
+        <v>7198608</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2525,27 +2529,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:31</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På stående död gran med brandljud. På kol</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2560,22 +2559,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128933932</v>
+        <v>128934084</v>
       </c>
       <c r="B19" t="n">
-        <v>57716</v>
+        <v>91508</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2583,21 +2582,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2607,13 +2606,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545212</v>
+        <v>544966</v>
       </c>
       <c r="R19" t="n">
-        <v>7198500</v>
+        <v>7198729</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2642,7 +2641,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2652,12 +2651,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack äldre än 5 år på tall</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2677,17 +2671,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128933161</v>
+        <v>128933896</v>
       </c>
       <c r="B20" t="n">
-        <v>91518</v>
+        <v>78881</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2695,41 +2689,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1204</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544891</v>
+        <v>545160</v>
       </c>
       <c r="R20" t="n">
-        <v>7198608</v>
+        <v>7198394</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2753,22 +2743,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På stående död gran med brandljud. På kol</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2783,22 +2778,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128934084</v>
+        <v>128933932</v>
       </c>
       <c r="B21" t="n">
-        <v>91504</v>
+        <v>57720</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2806,21 +2801,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2830,13 +2825,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544966</v>
+        <v>545212</v>
       </c>
       <c r="R21" t="n">
-        <v>7198729</v>
+        <v>7198500</v>
       </c>
       <c r="S21" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2865,7 +2860,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2875,7 +2870,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre än 5 år på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2895,17 +2895,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128933164</v>
+        <v>128933875</v>
       </c>
       <c r="B22" t="n">
-        <v>80225</v>
+        <v>79124</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2913,41 +2913,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544839</v>
+        <v>545139</v>
       </c>
       <c r="R22" t="n">
-        <v>7198665</v>
+        <v>7198365</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2971,22 +2967,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Mycket god förekomst</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3001,22 +3002,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128933986</v>
+        <v>128933164</v>
       </c>
       <c r="B23" t="n">
-        <v>91518</v>
+        <v>80229</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3024,37 +3025,41 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544828</v>
+        <v>544839</v>
       </c>
       <c r="R23" t="n">
-        <v>7198678</v>
+        <v>7198665</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3083,7 +3088,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3093,7 +3098,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3108,22 +3113,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128933875</v>
+        <v>128933986</v>
       </c>
       <c r="B24" t="n">
-        <v>79120</v>
+        <v>91522</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3131,21 +3136,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3155,13 +3160,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>545139</v>
+        <v>544828</v>
       </c>
       <c r="R24" t="n">
-        <v>7198365</v>
+        <v>7198678</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3185,27 +3190,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:41</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Mycket god förekomst</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3225,17 +3225,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128933989</v>
+        <v>128933166</v>
       </c>
       <c r="B25" t="n">
-        <v>80226</v>
+        <v>80229</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3243,37 +3243,41 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544830</v>
+        <v>544839</v>
       </c>
       <c r="R25" t="n">
-        <v>7198678</v>
+        <v>7198683</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3302,7 +3306,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3312,12 +3316,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På sälglåga</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3332,22 +3331,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128933165</v>
+        <v>128933989</v>
       </c>
       <c r="B26" t="n">
-        <v>80226</v>
+        <v>80230</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3372,24 +3371,20 @@
           <t>(Scop.) DC.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>544837</v>
+        <v>544830</v>
       </c>
       <c r="R26" t="n">
-        <v>7198665</v>
+        <v>7198678</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3418,7 +3413,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3428,7 +3423,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3443,22 +3443,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128933166</v>
+        <v>128933165</v>
       </c>
       <c r="B27" t="n">
-        <v>80225</v>
+        <v>80230</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,21 +3466,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3494,10 +3494,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>544839</v>
+        <v>544837</v>
       </c>
       <c r="R27" t="n">
-        <v>7198683</v>
+        <v>7198665</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3539,7 +3539,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3554,22 +3554,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128933158</v>
+        <v>128933879</v>
       </c>
       <c r="B28" t="n">
-        <v>57716</v>
+        <v>88908</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3577,46 +3577,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>544903</v>
+        <v>545153</v>
       </c>
       <c r="R28" t="n">
-        <v>7198597</v>
+        <v>7198363</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3640,22 +3631,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På låga av tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3670,12 +3666,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3685,7 +3681,7 @@
         <v>128933982</v>
       </c>
       <c r="B29" t="n">
-        <v>80226</v>
+        <v>80230</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3782,17 +3778,17 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128933879</v>
+        <v>128933158</v>
       </c>
       <c r="B30" t="n">
-        <v>88904</v>
+        <v>57720</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3800,37 +3796,46 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>545153</v>
+        <v>544903</v>
       </c>
       <c r="R30" t="n">
-        <v>7198363</v>
+        <v>7198597</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3854,27 +3859,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:50</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På låga av tall</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3889,22 +3889,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128933961</v>
+        <v>128933980</v>
       </c>
       <c r="B31" t="n">
-        <v>80226</v>
+        <v>91522</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3912,21 +3912,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3936,13 +3936,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>544872</v>
+        <v>544853</v>
       </c>
       <c r="R31" t="n">
-        <v>7198610</v>
+        <v>7198662</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>Väl nedbruten låga av sälg</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4006,17 +4006,17 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128933980</v>
+        <v>128933961</v>
       </c>
       <c r="B32" t="n">
-        <v>91518</v>
+        <v>80230</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4024,21 +4024,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1204</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4048,13 +4048,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>544853</v>
+        <v>544872</v>
       </c>
       <c r="R32" t="n">
-        <v>7198662</v>
+        <v>7198610</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Väl nedbruten låga av sälg</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4128,7 +4128,7 @@
         <v>128933141</v>
       </c>
       <c r="B33" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4224,12 +4224,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4239,7 +4239,7 @@
         <v>128933130</v>
       </c>
       <c r="B34" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4340,12 +4340,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4355,7 +4355,7 @@
         <v>128933213</v>
       </c>
       <c r="B35" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4464,12 +4464,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg, David Kenger, Petter Lindwall</t>
+          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4479,7 +4479,7 @@
         <v>128933156</v>
       </c>
       <c r="B36" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4583,69 +4583,60 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg, David Kenger, Petter Lindwall</t>
+          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128933147</v>
+        <v>128934001</v>
       </c>
       <c r="B37" t="n">
-        <v>57716</v>
+        <v>80265</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>545204</v>
+        <v>544806</v>
       </c>
       <c r="R37" t="n">
-        <v>7198506</v>
+        <v>7198678</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4674,7 +4665,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4684,7 +4675,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4699,60 +4695,69 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128934001</v>
+        <v>128933147</v>
       </c>
       <c r="B38" t="n">
-        <v>80261</v>
+        <v>57720</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>544806</v>
+        <v>545204</v>
       </c>
       <c r="R38" t="n">
-        <v>7198678</v>
+        <v>7198506</v>
       </c>
       <c r="S38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4781,7 +4786,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4791,12 +4796,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:21</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4811,12 +4811,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4826,7 +4826,7 @@
         <v>128933212</v>
       </c>
       <c r="B39" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4927,12 +4927,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4942,7 +4942,7 @@
         <v>128933908</v>
       </c>
       <c r="B40" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5054,7 +5054,7 @@
         <v>128933124</v>
       </c>
       <c r="B41" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5150,22 +5150,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128933978</v>
+        <v>128933171</v>
       </c>
       <c r="B42" t="n">
-        <v>91518</v>
+        <v>80229</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5173,37 +5173,41 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>544893</v>
+        <v>544807</v>
       </c>
       <c r="R42" t="n">
-        <v>7198604</v>
+        <v>7198685</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5232,7 +5236,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5242,12 +5246,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:39</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På väl nedbruten låga av gran</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5262,22 +5261,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128933171</v>
+        <v>128933978</v>
       </c>
       <c r="B43" t="n">
-        <v>80225</v>
+        <v>91522</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5285,41 +5284,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>544807</v>
+        <v>544893</v>
       </c>
       <c r="R43" t="n">
-        <v>7198685</v>
+        <v>7198604</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5348,7 +5343,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5358,7 +5353,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På väl nedbruten låga av gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5373,22 +5373,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128933163</v>
+        <v>128933154</v>
       </c>
       <c r="B44" t="n">
-        <v>79120</v>
+        <v>91508</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5396,21 +5396,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5424,10 +5424,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>544832</v>
+        <v>544968</v>
       </c>
       <c r="R44" t="n">
-        <v>7198667</v>
+        <v>7198730</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5469,7 +5469,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Gran, stor utbredning.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5484,12 +5489,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5499,7 +5504,7 @@
         <v>128933157</v>
       </c>
       <c r="B45" t="n">
-        <v>80226</v>
+        <v>80230</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5600,22 +5605,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128933129</v>
+        <v>128933163</v>
       </c>
       <c r="B46" t="n">
-        <v>78877</v>
+        <v>79124</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5623,21 +5628,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5651,10 +5656,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>545158</v>
+        <v>544832</v>
       </c>
       <c r="R46" t="n">
-        <v>7198403</v>
+        <v>7198667</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5681,27 +5686,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Liten kolad stubbe</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5716,22 +5716,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128933154</v>
+        <v>128933129</v>
       </c>
       <c r="B47" t="n">
-        <v>91504</v>
+        <v>78881</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5739,21 +5739,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>544968</v>
+        <v>545158</v>
       </c>
       <c r="R47" t="n">
-        <v>7198730</v>
+        <v>7198403</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5797,27 +5797,27 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Gran, stor utbredning.</t>
+          <t>Liten kolad stubbe</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5832,12 +5832,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5847,7 +5847,7 @@
         <v>128933139</v>
       </c>
       <c r="B48" t="n">
-        <v>80253</v>
+        <v>80257</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5943,22 +5943,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128933870</v>
+        <v>128933966</v>
       </c>
       <c r="B49" t="n">
-        <v>57716</v>
+        <v>80230</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5966,21 +5966,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5990,13 +5990,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>545136</v>
+        <v>544905</v>
       </c>
       <c r="R49" t="n">
-        <v>7198363</v>
+        <v>7198603</v>
       </c>
       <c r="S49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6020,27 +6020,27 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Nya ringbarkningar från tretåig hackspett på gran.</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6060,17 +6060,17 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128933984</v>
+        <v>128933136</v>
       </c>
       <c r="B50" t="n">
-        <v>80225</v>
+        <v>79124</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6078,37 +6078,41 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>544836</v>
+        <v>545109</v>
       </c>
       <c r="R50" t="n">
-        <v>7198663</v>
+        <v>7198551</v>
       </c>
       <c r="S50" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6132,27 +6136,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:56</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Högt upp på gammal sälg</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6167,22 +6166,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128933966</v>
+        <v>128933984</v>
       </c>
       <c r="B51" t="n">
-        <v>80226</v>
+        <v>80229</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6190,21 +6189,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6214,13 +6213,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>544905</v>
+        <v>544836</v>
       </c>
       <c r="R51" t="n">
-        <v>7198603</v>
+        <v>7198663</v>
       </c>
       <c r="S51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6249,7 +6248,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6259,12 +6258,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>Högt upp på gammal sälg</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6284,17 +6283,17 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128933973</v>
+        <v>128933870</v>
       </c>
       <c r="B52" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6326,10 +6325,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>544900</v>
+        <v>545136</v>
       </c>
       <c r="R52" t="n">
-        <v>7198597</v>
+        <v>7198363</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6356,27 +6355,27 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack äldre än 5 år på gran</t>
+          <t>Nya ringbarkningar från tretåig hackspett på gran.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6396,17 +6395,17 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128933136</v>
+        <v>128933973</v>
       </c>
       <c r="B53" t="n">
-        <v>79120</v>
+        <v>57720</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6414,41 +6413,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>545109</v>
+        <v>544900</v>
       </c>
       <c r="R53" t="n">
-        <v>7198551</v>
+        <v>7198597</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6472,22 +6467,27 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack äldre än 5 år på gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6502,22 +6502,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128933167</v>
+        <v>128933947</v>
       </c>
       <c r="B54" t="n">
-        <v>80129</v>
+        <v>91473</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6525,41 +6525,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>544823</v>
+        <v>544971</v>
       </c>
       <c r="R54" t="n">
-        <v>7198695</v>
+        <v>7198722</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6588,7 +6584,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6598,12 +6594,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:14</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Asp</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6618,22 +6609,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128933947</v>
+        <v>128933167</v>
       </c>
       <c r="B55" t="n">
-        <v>91469</v>
+        <v>80133</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6641,37 +6632,41 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>6456</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>544971</v>
+        <v>544823</v>
       </c>
       <c r="R55" t="n">
-        <v>7198722</v>
+        <v>7198695</v>
       </c>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6700,7 +6695,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6710,7 +6705,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Asp</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6725,44 +6725,44 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128934086</v>
+        <v>128933991</v>
       </c>
       <c r="B56" t="n">
-        <v>57716</v>
+        <v>80133</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6772,10 +6772,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>544908</v>
+        <v>544826</v>
       </c>
       <c r="R56" t="n">
-        <v>7198615</v>
+        <v>7198694</v>
       </c>
       <c r="S56" t="n">
         <v>4</v>
@@ -6807,7 +6807,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6842,39 +6842,39 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128933991</v>
+        <v>128934086</v>
       </c>
       <c r="B57" t="n">
-        <v>80129</v>
+        <v>57720</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6884,10 +6884,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>544826</v>
+        <v>544908</v>
       </c>
       <c r="R57" t="n">
-        <v>7198694</v>
+        <v>7198615</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -6919,7 +6919,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin  Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>

--- a/artfynd/A 13030-2025 artfynd.xlsx
+++ b/artfynd/A 13030-2025 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128933126</v>
+        <v>128933958</v>
       </c>
       <c r="B4" t="n">
-        <v>78881</v>
+        <v>80229</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,41 +910,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545150</v>
+        <v>544871</v>
       </c>
       <c r="R4" t="n">
-        <v>7198391</v>
+        <v>7198612</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -968,27 +964,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Kolad granved</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,22 +999,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128933958</v>
+        <v>128933126</v>
       </c>
       <c r="B5" t="n">
-        <v>80229</v>
+        <v>78881</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,37 +1022,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544871</v>
+        <v>545150</v>
       </c>
       <c r="R5" t="n">
-        <v>7198612</v>
+        <v>7198391</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,27 +1080,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>Kolad granved</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,12 +1115,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128933125</v>
+        <v>128933999</v>
       </c>
       <c r="B11" t="n">
-        <v>88908</v>
+        <v>80229</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,41 +1694,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545148</v>
+        <v>544807</v>
       </c>
       <c r="R11" t="n">
-        <v>7198360</v>
+        <v>7198677</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1752,22 +1748,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På gammal sälg i sluttning</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1782,12 +1783,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1906,48 +1907,52 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128933999</v>
+        <v>128933172</v>
       </c>
       <c r="B13" t="n">
-        <v>80229</v>
+        <v>80265</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544807</v>
+        <v>544801</v>
       </c>
       <c r="R13" t="n">
-        <v>7198677</v>
+        <v>7198690</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1976,7 +1981,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1986,12 +1991,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På gammal sälg i sluttning</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2006,44 +2006,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128933172</v>
+        <v>128933125</v>
       </c>
       <c r="B14" t="n">
-        <v>80265</v>
+        <v>88908</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>510</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2057,10 +2057,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544801</v>
+        <v>545148</v>
       </c>
       <c r="R14" t="n">
-        <v>7198690</v>
+        <v>7198360</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2087,22 +2087,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2460,10 +2460,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128933161</v>
+        <v>128933932</v>
       </c>
       <c r="B18" t="n">
-        <v>91522</v>
+        <v>57720</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2471,41 +2471,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544891</v>
+        <v>545212</v>
       </c>
       <c r="R18" t="n">
-        <v>7198608</v>
+        <v>7198500</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2534,7 +2530,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2544,7 +2540,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre än 5 år på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2559,22 +2560,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128934084</v>
+        <v>128933161</v>
       </c>
       <c r="B19" t="n">
-        <v>91508</v>
+        <v>91522</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2582,37 +2583,41 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544966</v>
+        <v>544891</v>
       </c>
       <c r="R19" t="n">
-        <v>7198729</v>
+        <v>7198608</v>
       </c>
       <c r="S19" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2641,7 +2646,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2651,7 +2656,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2666,22 +2671,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128933896</v>
+        <v>128934084</v>
       </c>
       <c r="B20" t="n">
-        <v>78881</v>
+        <v>91508</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2689,21 +2694,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2713,13 +2718,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545160</v>
+        <v>544966</v>
       </c>
       <c r="R20" t="n">
-        <v>7198394</v>
+        <v>7198729</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2743,27 +2748,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:31</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På stående död gran med brandljud. På kol</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2790,10 +2790,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128933932</v>
+        <v>128933896</v>
       </c>
       <c r="B21" t="n">
-        <v>57720</v>
+        <v>78881</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2801,21 +2801,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545212</v>
+        <v>545160</v>
       </c>
       <c r="R21" t="n">
-        <v>7198500</v>
+        <v>7198394</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -2855,27 +2855,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre än 5 år på tall</t>
+          <t>På stående död gran med brandljud. På kol</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2902,10 +2902,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128933875</v>
+        <v>128933986</v>
       </c>
       <c r="B22" t="n">
-        <v>79124</v>
+        <v>91522</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2913,21 +2913,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2937,13 +2937,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>545139</v>
+        <v>544828</v>
       </c>
       <c r="R22" t="n">
-        <v>7198365</v>
+        <v>7198678</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2967,27 +2967,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:41</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Mycket god förekomst</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3014,10 +3009,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128933164</v>
+        <v>128933875</v>
       </c>
       <c r="B23" t="n">
-        <v>80229</v>
+        <v>79124</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3025,41 +3020,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544839</v>
+        <v>545139</v>
       </c>
       <c r="R23" t="n">
-        <v>7198665</v>
+        <v>7198365</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3083,22 +3074,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Mycket god förekomst</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3113,22 +3109,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128933986</v>
+        <v>128933164</v>
       </c>
       <c r="B24" t="n">
-        <v>91522</v>
+        <v>80229</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3136,37 +3132,41 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544828</v>
+        <v>544839</v>
       </c>
       <c r="R24" t="n">
-        <v>7198678</v>
+        <v>7198665</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3220,22 +3220,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128933166</v>
+        <v>128933989</v>
       </c>
       <c r="B25" t="n">
-        <v>80229</v>
+        <v>80230</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3243,41 +3243,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544839</v>
+        <v>544830</v>
       </c>
       <c r="R25" t="n">
-        <v>7198683</v>
+        <v>7198678</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3306,7 +3302,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3316,7 +3312,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3331,19 +3332,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128933989</v>
+        <v>128933165</v>
       </c>
       <c r="B26" t="n">
         <v>80230</v>
@@ -3371,20 +3372,24 @@
           <t>(Scop.) DC.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>544830</v>
+        <v>544837</v>
       </c>
       <c r="R26" t="n">
-        <v>7198678</v>
+        <v>7198665</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3413,7 +3418,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3423,12 +3428,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På sälglåga</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3443,22 +3443,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128933165</v>
+        <v>128933166</v>
       </c>
       <c r="B27" t="n">
-        <v>80230</v>
+        <v>80229</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,21 +3466,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3494,10 +3494,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>544837</v>
+        <v>544839</v>
       </c>
       <c r="R27" t="n">
-        <v>7198665</v>
+        <v>7198683</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3539,7 +3539,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3566,10 +3566,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128933879</v>
+        <v>128933982</v>
       </c>
       <c r="B28" t="n">
-        <v>88908</v>
+        <v>80230</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3577,21 +3577,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>510</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>545153</v>
+        <v>544845</v>
       </c>
       <c r="R28" t="n">
-        <v>7198363</v>
+        <v>7198663</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3631,27 +3631,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:50</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På låga av tall</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3678,10 +3673,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128933982</v>
+        <v>128933158</v>
       </c>
       <c r="B29" t="n">
-        <v>80230</v>
+        <v>57720</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3689,37 +3684,46 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544845</v>
+        <v>544903</v>
       </c>
       <c r="R29" t="n">
-        <v>7198663</v>
+        <v>7198597</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3748,7 +3752,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3758,7 +3762,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3773,22 +3777,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128933158</v>
+        <v>128933879</v>
       </c>
       <c r="B30" t="n">
-        <v>57720</v>
+        <v>88908</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3796,46 +3800,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>544903</v>
+        <v>545153</v>
       </c>
       <c r="R30" t="n">
-        <v>7198597</v>
+        <v>7198363</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3859,22 +3854,27 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På låga av tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3889,22 +3889,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128933980</v>
+        <v>128933141</v>
       </c>
       <c r="B31" t="n">
-        <v>91522</v>
+        <v>79124</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3912,37 +3912,41 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>544853</v>
+        <v>545088</v>
       </c>
       <c r="R31" t="n">
-        <v>7198662</v>
+        <v>7198569</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3966,27 +3970,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Väl nedbruten låga av sälg</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4001,12 +4000,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4125,10 +4124,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128933141</v>
+        <v>128933980</v>
       </c>
       <c r="B33" t="n">
-        <v>79124</v>
+        <v>91522</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4136,41 +4135,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>545088</v>
+        <v>544853</v>
       </c>
       <c r="R33" t="n">
-        <v>7198569</v>
+        <v>7198662</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4194,22 +4189,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Väl nedbruten låga av sälg</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4224,12 +4224,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -5051,10 +5051,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128933124</v>
+        <v>128933978</v>
       </c>
       <c r="B41" t="n">
-        <v>79124</v>
+        <v>91522</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5062,41 +5062,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>545144</v>
+        <v>544893</v>
       </c>
       <c r="R41" t="n">
-        <v>7198368</v>
+        <v>7198604</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5120,22 +5116,27 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På väl nedbruten låga av gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5150,22 +5151,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128933171</v>
+        <v>128933124</v>
       </c>
       <c r="B42" t="n">
-        <v>80229</v>
+        <v>79124</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5173,21 +5174,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5201,10 +5202,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>544807</v>
+        <v>545144</v>
       </c>
       <c r="R42" t="n">
-        <v>7198685</v>
+        <v>7198368</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5231,22 +5232,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5273,10 +5274,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128933978</v>
+        <v>128933171</v>
       </c>
       <c r="B43" t="n">
-        <v>91522</v>
+        <v>80229</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5284,37 +5285,41 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>544893</v>
+        <v>544807</v>
       </c>
       <c r="R43" t="n">
-        <v>7198604</v>
+        <v>7198685</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5343,7 +5348,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5353,12 +5358,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:39</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På väl nedbruten låga av gran</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5373,22 +5373,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128933154</v>
+        <v>128933157</v>
       </c>
       <c r="B44" t="n">
-        <v>91508</v>
+        <v>80230</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5396,21 +5396,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5424,10 +5424,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>544968</v>
+        <v>544908</v>
       </c>
       <c r="R44" t="n">
-        <v>7198730</v>
+        <v>7198602</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5469,12 +5469,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Gran, stor utbredning.</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5501,10 +5501,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128933157</v>
+        <v>128933129</v>
       </c>
       <c r="B45" t="n">
-        <v>80230</v>
+        <v>78881</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5512,21 +5512,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5540,10 +5540,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>544908</v>
+        <v>545158</v>
       </c>
       <c r="R45" t="n">
-        <v>7198602</v>
+        <v>7198403</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5570,27 +5570,27 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Liten kolad stubbe</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5728,10 +5728,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128933129</v>
+        <v>128933154</v>
       </c>
       <c r="B47" t="n">
-        <v>78881</v>
+        <v>91508</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5739,21 +5739,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>545158</v>
+        <v>544968</v>
       </c>
       <c r="R47" t="n">
-        <v>7198403</v>
+        <v>7198730</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5797,27 +5797,27 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Liten kolad stubbe</t>
+          <t>Gran, stor utbredning.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6067,10 +6067,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128933136</v>
+        <v>128933984</v>
       </c>
       <c r="B50" t="n">
-        <v>79124</v>
+        <v>80229</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6078,41 +6078,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>545109</v>
+        <v>544836</v>
       </c>
       <c r="R50" t="n">
-        <v>7198551</v>
+        <v>7198663</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6136,22 +6132,27 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Högt upp på gammal sälg</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6166,22 +6167,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128933984</v>
+        <v>128933136</v>
       </c>
       <c r="B51" t="n">
-        <v>80229</v>
+        <v>79124</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6189,37 +6190,41 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>544836</v>
+        <v>545109</v>
       </c>
       <c r="R51" t="n">
-        <v>7198663</v>
+        <v>7198551</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6243,27 +6248,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:56</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Högt upp på gammal sälg</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6278,12 +6278,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6737,32 +6737,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128933991</v>
+        <v>128934086</v>
       </c>
       <c r="B56" t="n">
-        <v>80133</v>
+        <v>57720</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6772,10 +6772,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>544826</v>
+        <v>544908</v>
       </c>
       <c r="R56" t="n">
-        <v>7198694</v>
+        <v>7198615</v>
       </c>
       <c r="S56" t="n">
         <v>4</v>
@@ -6807,7 +6807,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6849,32 +6849,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128934086</v>
+        <v>128933991</v>
       </c>
       <c r="B57" t="n">
-        <v>57720</v>
+        <v>80133</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6884,10 +6884,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>544908</v>
+        <v>544826</v>
       </c>
       <c r="R57" t="n">
-        <v>7198615</v>
+        <v>7198694</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -6919,7 +6919,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 13030-2025 artfynd.xlsx
+++ b/artfynd/A 13030-2025 artfynd.xlsx
@@ -1127,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128933155</v>
+        <v>128933902</v>
       </c>
       <c r="B6" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,41 +1138,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544955</v>
+        <v>545147</v>
       </c>
       <c r="R6" t="n">
-        <v>7198720</v>
+        <v>7198430</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1196,22 +1192,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gamla ringbarkningar på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1226,22 +1227,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128933902</v>
+        <v>128933155</v>
       </c>
       <c r="B7" t="n">
-        <v>57720</v>
+        <v>79124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1249,37 +1250,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545147</v>
+        <v>544955</v>
       </c>
       <c r="R7" t="n">
-        <v>7198430</v>
+        <v>7198720</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,27 +1308,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:51</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Gamla ringbarkningar på tall</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1338,12 +1338,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128933999</v>
+        <v>128933125</v>
       </c>
       <c r="B11" t="n">
-        <v>80229</v>
+        <v>88908</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,37 +1694,41 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544807</v>
+        <v>545148</v>
       </c>
       <c r="R11" t="n">
-        <v>7198677</v>
+        <v>7198360</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1748,27 +1752,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På gammal sälg i sluttning</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1783,60 +1782,64 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128933891</v>
+        <v>128933172</v>
       </c>
       <c r="B12" t="n">
-        <v>78881</v>
+        <v>80265</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6464</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545149</v>
+        <v>544801</v>
       </c>
       <c r="R12" t="n">
-        <v>7198384</v>
+        <v>7198690</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1860,27 +1863,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På död naken gran med brandljud. På kol.</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1895,64 +1893,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128933172</v>
+        <v>128933999</v>
       </c>
       <c r="B13" t="n">
-        <v>80265</v>
+        <v>80229</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544801</v>
+        <v>544807</v>
       </c>
       <c r="R13" t="n">
-        <v>7198690</v>
+        <v>7198677</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1981,7 +1975,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1991,7 +1985,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På gammal sälg i sluttning</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2006,22 +2005,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128933125</v>
+        <v>128933891</v>
       </c>
       <c r="B14" t="n">
-        <v>88908</v>
+        <v>78881</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2029,41 +2028,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>510</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545148</v>
+        <v>545149</v>
       </c>
       <c r="R14" t="n">
-        <v>7198360</v>
+        <v>7198384</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2092,7 +2087,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2102,7 +2097,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På död naken gran med brandljud. På kol.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2117,12 +2117,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2460,10 +2460,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128933932</v>
+        <v>128933896</v>
       </c>
       <c r="B18" t="n">
-        <v>57720</v>
+        <v>78881</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2471,21 +2471,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545212</v>
+        <v>545160</v>
       </c>
       <c r="R18" t="n">
-        <v>7198500</v>
+        <v>7198394</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2525,27 +2525,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre än 5 år på tall</t>
+          <t>På stående död gran med brandljud. På kol</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2790,10 +2790,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128933896</v>
+        <v>128933932</v>
       </c>
       <c r="B21" t="n">
-        <v>78881</v>
+        <v>57720</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2801,21 +2801,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545160</v>
+        <v>545212</v>
       </c>
       <c r="R21" t="n">
-        <v>7198394</v>
+        <v>7198500</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -2855,27 +2855,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På stående död gran med brandljud. På kol</t>
+          <t>Ringhack äldre än 5 år på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3566,10 +3566,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128933982</v>
+        <v>128933879</v>
       </c>
       <c r="B28" t="n">
-        <v>80230</v>
+        <v>88908</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3577,21 +3577,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>510</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>544845</v>
+        <v>545153</v>
       </c>
       <c r="R28" t="n">
-        <v>7198663</v>
+        <v>7198363</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3631,22 +3631,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På låga av tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3673,10 +3678,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128933158</v>
+        <v>128933982</v>
       </c>
       <c r="B29" t="n">
-        <v>57720</v>
+        <v>80230</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3684,46 +3689,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544903</v>
+        <v>544845</v>
       </c>
       <c r="R29" t="n">
-        <v>7198597</v>
+        <v>7198663</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3752,7 +3748,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3762,7 +3758,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3777,22 +3773,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128933879</v>
+        <v>128933158</v>
       </c>
       <c r="B30" t="n">
-        <v>88908</v>
+        <v>57720</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3800,37 +3796,46 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>545153</v>
+        <v>544903</v>
       </c>
       <c r="R30" t="n">
-        <v>7198363</v>
+        <v>7198597</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3854,27 +3859,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:50</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På låga av tall</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3889,22 +3889,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128933141</v>
+        <v>128933961</v>
       </c>
       <c r="B31" t="n">
-        <v>79124</v>
+        <v>80230</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3912,41 +3912,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>545088</v>
+        <v>544872</v>
       </c>
       <c r="R31" t="n">
-        <v>7198569</v>
+        <v>7198610</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3970,22 +3966,27 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4000,22 +4001,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128933961</v>
+        <v>128933980</v>
       </c>
       <c r="B32" t="n">
-        <v>80230</v>
+        <v>91522</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4023,21 +4024,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4047,13 +4048,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>544872</v>
+        <v>544853</v>
       </c>
       <c r="R32" t="n">
-        <v>7198610</v>
+        <v>7198662</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4082,7 +4083,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4092,12 +4093,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>Väl nedbruten låga av sälg</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4124,10 +4125,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128933980</v>
+        <v>128933141</v>
       </c>
       <c r="B33" t="n">
-        <v>91522</v>
+        <v>79124</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4135,37 +4136,41 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>544853</v>
+        <v>545088</v>
       </c>
       <c r="R33" t="n">
-        <v>7198662</v>
+        <v>7198569</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4189,27 +4194,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Väl nedbruten låga av sälg</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4224,12 +4224,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -5051,10 +5051,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128933978</v>
+        <v>128933171</v>
       </c>
       <c r="B41" t="n">
-        <v>91522</v>
+        <v>80229</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5062,37 +5062,41 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>544893</v>
+        <v>544807</v>
       </c>
       <c r="R41" t="n">
-        <v>7198604</v>
+        <v>7198685</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5121,7 +5125,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5131,12 +5135,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:39</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På väl nedbruten låga av gran</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5151,22 +5150,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128933124</v>
+        <v>128933978</v>
       </c>
       <c r="B42" t="n">
-        <v>79124</v>
+        <v>91522</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5174,41 +5173,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>545144</v>
+        <v>544893</v>
       </c>
       <c r="R42" t="n">
-        <v>7198368</v>
+        <v>7198604</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5232,22 +5227,27 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På väl nedbruten låga av gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5262,22 +5262,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128933171</v>
+        <v>128933124</v>
       </c>
       <c r="B43" t="n">
-        <v>80229</v>
+        <v>79124</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5285,21 +5285,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5313,10 +5313,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>544807</v>
+        <v>545144</v>
       </c>
       <c r="R43" t="n">
-        <v>7198685</v>
+        <v>7198368</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5343,22 +5343,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5501,10 +5501,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128933129</v>
+        <v>128933163</v>
       </c>
       <c r="B45" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5512,21 +5512,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5540,10 +5540,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>545158</v>
+        <v>544832</v>
       </c>
       <c r="R45" t="n">
-        <v>7198403</v>
+        <v>7198667</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5570,27 +5570,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Liten kolad stubbe</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5617,10 +5612,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128933163</v>
+        <v>128933154</v>
       </c>
       <c r="B46" t="n">
-        <v>79124</v>
+        <v>91508</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5628,21 +5623,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5656,10 +5651,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>544832</v>
+        <v>544968</v>
       </c>
       <c r="R46" t="n">
-        <v>7198667</v>
+        <v>7198730</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5691,7 +5686,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5701,7 +5696,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Gran, stor utbredning.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5728,10 +5728,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128933154</v>
+        <v>128933129</v>
       </c>
       <c r="B47" t="n">
-        <v>91508</v>
+        <v>78881</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5739,21 +5739,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>544968</v>
+        <v>545158</v>
       </c>
       <c r="R47" t="n">
-        <v>7198730</v>
+        <v>7198403</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5797,27 +5797,27 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Gran, stor utbredning.</t>
+          <t>Liten kolad stubbe</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6067,10 +6067,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128933984</v>
+        <v>128933136</v>
       </c>
       <c r="B50" t="n">
-        <v>80229</v>
+        <v>79124</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6078,37 +6078,41 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>544836</v>
+        <v>545109</v>
       </c>
       <c r="R50" t="n">
-        <v>7198663</v>
+        <v>7198551</v>
       </c>
       <c r="S50" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6132,27 +6136,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:56</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Högt upp på gammal sälg</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6167,22 +6166,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128933136</v>
+        <v>128933984</v>
       </c>
       <c r="B51" t="n">
-        <v>79124</v>
+        <v>80229</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6190,41 +6189,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>545109</v>
+        <v>544836</v>
       </c>
       <c r="R51" t="n">
-        <v>7198551</v>
+        <v>7198663</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6248,22 +6243,27 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Högt upp på gammal sälg</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6278,12 +6278,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6737,32 +6737,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128934086</v>
+        <v>128933991</v>
       </c>
       <c r="B56" t="n">
-        <v>57720</v>
+        <v>80133</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6772,10 +6772,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>544908</v>
+        <v>544826</v>
       </c>
       <c r="R56" t="n">
-        <v>7198615</v>
+        <v>7198694</v>
       </c>
       <c r="S56" t="n">
         <v>4</v>
@@ -6807,7 +6807,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6849,32 +6849,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128933991</v>
+        <v>128934086</v>
       </c>
       <c r="B57" t="n">
-        <v>80133</v>
+        <v>57720</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6884,10 +6884,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>544826</v>
+        <v>544908</v>
       </c>
       <c r="R57" t="n">
-        <v>7198694</v>
+        <v>7198615</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -6919,7 +6919,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 13030-2025 artfynd.xlsx
+++ b/artfynd/A 13030-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128933955</v>
+        <v>128933901</v>
       </c>
       <c r="B2" t="n">
-        <v>92178</v>
+        <v>83005</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>898</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544957</v>
+        <v>545154</v>
       </c>
       <c r="R2" t="n">
-        <v>7198698</v>
+        <v>7198397</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,27 +740,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På bark av gammal gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128933901</v>
+        <v>128933955</v>
       </c>
       <c r="B3" t="n">
-        <v>75209</v>
+        <v>92183</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>898</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,13 +822,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545154</v>
+        <v>544957</v>
       </c>
       <c r="R3" t="n">
-        <v>7198397</v>
+        <v>7198698</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,27 +852,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På bark av gammal gran</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +902,7 @@
         <v>128933958</v>
       </c>
       <c r="B4" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>128933126</v>
       </c>
       <c r="B5" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>128933902</v>
       </c>
       <c r="B6" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>128933155</v>
       </c>
       <c r="B7" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,10 +1350,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128933159</v>
+        <v>128933127</v>
       </c>
       <c r="B8" t="n">
-        <v>91804</v>
+        <v>78786</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1361,21 +1361,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544907</v>
+        <v>545155</v>
       </c>
       <c r="R8" t="n">
-        <v>7198585</v>
+        <v>7198397</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1419,22 +1419,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,10 +1461,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128933127</v>
+        <v>128933159</v>
       </c>
       <c r="B9" t="n">
-        <v>78881</v>
+        <v>91809</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545155</v>
+        <v>544907</v>
       </c>
       <c r="R9" t="n">
-        <v>7198397</v>
+        <v>7198585</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1530,22 +1530,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,7 +1575,7 @@
         <v>128933131</v>
       </c>
       <c r="B10" t="n">
-        <v>80257</v>
+        <v>80162</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>128933125</v>
       </c>
       <c r="B11" t="n">
-        <v>88908</v>
+        <v>88913</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,52 +1794,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128933172</v>
+        <v>128933999</v>
       </c>
       <c r="B12" t="n">
-        <v>80265</v>
+        <v>80134</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544801</v>
+        <v>544807</v>
       </c>
       <c r="R12" t="n">
-        <v>7198690</v>
+        <v>7198677</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1868,7 +1864,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1878,7 +1874,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På gammal sälg i sluttning</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1893,22 +1894,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128933999</v>
+        <v>128933891</v>
       </c>
       <c r="B13" t="n">
-        <v>80229</v>
+        <v>78786</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1916,21 +1917,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1940,10 +1941,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544807</v>
+        <v>545149</v>
       </c>
       <c r="R13" t="n">
-        <v>7198677</v>
+        <v>7198384</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -1970,27 +1971,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gammal sälg i sluttning</t>
+          <t>På död naken gran med brandljud. På kol.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2017,48 +2018,52 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128933891</v>
+        <v>128933172</v>
       </c>
       <c r="B14" t="n">
-        <v>78881</v>
+        <v>80170</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545149</v>
+        <v>544801</v>
       </c>
       <c r="R14" t="n">
-        <v>7198384</v>
+        <v>7198690</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2082,27 +2087,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På död naken gran med brandljud. På kol.</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2117,22 +2117,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128933904</v>
+        <v>128933970</v>
       </c>
       <c r="B15" t="n">
-        <v>78527</v>
+        <v>91809</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2140,21 +2140,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6437</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2164,13 +2164,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545138</v>
+        <v>544900</v>
       </c>
       <c r="R15" t="n">
-        <v>7198414</v>
+        <v>7198605</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2194,22 +2194,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2236,10 +2241,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128933970</v>
+        <v>128933904</v>
       </c>
       <c r="B16" t="n">
-        <v>91804</v>
+        <v>78432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2247,21 +2252,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>6437</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2271,13 +2276,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544900</v>
+        <v>545138</v>
       </c>
       <c r="R16" t="n">
-        <v>7198605</v>
+        <v>7198414</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2301,27 +2306,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På gammal granlåga</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2351,7 +2351,7 @@
         <v>128933968</v>
       </c>
       <c r="B17" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2460,10 +2460,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128933896</v>
+        <v>128933161</v>
       </c>
       <c r="B18" t="n">
-        <v>78881</v>
+        <v>91527</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2471,37 +2471,41 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>1204</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545160</v>
+        <v>544891</v>
       </c>
       <c r="R18" t="n">
-        <v>7198394</v>
+        <v>7198608</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2525,27 +2529,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:31</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På stående död gran med brandljud. På kol</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2560,22 +2559,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128933161</v>
+        <v>128934084</v>
       </c>
       <c r="B19" t="n">
-        <v>91522</v>
+        <v>91513</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2583,41 +2582,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544891</v>
+        <v>544966</v>
       </c>
       <c r="R19" t="n">
-        <v>7198608</v>
+        <v>7198729</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2646,7 +2641,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2656,7 +2651,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2671,22 +2666,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128934084</v>
+        <v>128933896</v>
       </c>
       <c r="B20" t="n">
-        <v>91508</v>
+        <v>78786</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2694,21 +2689,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2718,13 +2713,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544966</v>
+        <v>545160</v>
       </c>
       <c r="R20" t="n">
-        <v>7198729</v>
+        <v>7198394</v>
       </c>
       <c r="S20" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2748,22 +2743,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På stående död gran med brandljud. På kol</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2793,7 +2793,7 @@
         <v>128933932</v>
       </c>
       <c r="B21" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>128933986</v>
       </c>
       <c r="B22" t="n">
-        <v>91522</v>
+        <v>91527</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3009,10 +3009,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128933875</v>
+        <v>128933164</v>
       </c>
       <c r="B23" t="n">
-        <v>79124</v>
+        <v>80134</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3020,37 +3020,41 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>545139</v>
+        <v>544839</v>
       </c>
       <c r="R23" t="n">
-        <v>7198365</v>
+        <v>7198665</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3074,27 +3078,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:41</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Mycket god förekomst</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3109,22 +3108,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128933164</v>
+        <v>128933875</v>
       </c>
       <c r="B24" t="n">
-        <v>80229</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3132,41 +3131,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544839</v>
+        <v>545139</v>
       </c>
       <c r="R24" t="n">
-        <v>7198665</v>
+        <v>7198365</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3190,22 +3185,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Mycket god förekomst</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3220,12 +3220,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3235,7 +3235,7 @@
         <v>128933989</v>
       </c>
       <c r="B25" t="n">
-        <v>80230</v>
+        <v>80135</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v>128933165</v>
       </c>
       <c r="B26" t="n">
-        <v>80230</v>
+        <v>80135</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>128933166</v>
       </c>
       <c r="B27" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>128933879</v>
       </c>
       <c r="B28" t="n">
-        <v>88908</v>
+        <v>88913</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
         <v>128933982</v>
       </c>
       <c r="B29" t="n">
-        <v>80230</v>
+        <v>80135</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>128933158</v>
       </c>
       <c r="B30" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>128933961</v>
       </c>
       <c r="B31" t="n">
-        <v>80230</v>
+        <v>80135</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4013,10 +4013,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128933980</v>
+        <v>128933141</v>
       </c>
       <c r="B32" t="n">
-        <v>91522</v>
+        <v>79029</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4024,37 +4024,41 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>544853</v>
+        <v>545088</v>
       </c>
       <c r="R32" t="n">
-        <v>7198662</v>
+        <v>7198569</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4078,27 +4082,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Väl nedbruten låga av sälg</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4113,22 +4112,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128933141</v>
+        <v>128933156</v>
       </c>
       <c r="B33" t="n">
-        <v>79124</v>
+        <v>57723</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4136,21 +4135,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4158,16 +4157,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>545088</v>
+        <v>544879</v>
       </c>
       <c r="R33" t="n">
-        <v>7198569</v>
+        <v>7198601</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4194,22 +4201,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4229,17 +4236,17 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128933130</v>
+        <v>128933980</v>
       </c>
       <c r="B34" t="n">
-        <v>57720</v>
+        <v>91527</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4247,46 +4254,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>545144</v>
+        <v>544853</v>
       </c>
       <c r="R34" t="n">
-        <v>7198419</v>
+        <v>7198662</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4310,22 +4308,27 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Väl nedbruten låga av sälg</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4340,22 +4343,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128933213</v>
+        <v>128933130</v>
       </c>
       <c r="B35" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4385,24 +4388,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>544897</v>
+        <v>545144</v>
       </c>
       <c r="R35" t="n">
-        <v>7198529</v>
+        <v>7198419</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4429,27 +4429,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Innanför gränsen, bild finns.</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4469,17 +4464,17 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128933156</v>
+        <v>128933213</v>
       </c>
       <c r="B36" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4523,10 +4518,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>544879</v>
+        <v>544897</v>
       </c>
       <c r="R36" t="n">
-        <v>7198601</v>
+        <v>7198529</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4558,7 +4553,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4568,7 +4563,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Innanför gränsen, bild finns.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4598,7 +4598,7 @@
         <v>128934001</v>
       </c>
       <c r="B37" t="n">
-        <v>80265</v>
+        <v>80170</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         <v>128933147</v>
       </c>
       <c r="B38" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>128933212</v>
       </c>
       <c r="B39" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>128933908</v>
       </c>
       <c r="B40" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5051,10 +5051,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128933171</v>
+        <v>128933978</v>
       </c>
       <c r="B41" t="n">
-        <v>80229</v>
+        <v>91527</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5062,41 +5062,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>544807</v>
+        <v>544893</v>
       </c>
       <c r="R41" t="n">
-        <v>7198685</v>
+        <v>7198604</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5125,7 +5121,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5135,7 +5131,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På väl nedbruten låga av gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5150,22 +5151,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128933978</v>
+        <v>128933124</v>
       </c>
       <c r="B42" t="n">
-        <v>91522</v>
+        <v>79029</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5173,37 +5174,41 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>544893</v>
+        <v>545144</v>
       </c>
       <c r="R42" t="n">
-        <v>7198604</v>
+        <v>7198368</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5227,27 +5232,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:39</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På väl nedbruten låga av gran</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5262,22 +5262,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128933124</v>
+        <v>128933171</v>
       </c>
       <c r="B43" t="n">
-        <v>79124</v>
+        <v>80134</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5285,21 +5285,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5313,10 +5313,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>545144</v>
+        <v>544807</v>
       </c>
       <c r="R43" t="n">
-        <v>7198368</v>
+        <v>7198685</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5343,22 +5343,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5385,10 +5385,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128933157</v>
+        <v>128933154</v>
       </c>
       <c r="B44" t="n">
-        <v>80230</v>
+        <v>91513</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5396,21 +5396,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5424,10 +5424,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>544908</v>
+        <v>544968</v>
       </c>
       <c r="R44" t="n">
-        <v>7198602</v>
+        <v>7198730</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5469,12 +5469,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Gran, stor utbredning.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5501,10 +5501,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128933163</v>
+        <v>128933157</v>
       </c>
       <c r="B45" t="n">
-        <v>79124</v>
+        <v>80135</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5512,21 +5512,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5540,10 +5540,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>544832</v>
+        <v>544908</v>
       </c>
       <c r="R45" t="n">
-        <v>7198667</v>
+        <v>7198602</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5575,7 +5575,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5585,7 +5585,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5612,10 +5617,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128933154</v>
+        <v>128933129</v>
       </c>
       <c r="B46" t="n">
-        <v>91508</v>
+        <v>78786</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5623,21 +5628,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5651,10 +5656,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>544968</v>
+        <v>545158</v>
       </c>
       <c r="R46" t="n">
-        <v>7198730</v>
+        <v>7198403</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5681,27 +5686,27 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Gran, stor utbredning.</t>
+          <t>Liten kolad stubbe</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5728,10 +5733,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128933129</v>
+        <v>128933163</v>
       </c>
       <c r="B47" t="n">
-        <v>78881</v>
+        <v>79029</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5739,21 +5744,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5767,10 +5772,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>545158</v>
+        <v>544832</v>
       </c>
       <c r="R47" t="n">
-        <v>7198403</v>
+        <v>7198667</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5797,27 +5802,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Liten kolad stubbe</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5847,7 +5847,7 @@
         <v>128933139</v>
       </c>
       <c r="B48" t="n">
-        <v>80257</v>
+        <v>80162</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>128933966</v>
       </c>
       <c r="B49" t="n">
-        <v>80230</v>
+        <v>80135</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>128933136</v>
       </c>
       <c r="B50" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6181,7 +6181,7 @@
         <v>128933984</v>
       </c>
       <c r="B51" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>128933870</v>
       </c>
       <c r="B52" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
         <v>128933973</v>
       </c>
       <c r="B53" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6514,10 +6514,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128933947</v>
+        <v>128933167</v>
       </c>
       <c r="B54" t="n">
-        <v>91473</v>
+        <v>80038</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6525,37 +6525,41 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5447</v>
+        <v>6456</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>544971</v>
+        <v>544823</v>
       </c>
       <c r="R54" t="n">
-        <v>7198722</v>
+        <v>7198695</v>
       </c>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6584,7 +6588,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6594,7 +6598,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Asp</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6609,22 +6618,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128933167</v>
+        <v>128933947</v>
       </c>
       <c r="B55" t="n">
-        <v>80133</v>
+        <v>91478</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6632,41 +6641,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>544823</v>
+        <v>544971</v>
       </c>
       <c r="R55" t="n">
-        <v>7198695</v>
+        <v>7198722</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6695,7 +6700,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6705,12 +6710,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:14</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Asp</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6725,12 +6725,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6740,7 +6740,7 @@
         <v>128933991</v>
       </c>
       <c r="B56" t="n">
-        <v>80133</v>
+        <v>80038</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>128934086</v>
       </c>
       <c r="B57" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 13030-2025 artfynd.xlsx
+++ b/artfynd/A 13030-2025 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128933126</v>
+        <v>128933958</v>
       </c>
       <c r="B4" t="n">
-        <v>78791</v>
+        <v>80139</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,41 +910,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545150</v>
+        <v>544871</v>
       </c>
       <c r="R4" t="n">
-        <v>7198391</v>
+        <v>7198612</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -968,27 +964,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Kolad granved</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,22 +999,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128933958</v>
+        <v>128933126</v>
       </c>
       <c r="B5" t="n">
-        <v>80139</v>
+        <v>78791</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,37 +1022,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544871</v>
+        <v>545150</v>
       </c>
       <c r="R5" t="n">
-        <v>7198612</v>
+        <v>7198391</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,27 +1080,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>Kolad granved</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,12 +1115,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1350,10 +1350,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128933127</v>
+        <v>128933159</v>
       </c>
       <c r="B8" t="n">
-        <v>78791</v>
+        <v>91805</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1361,21 +1361,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545155</v>
+        <v>544907</v>
       </c>
       <c r="R8" t="n">
-        <v>7198397</v>
+        <v>7198585</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1419,22 +1419,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,10 +1461,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128933159</v>
+        <v>128933127</v>
       </c>
       <c r="B9" t="n">
-        <v>91805</v>
+        <v>78791</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544907</v>
+        <v>545155</v>
       </c>
       <c r="R9" t="n">
-        <v>7198585</v>
+        <v>7198397</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1530,22 +1530,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2460,10 +2460,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128933932</v>
+        <v>128933161</v>
       </c>
       <c r="B18" t="n">
-        <v>57723</v>
+        <v>91534</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2471,37 +2471,41 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545212</v>
+        <v>544891</v>
       </c>
       <c r="R18" t="n">
-        <v>7198500</v>
+        <v>7198608</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2530,7 +2534,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2540,12 +2544,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack äldre än 5 år på tall</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2560,22 +2559,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128933896</v>
+        <v>128934084</v>
       </c>
       <c r="B19" t="n">
-        <v>78791</v>
+        <v>91520</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2583,21 +2582,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2607,13 +2606,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545160</v>
+        <v>544966</v>
       </c>
       <c r="R19" t="n">
-        <v>7198394</v>
+        <v>7198729</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2637,27 +2636,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:31</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På stående död gran med brandljud. På kol</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2684,10 +2678,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128933161</v>
+        <v>128933932</v>
       </c>
       <c r="B20" t="n">
-        <v>91534</v>
+        <v>57723</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2695,41 +2689,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544891</v>
+        <v>545212</v>
       </c>
       <c r="R20" t="n">
-        <v>7198608</v>
+        <v>7198500</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2758,7 +2748,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2768,7 +2758,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre än 5 år på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2783,22 +2778,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128934084</v>
+        <v>128933896</v>
       </c>
       <c r="B21" t="n">
-        <v>91520</v>
+        <v>78791</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2806,21 +2801,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2830,13 +2825,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544966</v>
+        <v>545160</v>
       </c>
       <c r="R21" t="n">
-        <v>7198729</v>
+        <v>7198394</v>
       </c>
       <c r="S21" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2860,22 +2855,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På stående död gran med brandljud. På kol</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2902,10 +2902,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128933986</v>
+        <v>128933164</v>
       </c>
       <c r="B22" t="n">
-        <v>91534</v>
+        <v>80139</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2913,37 +2913,41 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544828</v>
+        <v>544839</v>
       </c>
       <c r="R22" t="n">
-        <v>7198678</v>
+        <v>7198665</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2972,7 +2976,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2982,7 +2986,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2997,22 +3001,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128933875</v>
+        <v>128933986</v>
       </c>
       <c r="B23" t="n">
-        <v>79034</v>
+        <v>91534</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3020,21 +3024,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3044,13 +3048,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>545139</v>
+        <v>544828</v>
       </c>
       <c r="R23" t="n">
-        <v>7198365</v>
+        <v>7198678</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3074,27 +3078,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:41</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Mycket god förekomst</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3121,10 +3120,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128933164</v>
+        <v>128933875</v>
       </c>
       <c r="B24" t="n">
-        <v>80139</v>
+        <v>79034</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3132,41 +3131,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544839</v>
+        <v>545139</v>
       </c>
       <c r="R24" t="n">
-        <v>7198665</v>
+        <v>7198365</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3190,22 +3185,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Mycket god förekomst</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3220,12 +3220,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -5051,10 +5051,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128933978</v>
+        <v>128933124</v>
       </c>
       <c r="B41" t="n">
-        <v>91534</v>
+        <v>79034</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5062,37 +5062,41 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>544893</v>
+        <v>545144</v>
       </c>
       <c r="R41" t="n">
-        <v>7198604</v>
+        <v>7198368</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5116,27 +5120,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:39</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På väl nedbruten låga av gran</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5151,22 +5150,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128933124</v>
+        <v>128933978</v>
       </c>
       <c r="B42" t="n">
-        <v>79034</v>
+        <v>91534</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5174,41 +5173,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>545144</v>
+        <v>544893</v>
       </c>
       <c r="R42" t="n">
-        <v>7198368</v>
+        <v>7198604</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5232,22 +5227,27 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På väl nedbruten låga av gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5262,12 +5262,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>

--- a/artfynd/A 13030-2025 artfynd.xlsx
+++ b/artfynd/A 13030-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128933955</v>
       </c>
       <c r="B2" t="n">
-        <v>92191</v>
+        <v>92196</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>128933159</v>
       </c>
       <c r="B8" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128933125</v>
+        <v>128933999</v>
       </c>
       <c r="B11" t="n">
-        <v>88920</v>
+        <v>80139</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,41 +1694,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545148</v>
+        <v>544807</v>
       </c>
       <c r="R11" t="n">
-        <v>7198360</v>
+        <v>7198677</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1752,22 +1748,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På gammal sälg i sluttning</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1782,12 +1783,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1906,48 +1907,52 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128933999</v>
+        <v>128933172</v>
       </c>
       <c r="B13" t="n">
-        <v>80139</v>
+        <v>80175</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544807</v>
+        <v>544801</v>
       </c>
       <c r="R13" t="n">
-        <v>7198677</v>
+        <v>7198690</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1976,7 +1981,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1986,12 +1991,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På gammal sälg i sluttning</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2006,44 +2006,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128933172</v>
+        <v>128933125</v>
       </c>
       <c r="B14" t="n">
-        <v>80175</v>
+        <v>88923</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>510</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2057,10 +2057,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544801</v>
+        <v>545148</v>
       </c>
       <c r="R14" t="n">
-        <v>7198690</v>
+        <v>7198360</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2087,22 +2087,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2132,7 +2132,7 @@
         <v>128933970</v>
       </c>
       <c r="B15" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         <v>128933161</v>
       </c>
       <c r="B18" t="n">
-        <v>91534</v>
+        <v>91537</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         <v>128934084</v>
       </c>
       <c r="B19" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2671,17 +2671,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128933932</v>
+        <v>128933896</v>
       </c>
       <c r="B20" t="n">
-        <v>57723</v>
+        <v>78791</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2689,21 +2689,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545212</v>
+        <v>545160</v>
       </c>
       <c r="R20" t="n">
-        <v>7198500</v>
+        <v>7198394</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2743,27 +2743,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre än 5 år på tall</t>
+          <t>På stående död gran med brandljud. På kol</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2790,10 +2790,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128933896</v>
+        <v>128933932</v>
       </c>
       <c r="B21" t="n">
-        <v>78791</v>
+        <v>57723</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2801,21 +2801,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545160</v>
+        <v>545212</v>
       </c>
       <c r="R21" t="n">
-        <v>7198394</v>
+        <v>7198500</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -2855,27 +2855,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På stående död gran med brandljud. På kol</t>
+          <t>Ringhack äldre än 5 år på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2902,10 +2902,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128933164</v>
+        <v>128933875</v>
       </c>
       <c r="B22" t="n">
-        <v>80139</v>
+        <v>79034</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2913,41 +2913,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544839</v>
+        <v>545139</v>
       </c>
       <c r="R22" t="n">
-        <v>7198665</v>
+        <v>7198365</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2971,22 +2967,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Mycket god förekomst</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3001,12 +3002,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3016,7 +3017,7 @@
         <v>128933986</v>
       </c>
       <c r="B23" t="n">
-        <v>91534</v>
+        <v>91537</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3113,17 +3114,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128933875</v>
+        <v>128933164</v>
       </c>
       <c r="B24" t="n">
-        <v>79034</v>
+        <v>80139</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3131,37 +3132,41 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>545139</v>
+        <v>544839</v>
       </c>
       <c r="R24" t="n">
-        <v>7198365</v>
+        <v>7198665</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3185,27 +3190,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:41</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Mycket god förekomst</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3220,22 +3220,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128933989</v>
+        <v>128933166</v>
       </c>
       <c r="B25" t="n">
-        <v>80140</v>
+        <v>80139</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3243,37 +3243,41 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544830</v>
+        <v>544839</v>
       </c>
       <c r="R25" t="n">
-        <v>7198678</v>
+        <v>7198683</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3302,7 +3306,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3312,12 +3316,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På sälglåga</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3332,12 +3331,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3455,10 +3454,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128933166</v>
+        <v>128933989</v>
       </c>
       <c r="B27" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,41 +3465,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>544839</v>
+        <v>544830</v>
       </c>
       <c r="R27" t="n">
-        <v>7198683</v>
+        <v>7198678</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3529,7 +3524,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3539,7 +3534,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3554,22 +3554,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128933879</v>
+        <v>128933982</v>
       </c>
       <c r="B28" t="n">
-        <v>88920</v>
+        <v>80140</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3577,21 +3577,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>510</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>545153</v>
+        <v>544845</v>
       </c>
       <c r="R28" t="n">
-        <v>7198363</v>
+        <v>7198663</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3631,27 +3631,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:50</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På låga av tall</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3671,17 +3666,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128933982</v>
+        <v>128933879</v>
       </c>
       <c r="B29" t="n">
-        <v>80140</v>
+        <v>88923</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3689,21 +3684,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>510</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3713,10 +3708,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544845</v>
+        <v>545153</v>
       </c>
       <c r="R29" t="n">
-        <v>7198663</v>
+        <v>7198363</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -3743,22 +3738,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På låga av tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3904,7 +3904,7 @@
         <v>128933980</v>
       </c>
       <c r="B31" t="n">
-        <v>91534</v>
+        <v>91537</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4125,10 +4125,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128933130</v>
+        <v>128933141</v>
       </c>
       <c r="B33" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4136,21 +4136,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4158,21 +4158,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>545144</v>
+        <v>545088</v>
       </c>
       <c r="R33" t="n">
-        <v>7198419</v>
+        <v>7198569</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4204,7 +4199,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4214,7 +4209,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4241,7 +4236,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128933213</v>
+        <v>128933156</v>
       </c>
       <c r="B34" t="n">
         <v>57723</v>
@@ -4288,10 +4283,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>544897</v>
+        <v>544879</v>
       </c>
       <c r="R34" t="n">
-        <v>7198529</v>
+        <v>7198601</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4323,7 +4318,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4333,12 +4328,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Innanför gränsen, bild finns.</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4358,14 +4348,14 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Edvin Strandberg, Petter Lindwall, David Kenger</t>
+          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128933156</v>
+        <v>128933130</v>
       </c>
       <c r="B35" t="n">
         <v>57723</v>
@@ -4398,24 +4388,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>544879</v>
+        <v>545144</v>
       </c>
       <c r="R35" t="n">
-        <v>7198601</v>
+        <v>7198419</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4442,22 +4429,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4477,17 +4464,17 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Edvin Strandberg, Petter Lindwall, David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128933141</v>
+        <v>128933213</v>
       </c>
       <c r="B36" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4495,21 +4482,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4517,16 +4504,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>545088</v>
+        <v>544897</v>
       </c>
       <c r="R36" t="n">
-        <v>7198569</v>
+        <v>7198529</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4553,22 +4548,27 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Innanför gränsen, bild finns.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4588,64 +4588,55 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128933147</v>
+        <v>128934001</v>
       </c>
       <c r="B37" t="n">
-        <v>57723</v>
+        <v>80175</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>545204</v>
+        <v>544806</v>
       </c>
       <c r="R37" t="n">
-        <v>7198506</v>
+        <v>7198678</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4674,7 +4665,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4684,7 +4675,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4699,19 +4695,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128933212</v>
+        <v>128933147</v>
       </c>
       <c r="B38" t="n">
         <v>57723</v>
@@ -4755,10 +4751,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>544911</v>
+        <v>545204</v>
       </c>
       <c r="R38" t="n">
-        <v>7198620</v>
+        <v>7198506</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4790,7 +4786,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4800,7 +4796,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4827,48 +4823,57 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128934001</v>
+        <v>128933212</v>
       </c>
       <c r="B39" t="n">
-        <v>80175</v>
+        <v>57723</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>544806</v>
+        <v>544911</v>
       </c>
       <c r="R39" t="n">
-        <v>7198678</v>
+        <v>7198620</v>
       </c>
       <c r="S39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4897,7 +4902,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4907,12 +4912,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:21</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4927,12 +4927,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5051,10 +5051,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128933124</v>
+        <v>128933978</v>
       </c>
       <c r="B41" t="n">
-        <v>79034</v>
+        <v>91537</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5062,41 +5062,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>545144</v>
+        <v>544893</v>
       </c>
       <c r="R41" t="n">
-        <v>7198368</v>
+        <v>7198604</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5120,22 +5116,27 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På väl nedbruten låga av gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5150,22 +5151,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128933978</v>
+        <v>128933124</v>
       </c>
       <c r="B42" t="n">
-        <v>91534</v>
+        <v>79034</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5173,37 +5174,41 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>544893</v>
+        <v>545144</v>
       </c>
       <c r="R42" t="n">
-        <v>7198604</v>
+        <v>7198368</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5227,27 +5232,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:39</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På väl nedbruten låga av gran</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5262,12 +5262,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5385,10 +5385,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128933154</v>
+        <v>128933157</v>
       </c>
       <c r="B44" t="n">
-        <v>91520</v>
+        <v>80140</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5396,21 +5396,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5424,10 +5424,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>544968</v>
+        <v>544908</v>
       </c>
       <c r="R44" t="n">
-        <v>7198730</v>
+        <v>7198602</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5469,12 +5469,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Gran, stor utbredning.</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5501,10 +5501,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128933157</v>
+        <v>128933154</v>
       </c>
       <c r="B45" t="n">
-        <v>80140</v>
+        <v>91523</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5512,21 +5512,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5540,10 +5540,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>544908</v>
+        <v>544968</v>
       </c>
       <c r="R45" t="n">
-        <v>7198602</v>
+        <v>7198730</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5575,7 +5575,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5585,12 +5585,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Gran, stor utbredning.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6067,10 +6067,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128933870</v>
+        <v>128933136</v>
       </c>
       <c r="B50" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6078,37 +6078,41 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>545136</v>
+        <v>545109</v>
       </c>
       <c r="R50" t="n">
-        <v>7198363</v>
+        <v>7198551</v>
       </c>
       <c r="S50" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6137,7 +6141,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6147,12 +6151,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Nya ringbarkningar från tretåig hackspett på gran.</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6167,22 +6166,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128933973</v>
+        <v>128933984</v>
       </c>
       <c r="B51" t="n">
-        <v>57723</v>
+        <v>80139</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6190,21 +6189,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6214,10 +6213,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>544900</v>
+        <v>544836</v>
       </c>
       <c r="R51" t="n">
-        <v>7198597</v>
+        <v>7198663</v>
       </c>
       <c r="S51" t="n">
         <v>4</v>
@@ -6249,7 +6248,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6259,12 +6258,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack äldre än 5 år på gran</t>
+          <t>Högt upp på gammal sälg</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6284,17 +6283,17 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128933136</v>
+        <v>128933870</v>
       </c>
       <c r="B52" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6302,41 +6301,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>545109</v>
+        <v>545136</v>
       </c>
       <c r="R52" t="n">
-        <v>7198551</v>
+        <v>7198363</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6365,7 +6360,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6375,7 +6370,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Nya ringbarkningar från tretåig hackspett på gran.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6390,22 +6390,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128933984</v>
+        <v>128933973</v>
       </c>
       <c r="B53" t="n">
-        <v>80139</v>
+        <v>57723</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6413,21 +6413,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6437,10 +6437,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>544836</v>
+        <v>544900</v>
       </c>
       <c r="R53" t="n">
-        <v>7198663</v>
+        <v>7198597</v>
       </c>
       <c r="S53" t="n">
         <v>4</v>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6482,12 +6482,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Högt upp på gammal sälg</t>
+          <t>Ringhack äldre än 5 år på gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6507,17 +6507,17 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128933947</v>
+        <v>128933167</v>
       </c>
       <c r="B54" t="n">
-        <v>91485</v>
+        <v>80043</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6525,37 +6525,41 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5447</v>
+        <v>6456</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>544971</v>
+        <v>544823</v>
       </c>
       <c r="R54" t="n">
-        <v>7198722</v>
+        <v>7198695</v>
       </c>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6584,7 +6588,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6594,7 +6598,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Asp</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6609,22 +6618,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128933167</v>
+        <v>128933947</v>
       </c>
       <c r="B55" t="n">
-        <v>80043</v>
+        <v>91488</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6632,41 +6641,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>544823</v>
+        <v>544971</v>
       </c>
       <c r="R55" t="n">
-        <v>7198695</v>
+        <v>7198722</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6695,7 +6700,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6705,12 +6710,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:14</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Asp</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6725,44 +6725,44 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128934086</v>
+        <v>128933991</v>
       </c>
       <c r="B56" t="n">
-        <v>57723</v>
+        <v>80043</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6772,10 +6772,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>544908</v>
+        <v>544826</v>
       </c>
       <c r="R56" t="n">
-        <v>7198615</v>
+        <v>7198694</v>
       </c>
       <c r="S56" t="n">
         <v>4</v>
@@ -6807,7 +6807,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6842,39 +6842,39 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128933991</v>
+        <v>128934086</v>
       </c>
       <c r="B57" t="n">
-        <v>80043</v>
+        <v>57723</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6884,10 +6884,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>544826</v>
+        <v>544908</v>
       </c>
       <c r="R57" t="n">
-        <v>7198694</v>
+        <v>7198615</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -6919,7 +6919,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>

--- a/artfynd/A 13030-2025 artfynd.xlsx
+++ b/artfynd/A 13030-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128933955</v>
       </c>
       <c r="B2" t="n">
-        <v>92196</v>
+        <v>92199</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>128933901</v>
       </c>
       <c r="B3" t="n">
-        <v>83010</v>
+        <v>83011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>128933958</v>
       </c>
       <c r="B4" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>128933126</v>
       </c>
       <c r="B5" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>128933155</v>
       </c>
       <c r="B6" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>128933159</v>
       </c>
       <c r="B8" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>128933127</v>
       </c>
       <c r="B9" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>128933131</v>
       </c>
       <c r="B10" t="n">
-        <v>80167</v>
+        <v>80168</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,48 +1683,52 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128933999</v>
+        <v>128933172</v>
       </c>
       <c r="B11" t="n">
-        <v>80139</v>
+        <v>80176</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544807</v>
+        <v>544801</v>
       </c>
       <c r="R11" t="n">
-        <v>7198677</v>
+        <v>7198690</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1753,7 +1757,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,12 +1767,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På gammal sälg i sluttning</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1783,22 +1782,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128933891</v>
+        <v>128933125</v>
       </c>
       <c r="B12" t="n">
-        <v>78791</v>
+        <v>88926</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,37 +1805,41 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>510</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545149</v>
+        <v>545148</v>
       </c>
       <c r="R12" t="n">
-        <v>7198384</v>
+        <v>7198360</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1865,7 +1868,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1875,12 +1878,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På död naken gran med brandljud. På kol.</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1895,64 +1893,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128933172</v>
+        <v>128933999</v>
       </c>
       <c r="B13" t="n">
-        <v>80175</v>
+        <v>80140</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544801</v>
+        <v>544807</v>
       </c>
       <c r="R13" t="n">
-        <v>7198690</v>
+        <v>7198677</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1981,7 +1975,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1991,7 +1985,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På gammal sälg i sluttning</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2006,22 +2005,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128933125</v>
+        <v>128933891</v>
       </c>
       <c r="B14" t="n">
-        <v>88923</v>
+        <v>78792</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2029,41 +2028,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>510</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545148</v>
+        <v>545149</v>
       </c>
       <c r="R14" t="n">
-        <v>7198360</v>
+        <v>7198384</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2092,7 +2087,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2102,7 +2097,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På död naken gran med brandljud. På kol.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2117,22 +2117,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128933970</v>
+        <v>128933904</v>
       </c>
       <c r="B15" t="n">
-        <v>91808</v>
+        <v>78438</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2140,21 +2140,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>6437</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2164,13 +2164,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544900</v>
+        <v>545138</v>
       </c>
       <c r="R15" t="n">
-        <v>7198605</v>
+        <v>7198414</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2194,27 +2194,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På gammal granlåga</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2241,10 +2236,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128933904</v>
+        <v>128933970</v>
       </c>
       <c r="B16" t="n">
-        <v>78437</v>
+        <v>91811</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2252,21 +2247,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6437</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2276,13 +2271,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>545138</v>
+        <v>544900</v>
       </c>
       <c r="R16" t="n">
-        <v>7198414</v>
+        <v>7198605</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2306,22 +2301,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2351,7 +2351,7 @@
         <v>128933968</v>
       </c>
       <c r="B17" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2460,10 +2460,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128933161</v>
+        <v>128933896</v>
       </c>
       <c r="B18" t="n">
-        <v>91537</v>
+        <v>78792</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2471,41 +2471,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1204</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544891</v>
+        <v>545160</v>
       </c>
       <c r="R18" t="n">
-        <v>7198608</v>
+        <v>7198394</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2529,22 +2525,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På stående död gran med brandljud. På kol</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2559,22 +2560,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128934084</v>
+        <v>128933932</v>
       </c>
       <c r="B19" t="n">
-        <v>91523</v>
+        <v>57723</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2582,21 +2583,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2606,13 +2607,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544966</v>
+        <v>545212</v>
       </c>
       <c r="R19" t="n">
-        <v>7198729</v>
+        <v>7198500</v>
       </c>
       <c r="S19" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2641,7 +2642,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2651,7 +2652,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre än 5 år på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2671,17 +2677,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128933896</v>
+        <v>128933161</v>
       </c>
       <c r="B20" t="n">
-        <v>78791</v>
+        <v>91540</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2689,37 +2695,41 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>1204</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545160</v>
+        <v>544891</v>
       </c>
       <c r="R20" t="n">
-        <v>7198394</v>
+        <v>7198608</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2743,27 +2753,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:31</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På stående död gran med brandljud. På kol</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2778,22 +2783,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128933932</v>
+        <v>128934084</v>
       </c>
       <c r="B21" t="n">
-        <v>57723</v>
+        <v>91526</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2801,21 +2806,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2825,13 +2830,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545212</v>
+        <v>544966</v>
       </c>
       <c r="R21" t="n">
-        <v>7198500</v>
+        <v>7198729</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2860,7 +2865,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2870,12 +2875,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack äldre än 5 år på tall</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2902,10 +2902,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128933875</v>
+        <v>128933986</v>
       </c>
       <c r="B22" t="n">
-        <v>79034</v>
+        <v>91540</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2913,21 +2913,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2937,13 +2937,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>545139</v>
+        <v>544828</v>
       </c>
       <c r="R22" t="n">
-        <v>7198365</v>
+        <v>7198678</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2967,27 +2967,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:41</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Mycket god förekomst</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3014,10 +3009,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128933986</v>
+        <v>128933875</v>
       </c>
       <c r="B23" t="n">
-        <v>91537</v>
+        <v>79035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3025,21 +3020,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3049,13 +3044,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544828</v>
+        <v>545139</v>
       </c>
       <c r="R23" t="n">
-        <v>7198678</v>
+        <v>7198365</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3079,22 +3074,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Mycket god förekomst</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3124,7 +3124,7 @@
         <v>128933164</v>
       </c>
       <c r="B24" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>128933166</v>
       </c>
       <c r="B25" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3343,10 +3343,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128933165</v>
+        <v>128933989</v>
       </c>
       <c r="B26" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3371,24 +3371,20 @@
           <t>(Scop.) DC.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>544837</v>
+        <v>544830</v>
       </c>
       <c r="R26" t="n">
-        <v>7198665</v>
+        <v>7198678</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3417,7 +3413,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3427,7 +3423,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3442,22 +3443,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128933989</v>
+        <v>128933165</v>
       </c>
       <c r="B27" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3482,20 +3483,24 @@
           <t>(Scop.) DC.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>544830</v>
+        <v>544837</v>
       </c>
       <c r="R27" t="n">
-        <v>7198678</v>
+        <v>7198665</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3524,7 +3529,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3534,12 +3539,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På sälglåga</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3554,12 +3554,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3569,7 +3569,7 @@
         <v>128933982</v>
       </c>
       <c r="B28" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3666,17 +3666,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128933879</v>
+        <v>128933158</v>
       </c>
       <c r="B29" t="n">
-        <v>88923</v>
+        <v>57723</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3684,37 +3684,46 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>545153</v>
+        <v>544903</v>
       </c>
       <c r="R29" t="n">
-        <v>7198363</v>
+        <v>7198597</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3738,27 +3747,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:50</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På låga av tall</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3773,22 +3777,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128933158</v>
+        <v>128933879</v>
       </c>
       <c r="B30" t="n">
-        <v>57723</v>
+        <v>88926</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3796,46 +3800,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>544903</v>
+        <v>545153</v>
       </c>
       <c r="R30" t="n">
-        <v>7198597</v>
+        <v>7198363</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3859,22 +3854,27 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På låga av tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3889,22 +3889,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128933980</v>
+        <v>128933961</v>
       </c>
       <c r="B31" t="n">
-        <v>91537</v>
+        <v>80141</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3912,21 +3912,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1204</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3936,13 +3936,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>544853</v>
+        <v>544872</v>
       </c>
       <c r="R31" t="n">
-        <v>7198662</v>
+        <v>7198610</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Väl nedbruten låga av sälg</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4006,17 +4006,17 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128933961</v>
+        <v>128933980</v>
       </c>
       <c r="B32" t="n">
-        <v>80140</v>
+        <v>91540</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4024,21 +4024,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4048,13 +4048,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>544872</v>
+        <v>544853</v>
       </c>
       <c r="R32" t="n">
-        <v>7198610</v>
+        <v>7198662</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>Väl nedbruten låga av sälg</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4128,7 +4128,7 @@
         <v>128933141</v>
       </c>
       <c r="B33" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128933156</v>
+        <v>128933130</v>
       </c>
       <c r="B34" t="n">
         <v>57723</v>
@@ -4269,24 +4269,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>544879</v>
+        <v>545144</v>
       </c>
       <c r="R34" t="n">
-        <v>7198601</v>
+        <v>7198419</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4313,22 +4310,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4348,14 +4345,14 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128933130</v>
+        <v>128933213</v>
       </c>
       <c r="B35" t="n">
         <v>57723</v>
@@ -4388,21 +4385,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>545144</v>
+        <v>544897</v>
       </c>
       <c r="R35" t="n">
-        <v>7198419</v>
+        <v>7198529</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4429,22 +4429,27 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Innanför gränsen, bild finns.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4464,14 +4469,14 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128933213</v>
+        <v>128933156</v>
       </c>
       <c r="B36" t="n">
         <v>57723</v>
@@ -4518,10 +4523,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>544897</v>
+        <v>544879</v>
       </c>
       <c r="R36" t="n">
-        <v>7198529</v>
+        <v>7198601</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4553,7 +4558,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4563,12 +4568,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Innanför gränsen, bild finns.</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4598,7 +4598,7 @@
         <v>128934001</v>
       </c>
       <c r="B37" t="n">
-        <v>80175</v>
+        <v>80176</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -5054,7 +5054,7 @@
         <v>128933978</v>
       </c>
       <c r="B41" t="n">
-        <v>91537</v>
+        <v>91540</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5166,7 +5166,7 @@
         <v>128933124</v>
       </c>
       <c r="B42" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>128933171</v>
       </c>
       <c r="B43" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5385,10 +5385,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128933157</v>
+        <v>128933163</v>
       </c>
       <c r="B44" t="n">
-        <v>80140</v>
+        <v>79035</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5396,21 +5396,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5424,10 +5424,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>544908</v>
+        <v>544832</v>
       </c>
       <c r="R44" t="n">
-        <v>7198602</v>
+        <v>7198667</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5469,12 +5469,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Sälg</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5501,10 +5496,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128933154</v>
+        <v>128933129</v>
       </c>
       <c r="B45" t="n">
-        <v>91523</v>
+        <v>78792</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5512,21 +5507,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5540,10 +5535,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>544968</v>
+        <v>545158</v>
       </c>
       <c r="R45" t="n">
-        <v>7198730</v>
+        <v>7198403</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5570,27 +5565,27 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Gran, stor utbredning.</t>
+          <t>Liten kolad stubbe</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5617,10 +5612,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128933163</v>
+        <v>128933157</v>
       </c>
       <c r="B46" t="n">
-        <v>79034</v>
+        <v>80141</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5628,21 +5623,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5656,10 +5651,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>544832</v>
+        <v>544908</v>
       </c>
       <c r="R46" t="n">
-        <v>7198667</v>
+        <v>7198602</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5691,7 +5686,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5701,7 +5696,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5728,10 +5728,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128933129</v>
+        <v>128933154</v>
       </c>
       <c r="B47" t="n">
-        <v>78791</v>
+        <v>91526</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5739,21 +5739,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>545158</v>
+        <v>544968</v>
       </c>
       <c r="R47" t="n">
-        <v>7198403</v>
+        <v>7198730</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5797,27 +5797,27 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Liten kolad stubbe</t>
+          <t>Gran, stor utbredning.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5847,7 +5847,7 @@
         <v>128933139</v>
       </c>
       <c r="B48" t="n">
-        <v>80167</v>
+        <v>80168</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>128933966</v>
       </c>
       <c r="B49" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>128933136</v>
       </c>
       <c r="B50" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6181,7 +6181,7 @@
         <v>128933984</v>
       </c>
       <c r="B51" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6507,17 +6507,17 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128933167</v>
+        <v>128933947</v>
       </c>
       <c r="B54" t="n">
-        <v>80043</v>
+        <v>91491</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6525,41 +6525,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>544823</v>
+        <v>544971</v>
       </c>
       <c r="R54" t="n">
-        <v>7198695</v>
+        <v>7198722</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6588,7 +6584,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6598,12 +6594,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:14</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Asp</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6618,22 +6609,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128933947</v>
+        <v>128933167</v>
       </c>
       <c r="B55" t="n">
-        <v>91488</v>
+        <v>80044</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6641,37 +6632,41 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>6456</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>544971</v>
+        <v>544823</v>
       </c>
       <c r="R55" t="n">
-        <v>7198722</v>
+        <v>7198695</v>
       </c>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6700,7 +6695,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6710,7 +6705,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Asp</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6725,44 +6725,44 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128933991</v>
+        <v>128934086</v>
       </c>
       <c r="B56" t="n">
-        <v>80043</v>
+        <v>57723</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6772,10 +6772,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>544826</v>
+        <v>544908</v>
       </c>
       <c r="R56" t="n">
-        <v>7198694</v>
+        <v>7198615</v>
       </c>
       <c r="S56" t="n">
         <v>4</v>
@@ -6807,7 +6807,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6842,39 +6842,39 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128934086</v>
+        <v>128933991</v>
       </c>
       <c r="B57" t="n">
-        <v>57723</v>
+        <v>80044</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6884,10 +6884,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>544908</v>
+        <v>544826</v>
       </c>
       <c r="R57" t="n">
-        <v>7198615</v>
+        <v>7198694</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -6919,7 +6919,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>

--- a/artfynd/A 13030-2025 artfynd.xlsx
+++ b/artfynd/A 13030-2025 artfynd.xlsx
@@ -1127,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128933155</v>
+        <v>128933902</v>
       </c>
       <c r="B6" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,41 +1138,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544955</v>
+        <v>545147</v>
       </c>
       <c r="R6" t="n">
-        <v>7198720</v>
+        <v>7198430</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1196,22 +1192,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gamla ringbarkningar på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1226,22 +1227,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128933902</v>
+        <v>128933155</v>
       </c>
       <c r="B7" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1249,37 +1250,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545147</v>
+        <v>544955</v>
       </c>
       <c r="R7" t="n">
-        <v>7198430</v>
+        <v>7198720</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,27 +1308,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:51</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Gamla ringbarkningar på tall</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1338,22 +1338,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128933159</v>
+        <v>128933127</v>
       </c>
       <c r="B8" t="n">
-        <v>91811</v>
+        <v>78792</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1361,21 +1361,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544907</v>
+        <v>545155</v>
       </c>
       <c r="R8" t="n">
-        <v>7198585</v>
+        <v>7198397</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1419,22 +1419,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,10 +1461,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128933127</v>
+        <v>128933159</v>
       </c>
       <c r="B9" t="n">
-        <v>78792</v>
+        <v>91811</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545155</v>
+        <v>544907</v>
       </c>
       <c r="R9" t="n">
-        <v>7198397</v>
+        <v>7198585</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1530,22 +1530,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2129,10 +2129,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128933904</v>
+        <v>128933970</v>
       </c>
       <c r="B15" t="n">
-        <v>78438</v>
+        <v>91811</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2140,21 +2140,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6437</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2164,13 +2164,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545138</v>
+        <v>544900</v>
       </c>
       <c r="R15" t="n">
-        <v>7198414</v>
+        <v>7198605</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2194,22 +2194,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2236,10 +2241,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128933970</v>
+        <v>128933904</v>
       </c>
       <c r="B16" t="n">
-        <v>91811</v>
+        <v>78438</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2247,21 +2252,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>6437</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2271,13 +2276,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544900</v>
+        <v>545138</v>
       </c>
       <c r="R16" t="n">
-        <v>7198605</v>
+        <v>7198414</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2301,27 +2306,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På gammal granlåga</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2460,10 +2460,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128933896</v>
+        <v>128933161</v>
       </c>
       <c r="B18" t="n">
-        <v>78792</v>
+        <v>91540</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2471,37 +2471,41 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>1204</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545160</v>
+        <v>544891</v>
       </c>
       <c r="R18" t="n">
-        <v>7198394</v>
+        <v>7198608</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2525,27 +2529,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:31</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På stående död gran med brandljud. På kol</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2560,22 +2559,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128933932</v>
+        <v>128934084</v>
       </c>
       <c r="B19" t="n">
-        <v>57723</v>
+        <v>91526</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2583,21 +2582,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2607,13 +2606,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545212</v>
+        <v>544966</v>
       </c>
       <c r="R19" t="n">
-        <v>7198500</v>
+        <v>7198729</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2642,7 +2641,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2652,12 +2651,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack äldre än 5 år på tall</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2684,10 +2678,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128933161</v>
+        <v>128933896</v>
       </c>
       <c r="B20" t="n">
-        <v>91540</v>
+        <v>78792</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2695,41 +2689,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1204</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544891</v>
+        <v>545160</v>
       </c>
       <c r="R20" t="n">
-        <v>7198608</v>
+        <v>7198394</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2753,22 +2743,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På stående död gran med brandljud. På kol</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2783,22 +2778,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128934084</v>
+        <v>128933932</v>
       </c>
       <c r="B21" t="n">
-        <v>91526</v>
+        <v>57723</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2806,21 +2801,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2830,13 +2825,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544966</v>
+        <v>545212</v>
       </c>
       <c r="R21" t="n">
-        <v>7198729</v>
+        <v>7198500</v>
       </c>
       <c r="S21" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2865,7 +2860,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2875,7 +2870,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre än 5 år på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3009,10 +3009,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128933875</v>
+        <v>128933164</v>
       </c>
       <c r="B23" t="n">
-        <v>79035</v>
+        <v>80140</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3020,37 +3020,41 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>545139</v>
+        <v>544839</v>
       </c>
       <c r="R23" t="n">
-        <v>7198365</v>
+        <v>7198665</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3074,27 +3078,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:41</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Mycket god förekomst</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3109,22 +3108,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128933164</v>
+        <v>128933875</v>
       </c>
       <c r="B24" t="n">
-        <v>80140</v>
+        <v>79035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3132,41 +3131,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544839</v>
+        <v>545139</v>
       </c>
       <c r="R24" t="n">
-        <v>7198665</v>
+        <v>7198365</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3190,22 +3185,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Mycket god förekomst</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3220,22 +3220,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128933166</v>
+        <v>128933989</v>
       </c>
       <c r="B25" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3243,41 +3243,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544839</v>
+        <v>544830</v>
       </c>
       <c r="R25" t="n">
-        <v>7198683</v>
+        <v>7198678</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3306,7 +3302,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3316,7 +3312,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3331,19 +3332,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128933989</v>
+        <v>128933165</v>
       </c>
       <c r="B26" t="n">
         <v>80141</v>
@@ -3371,20 +3372,24 @@
           <t>(Scop.) DC.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>544830</v>
+        <v>544837</v>
       </c>
       <c r="R26" t="n">
-        <v>7198678</v>
+        <v>7198665</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3413,7 +3418,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3423,12 +3428,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På sälglåga</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3443,22 +3443,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128933165</v>
+        <v>128933166</v>
       </c>
       <c r="B27" t="n">
-        <v>80141</v>
+        <v>80140</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,21 +3466,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3494,10 +3494,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>544837</v>
+        <v>544839</v>
       </c>
       <c r="R27" t="n">
-        <v>7198665</v>
+        <v>7198683</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3539,7 +3539,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3566,10 +3566,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128933982</v>
+        <v>128933879</v>
       </c>
       <c r="B28" t="n">
-        <v>80141</v>
+        <v>88926</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3577,21 +3577,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>510</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>544845</v>
+        <v>545153</v>
       </c>
       <c r="R28" t="n">
-        <v>7198663</v>
+        <v>7198363</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3631,22 +3631,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På låga av tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3789,10 +3794,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128933879</v>
+        <v>128933982</v>
       </c>
       <c r="B30" t="n">
-        <v>88926</v>
+        <v>80141</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3800,21 +3805,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>510</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3824,10 +3829,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>545153</v>
+        <v>544845</v>
       </c>
       <c r="R30" t="n">
-        <v>7198363</v>
+        <v>7198663</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -3854,27 +3859,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:50</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På låga av tall</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4013,10 +4013,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128933980</v>
+        <v>128933130</v>
       </c>
       <c r="B32" t="n">
-        <v>91540</v>
+        <v>57723</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4024,37 +4024,46 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>544853</v>
+        <v>545144</v>
       </c>
       <c r="R32" t="n">
-        <v>7198662</v>
+        <v>7198419</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4078,27 +4087,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Väl nedbruten låga av sälg</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4113,22 +4117,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128933141</v>
+        <v>128933213</v>
       </c>
       <c r="B33" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4136,21 +4140,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4158,16 +4162,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>545088</v>
+        <v>544897</v>
       </c>
       <c r="R33" t="n">
-        <v>7198569</v>
+        <v>7198529</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4194,22 +4206,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Innanför gränsen, bild finns.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4229,14 +4246,14 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128933130</v>
+        <v>128933156</v>
       </c>
       <c r="B34" t="n">
         <v>57723</v>
@@ -4269,21 +4286,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>545144</v>
+        <v>544879</v>
       </c>
       <c r="R34" t="n">
-        <v>7198419</v>
+        <v>7198601</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4310,22 +4330,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4345,17 +4365,17 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128933213</v>
+        <v>128933980</v>
       </c>
       <c r="B35" t="n">
-        <v>57723</v>
+        <v>91540</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4363,49 +4383,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>544897</v>
+        <v>544853</v>
       </c>
       <c r="R35" t="n">
-        <v>7198529</v>
+        <v>7198662</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4434,7 +4442,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4444,12 +4452,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Innanför gränsen, bild finns.</t>
+          <t>Väl nedbruten låga av sälg</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4464,22 +4472,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128933156</v>
+        <v>128933141</v>
       </c>
       <c r="B36" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4487,21 +4495,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4509,24 +4517,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>544879</v>
+        <v>545088</v>
       </c>
       <c r="R36" t="n">
-        <v>7198601</v>
+        <v>7198569</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4553,22 +4553,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4707,7 +4707,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128933147</v>
+        <v>128933212</v>
       </c>
       <c r="B38" t="n">
         <v>57723</v>
@@ -4751,10 +4751,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>545204</v>
+        <v>544911</v>
       </c>
       <c r="R38" t="n">
-        <v>7198506</v>
+        <v>7198620</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4823,10 +4823,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128933212</v>
+        <v>128933908</v>
       </c>
       <c r="B39" t="n">
-        <v>57723</v>
+        <v>57883</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4834,46 +4834,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>544911</v>
+        <v>545139</v>
       </c>
       <c r="R39" t="n">
-        <v>7198620</v>
+        <v>7198504</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4897,22 +4888,27 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Två talltitor</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4927,22 +4923,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128933908</v>
+        <v>128933147</v>
       </c>
       <c r="B40" t="n">
-        <v>57883</v>
+        <v>57723</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4950,37 +4946,46 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>545139</v>
+        <v>545204</v>
       </c>
       <c r="R40" t="n">
-        <v>7198504</v>
+        <v>7198506</v>
       </c>
       <c r="S40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5004,27 +5009,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Två talltitor</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5039,12 +5039,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5385,10 +5385,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128933163</v>
+        <v>128933157</v>
       </c>
       <c r="B44" t="n">
-        <v>79035</v>
+        <v>80141</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5396,21 +5396,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5424,10 +5424,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>544832</v>
+        <v>544908</v>
       </c>
       <c r="R44" t="n">
-        <v>7198667</v>
+        <v>7198602</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5469,7 +5469,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5496,10 +5501,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128933129</v>
+        <v>128933154</v>
       </c>
       <c r="B45" t="n">
-        <v>78792</v>
+        <v>91526</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5507,21 +5512,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5535,10 +5540,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>545158</v>
+        <v>544968</v>
       </c>
       <c r="R45" t="n">
-        <v>7198403</v>
+        <v>7198730</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5565,27 +5570,27 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Liten kolad stubbe</t>
+          <t>Gran, stor utbredning.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5612,10 +5617,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128933157</v>
+        <v>128933163</v>
       </c>
       <c r="B46" t="n">
-        <v>80141</v>
+        <v>79035</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5623,21 +5628,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5651,10 +5656,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>544908</v>
+        <v>544832</v>
       </c>
       <c r="R46" t="n">
-        <v>7198602</v>
+        <v>7198667</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5686,7 +5691,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5696,12 +5701,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Sälg</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5728,10 +5728,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128933154</v>
+        <v>128933129</v>
       </c>
       <c r="B47" t="n">
-        <v>91526</v>
+        <v>78792</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5739,21 +5739,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>544968</v>
+        <v>545158</v>
       </c>
       <c r="R47" t="n">
-        <v>7198730</v>
+        <v>7198403</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5797,27 +5797,27 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Gran, stor utbredning.</t>
+          <t>Liten kolad stubbe</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6067,10 +6067,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128933136</v>
+        <v>128933984</v>
       </c>
       <c r="B50" t="n">
-        <v>79035</v>
+        <v>80140</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6078,41 +6078,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>545109</v>
+        <v>544836</v>
       </c>
       <c r="R50" t="n">
-        <v>7198551</v>
+        <v>7198663</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6136,22 +6132,27 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Högt upp på gammal sälg</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6166,22 +6167,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128933984</v>
+        <v>128933136</v>
       </c>
       <c r="B51" t="n">
-        <v>80140</v>
+        <v>79035</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6189,37 +6190,41 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>544836</v>
+        <v>545109</v>
       </c>
       <c r="R51" t="n">
-        <v>7198663</v>
+        <v>7198551</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6243,27 +6248,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:56</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Högt upp på gammal sälg</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6278,12 +6278,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6737,32 +6737,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128934086</v>
+        <v>128933991</v>
       </c>
       <c r="B56" t="n">
-        <v>57723</v>
+        <v>80044</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6772,10 +6772,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>544908</v>
+        <v>544826</v>
       </c>
       <c r="R56" t="n">
-        <v>7198615</v>
+        <v>7198694</v>
       </c>
       <c r="S56" t="n">
         <v>4</v>
@@ -6807,7 +6807,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6849,32 +6849,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128933991</v>
+        <v>128934086</v>
       </c>
       <c r="B57" t="n">
-        <v>80044</v>
+        <v>57723</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6884,10 +6884,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>544826</v>
+        <v>544908</v>
       </c>
       <c r="R57" t="n">
-        <v>7198694</v>
+        <v>7198615</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -6919,7 +6919,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 13030-2025 artfynd.xlsx
+++ b/artfynd/A 13030-2025 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128933958</v>
+        <v>128933126</v>
       </c>
       <c r="B4" t="n">
-        <v>80140</v>
+        <v>78792</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,37 +910,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544871</v>
+        <v>545150</v>
       </c>
       <c r="R4" t="n">
-        <v>7198612</v>
+        <v>7198391</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,27 +968,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>Kolad granved</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,22 +1003,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128933126</v>
+        <v>128933958</v>
       </c>
       <c r="B5" t="n">
-        <v>78792</v>
+        <v>80140</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,41 +1026,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545150</v>
+        <v>544871</v>
       </c>
       <c r="R5" t="n">
-        <v>7198391</v>
+        <v>7198612</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,27 +1080,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Kolad granved</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,12 +1115,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1350,10 +1350,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128933127</v>
+        <v>128933159</v>
       </c>
       <c r="B8" t="n">
-        <v>78792</v>
+        <v>91811</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1361,21 +1361,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545155</v>
+        <v>544907</v>
       </c>
       <c r="R8" t="n">
-        <v>7198397</v>
+        <v>7198585</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1419,22 +1419,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,10 +1461,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128933159</v>
+        <v>128933127</v>
       </c>
       <c r="B9" t="n">
-        <v>91811</v>
+        <v>78792</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544907</v>
+        <v>545155</v>
       </c>
       <c r="R9" t="n">
-        <v>7198585</v>
+        <v>7198397</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1530,22 +1530,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1683,32 +1683,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128933172</v>
+        <v>128933125</v>
       </c>
       <c r="B11" t="n">
-        <v>80176</v>
+        <v>88926</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>510</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544801</v>
+        <v>545148</v>
       </c>
       <c r="R11" t="n">
-        <v>7198690</v>
+        <v>7198360</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1752,22 +1752,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1794,10 +1794,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128933125</v>
+        <v>128933999</v>
       </c>
       <c r="B12" t="n">
-        <v>88926</v>
+        <v>80140</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,41 +1805,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545148</v>
+        <v>544807</v>
       </c>
       <c r="R12" t="n">
-        <v>7198360</v>
+        <v>7198677</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1863,22 +1859,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På gammal sälg i sluttning</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1893,22 +1894,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128933999</v>
+        <v>128933891</v>
       </c>
       <c r="B13" t="n">
-        <v>80140</v>
+        <v>78792</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1916,21 +1917,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1940,10 +1941,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544807</v>
+        <v>545149</v>
       </c>
       <c r="R13" t="n">
-        <v>7198677</v>
+        <v>7198384</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -1970,27 +1971,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gammal sälg i sluttning</t>
+          <t>På död naken gran med brandljud. På kol.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2017,48 +2018,52 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128933891</v>
+        <v>128933172</v>
       </c>
       <c r="B14" t="n">
-        <v>78792</v>
+        <v>80176</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545149</v>
+        <v>544801</v>
       </c>
       <c r="R14" t="n">
-        <v>7198384</v>
+        <v>7198690</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2082,27 +2087,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På död naken gran med brandljud. På kol.</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2117,12 +2117,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2460,10 +2460,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128933161</v>
+        <v>128933896</v>
       </c>
       <c r="B18" t="n">
-        <v>91540</v>
+        <v>78792</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2471,41 +2471,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1204</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544891</v>
+        <v>545160</v>
       </c>
       <c r="R18" t="n">
-        <v>7198608</v>
+        <v>7198394</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2529,22 +2525,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På stående död gran med brandljud. På kol</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2559,22 +2560,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128934084</v>
+        <v>128933932</v>
       </c>
       <c r="B19" t="n">
-        <v>91526</v>
+        <v>57723</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2582,21 +2583,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2606,13 +2607,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544966</v>
+        <v>545212</v>
       </c>
       <c r="R19" t="n">
-        <v>7198729</v>
+        <v>7198500</v>
       </c>
       <c r="S19" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2641,7 +2642,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2651,7 +2652,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre än 5 år på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2678,10 +2684,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128933896</v>
+        <v>128933161</v>
       </c>
       <c r="B20" t="n">
-        <v>78792</v>
+        <v>91540</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2689,37 +2695,41 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>1204</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545160</v>
+        <v>544891</v>
       </c>
       <c r="R20" t="n">
-        <v>7198394</v>
+        <v>7198608</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2743,27 +2753,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:31</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På stående död gran med brandljud. På kol</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2778,22 +2783,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128933932</v>
+        <v>128934084</v>
       </c>
       <c r="B21" t="n">
-        <v>57723</v>
+        <v>91526</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2801,21 +2806,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2825,13 +2830,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545212</v>
+        <v>544966</v>
       </c>
       <c r="R21" t="n">
-        <v>7198500</v>
+        <v>7198729</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2860,7 +2865,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2870,12 +2875,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack äldre än 5 år på tall</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -4707,7 +4707,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128933212</v>
+        <v>128933147</v>
       </c>
       <c r="B38" t="n">
         <v>57723</v>
@@ -4751,10 +4751,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>544911</v>
+        <v>545204</v>
       </c>
       <c r="R38" t="n">
-        <v>7198620</v>
+        <v>7198506</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4823,10 +4823,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128933908</v>
+        <v>128933212</v>
       </c>
       <c r="B39" t="n">
-        <v>57883</v>
+        <v>57723</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4834,37 +4834,46 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>545139</v>
+        <v>544911</v>
       </c>
       <c r="R39" t="n">
-        <v>7198504</v>
+        <v>7198620</v>
       </c>
       <c r="S39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4888,27 +4897,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Två talltitor</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4923,22 +4927,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128933147</v>
+        <v>128933908</v>
       </c>
       <c r="B40" t="n">
-        <v>57723</v>
+        <v>57883</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4946,46 +4950,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>545204</v>
+        <v>545139</v>
       </c>
       <c r="R40" t="n">
-        <v>7198506</v>
+        <v>7198504</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5009,22 +5004,27 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Två talltitor</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5039,12 +5039,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>

--- a/artfynd/A 13030-2025 artfynd.xlsx
+++ b/artfynd/A 13030-2025 artfynd.xlsx
@@ -1127,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128933902</v>
+        <v>128933155</v>
       </c>
       <c r="B6" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,37 +1138,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545147</v>
+        <v>544955</v>
       </c>
       <c r="R6" t="n">
-        <v>7198430</v>
+        <v>7198720</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1192,27 +1196,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:51</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gamla ringbarkningar på tall</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1227,22 +1226,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128933155</v>
+        <v>128933902</v>
       </c>
       <c r="B7" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1250,41 +1249,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544955</v>
+        <v>545147</v>
       </c>
       <c r="R7" t="n">
-        <v>7198720</v>
+        <v>7198430</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1308,22 +1303,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gamla ringbarkningar på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1338,22 +1338,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128933159</v>
+        <v>128933127</v>
       </c>
       <c r="B8" t="n">
-        <v>91811</v>
+        <v>78792</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1361,21 +1361,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544907</v>
+        <v>545155</v>
       </c>
       <c r="R8" t="n">
-        <v>7198585</v>
+        <v>7198397</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1419,22 +1419,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,10 +1461,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128933127</v>
+        <v>128933159</v>
       </c>
       <c r="B9" t="n">
-        <v>78792</v>
+        <v>91811</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545155</v>
+        <v>544907</v>
       </c>
       <c r="R9" t="n">
-        <v>7198397</v>
+        <v>7198585</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1530,22 +1530,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1683,32 +1683,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128933125</v>
+        <v>128933172</v>
       </c>
       <c r="B11" t="n">
-        <v>88926</v>
+        <v>80176</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>510</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545148</v>
+        <v>544801</v>
       </c>
       <c r="R11" t="n">
-        <v>7198360</v>
+        <v>7198690</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1752,22 +1752,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2018,32 +2018,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128933172</v>
+        <v>128933125</v>
       </c>
       <c r="B14" t="n">
-        <v>80176</v>
+        <v>88926</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>510</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2057,10 +2057,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544801</v>
+        <v>545148</v>
       </c>
       <c r="R14" t="n">
-        <v>7198690</v>
+        <v>7198360</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2087,22 +2087,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2460,10 +2460,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128933896</v>
+        <v>128934084</v>
       </c>
       <c r="B18" t="n">
-        <v>78792</v>
+        <v>91526</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2471,21 +2471,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2495,13 +2495,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545160</v>
+        <v>544966</v>
       </c>
       <c r="R18" t="n">
-        <v>7198394</v>
+        <v>7198729</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2525,27 +2525,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:31</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På stående död gran med brandljud. På kol</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2572,10 +2567,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128933932</v>
+        <v>128933161</v>
       </c>
       <c r="B19" t="n">
-        <v>57723</v>
+        <v>91540</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2583,37 +2578,41 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545212</v>
+        <v>544891</v>
       </c>
       <c r="R19" t="n">
-        <v>7198500</v>
+        <v>7198608</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2642,7 +2641,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2652,12 +2651,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack äldre än 5 år på tall</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2672,22 +2666,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128933161</v>
+        <v>128933896</v>
       </c>
       <c r="B20" t="n">
-        <v>91540</v>
+        <v>78792</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2695,41 +2689,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1204</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544891</v>
+        <v>545160</v>
       </c>
       <c r="R20" t="n">
-        <v>7198608</v>
+        <v>7198394</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2753,22 +2743,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På stående död gran med brandljud. På kol</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2783,22 +2778,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128934084</v>
+        <v>128933932</v>
       </c>
       <c r="B21" t="n">
-        <v>91526</v>
+        <v>57723</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2806,21 +2801,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2830,13 +2825,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544966</v>
+        <v>545212</v>
       </c>
       <c r="R21" t="n">
-        <v>7198729</v>
+        <v>7198500</v>
       </c>
       <c r="S21" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2865,7 +2860,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2875,7 +2870,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre än 5 år på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2902,10 +2902,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128933986</v>
+        <v>128933164</v>
       </c>
       <c r="B22" t="n">
-        <v>91540</v>
+        <v>80140</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2913,37 +2913,41 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544828</v>
+        <v>544839</v>
       </c>
       <c r="R22" t="n">
-        <v>7198678</v>
+        <v>7198665</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2972,7 +2976,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2982,7 +2986,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2997,22 +3001,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128933164</v>
+        <v>128933875</v>
       </c>
       <c r="B23" t="n">
-        <v>80140</v>
+        <v>79035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3020,41 +3024,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544839</v>
+        <v>545139</v>
       </c>
       <c r="R23" t="n">
-        <v>7198665</v>
+        <v>7198365</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3078,22 +3078,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Mycket god förekomst</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3108,22 +3113,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128933875</v>
+        <v>128933986</v>
       </c>
       <c r="B24" t="n">
-        <v>79035</v>
+        <v>91540</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3131,21 +3136,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3155,13 +3160,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>545139</v>
+        <v>544828</v>
       </c>
       <c r="R24" t="n">
-        <v>7198365</v>
+        <v>7198678</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3185,27 +3190,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:41</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Mycket god förekomst</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3232,7 +3232,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128933989</v>
+        <v>128933165</v>
       </c>
       <c r="B25" t="n">
         <v>80141</v>
@@ -3260,20 +3260,24 @@
           <t>(Scop.) DC.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544830</v>
+        <v>544837</v>
       </c>
       <c r="R25" t="n">
-        <v>7198678</v>
+        <v>7198665</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3302,7 +3306,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3312,12 +3316,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På sälglåga</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3332,19 +3331,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128933165</v>
+        <v>128933989</v>
       </c>
       <c r="B26" t="n">
         <v>80141</v>
@@ -3372,24 +3371,20 @@
           <t>(Scop.) DC.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>544837</v>
+        <v>544830</v>
       </c>
       <c r="R26" t="n">
-        <v>7198665</v>
+        <v>7198678</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3418,7 +3413,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3428,7 +3423,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3443,12 +3443,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3566,10 +3566,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128933879</v>
+        <v>128933982</v>
       </c>
       <c r="B28" t="n">
-        <v>88926</v>
+        <v>80141</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3577,21 +3577,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>510</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>545153</v>
+        <v>544845</v>
       </c>
       <c r="R28" t="n">
-        <v>7198363</v>
+        <v>7198663</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3631,27 +3631,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:50</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På låga av tall</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3794,10 +3789,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128933982</v>
+        <v>128933879</v>
       </c>
       <c r="B30" t="n">
-        <v>80141</v>
+        <v>88926</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3805,21 +3800,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>510</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3829,10 +3824,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>544845</v>
+        <v>545153</v>
       </c>
       <c r="R30" t="n">
-        <v>7198663</v>
+        <v>7198363</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -3859,22 +3854,27 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På låga av tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3901,10 +3901,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128933961</v>
+        <v>128933980</v>
       </c>
       <c r="B31" t="n">
-        <v>80141</v>
+        <v>91540</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3912,21 +3912,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3936,13 +3936,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>544872</v>
+        <v>544853</v>
       </c>
       <c r="R31" t="n">
-        <v>7198610</v>
+        <v>7198662</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>Väl nedbruten låga av sälg</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4013,10 +4013,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128933130</v>
+        <v>128933961</v>
       </c>
       <c r="B32" t="n">
-        <v>57723</v>
+        <v>80141</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4024,46 +4024,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>545144</v>
+        <v>544872</v>
       </c>
       <c r="R32" t="n">
-        <v>7198419</v>
+        <v>7198610</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4087,22 +4078,27 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4117,22 +4113,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128933213</v>
+        <v>128933141</v>
       </c>
       <c r="B33" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4140,21 +4136,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4162,24 +4158,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>544897</v>
+        <v>545088</v>
       </c>
       <c r="R33" t="n">
-        <v>7198529</v>
+        <v>7198569</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4206,27 +4194,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Innanför gränsen, bild finns.</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4246,14 +4229,14 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128933156</v>
+        <v>128933130</v>
       </c>
       <c r="B34" t="n">
         <v>57723</v>
@@ -4286,24 +4269,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>544879</v>
+        <v>545144</v>
       </c>
       <c r="R34" t="n">
-        <v>7198601</v>
+        <v>7198419</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4330,22 +4310,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4365,17 +4345,17 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128933980</v>
+        <v>128933213</v>
       </c>
       <c r="B35" t="n">
-        <v>91540</v>
+        <v>57723</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4383,37 +4363,49 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>544853</v>
+        <v>544897</v>
       </c>
       <c r="R35" t="n">
-        <v>7198662</v>
+        <v>7198529</v>
       </c>
       <c r="S35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4442,7 +4434,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4452,12 +4444,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Väl nedbruten låga av sälg</t>
+          <t>Innanför gränsen, bild finns.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4472,22 +4464,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128933141</v>
+        <v>128933156</v>
       </c>
       <c r="B36" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4495,21 +4487,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4517,16 +4509,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>545088</v>
+        <v>544879</v>
       </c>
       <c r="R36" t="n">
-        <v>7198569</v>
+        <v>7198601</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4553,22 +4553,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -5051,10 +5051,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128933978</v>
+        <v>128933171</v>
       </c>
       <c r="B41" t="n">
-        <v>91540</v>
+        <v>80140</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5062,37 +5062,41 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>544893</v>
+        <v>544807</v>
       </c>
       <c r="R41" t="n">
-        <v>7198604</v>
+        <v>7198685</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5121,7 +5125,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5131,12 +5135,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:39</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På väl nedbruten låga av gran</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5151,12 +5150,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5274,10 +5273,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128933171</v>
+        <v>128933978</v>
       </c>
       <c r="B43" t="n">
-        <v>80140</v>
+        <v>91540</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5285,41 +5284,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>544807</v>
+        <v>544893</v>
       </c>
       <c r="R43" t="n">
-        <v>7198685</v>
+        <v>7198604</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5348,7 +5343,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5358,7 +5353,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På väl nedbruten låga av gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5373,22 +5373,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128933157</v>
+        <v>128933154</v>
       </c>
       <c r="B44" t="n">
-        <v>80141</v>
+        <v>91526</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5396,21 +5396,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5424,10 +5424,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>544908</v>
+        <v>544968</v>
       </c>
       <c r="R44" t="n">
-        <v>7198602</v>
+        <v>7198730</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5469,12 +5469,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Gran, stor utbredning.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5501,10 +5501,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128933154</v>
+        <v>128933157</v>
       </c>
       <c r="B45" t="n">
-        <v>91526</v>
+        <v>80141</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5512,21 +5512,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5540,10 +5540,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>544968</v>
+        <v>544908</v>
       </c>
       <c r="R45" t="n">
-        <v>7198730</v>
+        <v>7198602</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5575,7 +5575,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5585,12 +5585,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Gran, stor utbredning.</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6067,10 +6067,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128933984</v>
+        <v>128933870</v>
       </c>
       <c r="B50" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6078,21 +6078,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6102,10 +6102,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>544836</v>
+        <v>545136</v>
       </c>
       <c r="R50" t="n">
-        <v>7198663</v>
+        <v>7198363</v>
       </c>
       <c r="S50" t="n">
         <v>4</v>
@@ -6132,27 +6132,27 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Högt upp på gammal sälg</t>
+          <t>Nya ringbarkningar från tretåig hackspett på gran.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6179,10 +6179,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128933136</v>
+        <v>128933973</v>
       </c>
       <c r="B51" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6190,41 +6190,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>545109</v>
+        <v>544900</v>
       </c>
       <c r="R51" t="n">
-        <v>7198551</v>
+        <v>7198597</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6248,22 +6244,27 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack äldre än 5 år på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6278,22 +6279,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128933870</v>
+        <v>128933984</v>
       </c>
       <c r="B52" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6301,21 +6302,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6325,10 +6326,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>545136</v>
+        <v>544836</v>
       </c>
       <c r="R52" t="n">
-        <v>7198363</v>
+        <v>7198663</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6355,27 +6356,27 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Nya ringbarkningar från tretåig hackspett på gran.</t>
+          <t>Högt upp på gammal sälg</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6402,10 +6403,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128933973</v>
+        <v>128933136</v>
       </c>
       <c r="B53" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6413,37 +6414,41 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>544900</v>
+        <v>545109</v>
       </c>
       <c r="R53" t="n">
-        <v>7198597</v>
+        <v>7198551</v>
       </c>
       <c r="S53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6467,27 +6472,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack äldre än 5 år på gran</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6502,12 +6502,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>

--- a/artfynd/A 13030-2025 artfynd.xlsx
+++ b/artfynd/A 13030-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128933955</v>
       </c>
       <c r="B2" t="n">
-        <v>92199</v>
+        <v>92206</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>128933901</v>
       </c>
       <c r="B3" t="n">
-        <v>83011</v>
+        <v>83015</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128933126</v>
+        <v>128933958</v>
       </c>
       <c r="B4" t="n">
-        <v>78792</v>
+        <v>80144</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,41 +910,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545150</v>
+        <v>544871</v>
       </c>
       <c r="R4" t="n">
-        <v>7198391</v>
+        <v>7198612</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -968,27 +964,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Kolad granved</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,22 +999,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128933958</v>
+        <v>128933126</v>
       </c>
       <c r="B5" t="n">
-        <v>80140</v>
+        <v>78796</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,37 +1022,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544871</v>
+        <v>545150</v>
       </c>
       <c r="R5" t="n">
-        <v>7198612</v>
+        <v>7198391</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,27 +1080,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>Kolad granved</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,12 +1115,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1130,7 +1130,7 @@
         <v>128933155</v>
       </c>
       <c r="B6" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>128933902</v>
       </c>
       <c r="B7" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,10 +1350,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128933127</v>
+        <v>128933159</v>
       </c>
       <c r="B8" t="n">
-        <v>78792</v>
+        <v>91818</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1361,21 +1361,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545155</v>
+        <v>544907</v>
       </c>
       <c r="R8" t="n">
-        <v>7198397</v>
+        <v>7198585</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1419,22 +1419,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,10 +1461,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128933159</v>
+        <v>128933127</v>
       </c>
       <c r="B9" t="n">
-        <v>91811</v>
+        <v>78796</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544907</v>
+        <v>545155</v>
       </c>
       <c r="R9" t="n">
-        <v>7198585</v>
+        <v>7198397</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1530,22 +1530,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,7 +1575,7 @@
         <v>128933131</v>
       </c>
       <c r="B10" t="n">
-        <v>80168</v>
+        <v>80172</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,52 +1683,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128933172</v>
+        <v>128933999</v>
       </c>
       <c r="B11" t="n">
-        <v>80176</v>
+        <v>80144</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544801</v>
+        <v>544807</v>
       </c>
       <c r="R11" t="n">
-        <v>7198690</v>
+        <v>7198677</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1757,7 +1753,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1767,7 +1763,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På gammal sälg i sluttning</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1782,60 +1783,64 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128933999</v>
+        <v>128933172</v>
       </c>
       <c r="B12" t="n">
-        <v>80140</v>
+        <v>80180</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544807</v>
+        <v>544801</v>
       </c>
       <c r="R12" t="n">
-        <v>7198677</v>
+        <v>7198690</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1864,7 +1869,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1874,12 +1879,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På gammal sälg i sluttning</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1894,22 +1894,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128933891</v>
+        <v>128933125</v>
       </c>
       <c r="B13" t="n">
-        <v>78792</v>
+        <v>88930</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1917,37 +1917,41 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>510</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545149</v>
+        <v>545148</v>
       </c>
       <c r="R13" t="n">
-        <v>7198384</v>
+        <v>7198360</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1976,7 +1980,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1986,12 +1990,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På död naken gran med brandljud. På kol.</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2006,22 +2005,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128933125</v>
+        <v>128933891</v>
       </c>
       <c r="B14" t="n">
-        <v>88926</v>
+        <v>78796</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2029,41 +2028,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>510</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545148</v>
+        <v>545149</v>
       </c>
       <c r="R14" t="n">
-        <v>7198360</v>
+        <v>7198384</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2092,7 +2087,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2102,7 +2097,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På död naken gran med brandljud. På kol.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2117,12 +2117,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2132,7 +2132,7 @@
         <v>128933970</v>
       </c>
       <c r="B15" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>128933904</v>
       </c>
       <c r="B16" t="n">
-        <v>78438</v>
+        <v>78442</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>128933968</v>
       </c>
       <c r="B17" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2460,10 +2460,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128934084</v>
+        <v>128933161</v>
       </c>
       <c r="B18" t="n">
-        <v>91526</v>
+        <v>91547</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2471,37 +2471,41 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544966</v>
+        <v>544891</v>
       </c>
       <c r="R18" t="n">
-        <v>7198729</v>
+        <v>7198608</v>
       </c>
       <c r="S18" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2530,7 +2534,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2540,7 +2544,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2555,22 +2559,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128933161</v>
+        <v>128934084</v>
       </c>
       <c r="B19" t="n">
-        <v>91540</v>
+        <v>91533</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2578,41 +2582,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544891</v>
+        <v>544966</v>
       </c>
       <c r="R19" t="n">
-        <v>7198608</v>
+        <v>7198729</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2666,12 +2666,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2681,7 +2681,7 @@
         <v>128933896</v>
       </c>
       <c r="B20" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>128933932</v>
       </c>
       <c r="B21" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2902,10 +2902,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128933164</v>
+        <v>128933875</v>
       </c>
       <c r="B22" t="n">
-        <v>80140</v>
+        <v>79039</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2913,41 +2913,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544839</v>
+        <v>545139</v>
       </c>
       <c r="R22" t="n">
-        <v>7198665</v>
+        <v>7198365</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2971,22 +2967,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Mycket god förekomst</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3001,22 +3002,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128933875</v>
+        <v>128933986</v>
       </c>
       <c r="B23" t="n">
-        <v>79035</v>
+        <v>91547</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3024,21 +3025,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3048,13 +3049,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>545139</v>
+        <v>544828</v>
       </c>
       <c r="R23" t="n">
-        <v>7198365</v>
+        <v>7198678</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3078,27 +3079,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:41</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Mycket god förekomst</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3125,10 +3121,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128933986</v>
+        <v>128933164</v>
       </c>
       <c r="B24" t="n">
-        <v>91540</v>
+        <v>80144</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3136,37 +3132,41 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544828</v>
+        <v>544839</v>
       </c>
       <c r="R24" t="n">
-        <v>7198678</v>
+        <v>7198665</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3220,22 +3220,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128933165</v>
+        <v>128933989</v>
       </c>
       <c r="B25" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3260,24 +3260,20 @@
           <t>(Scop.) DC.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544837</v>
+        <v>544830</v>
       </c>
       <c r="R25" t="n">
-        <v>7198665</v>
+        <v>7198678</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3306,7 +3302,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3316,7 +3312,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3331,22 +3332,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128933989</v>
+        <v>128933165</v>
       </c>
       <c r="B26" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3371,20 +3372,24 @@
           <t>(Scop.) DC.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>544830</v>
+        <v>544837</v>
       </c>
       <c r="R26" t="n">
-        <v>7198678</v>
+        <v>7198665</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3413,7 +3418,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3423,12 +3428,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På sälglåga</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3443,12 +3443,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3458,7 +3458,7 @@
         <v>128933166</v>
       </c>
       <c r="B27" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>128933982</v>
       </c>
       <c r="B28" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3673,10 +3673,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128933158</v>
+        <v>128933879</v>
       </c>
       <c r="B29" t="n">
-        <v>57723</v>
+        <v>88930</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3684,46 +3684,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544903</v>
+        <v>545153</v>
       </c>
       <c r="R29" t="n">
-        <v>7198597</v>
+        <v>7198363</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3747,22 +3738,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På låga av tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3777,22 +3773,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128933879</v>
+        <v>128933158</v>
       </c>
       <c r="B30" t="n">
-        <v>88926</v>
+        <v>57725</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3800,37 +3796,46 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>545153</v>
+        <v>544903</v>
       </c>
       <c r="R30" t="n">
-        <v>7198363</v>
+        <v>7198597</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3854,27 +3859,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:50</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På låga av tall</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3889,22 +3889,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128933980</v>
+        <v>128933141</v>
       </c>
       <c r="B31" t="n">
-        <v>91540</v>
+        <v>79039</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3912,37 +3912,41 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>544853</v>
+        <v>545088</v>
       </c>
       <c r="R31" t="n">
-        <v>7198662</v>
+        <v>7198569</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3966,27 +3970,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Väl nedbruten låga av sälg</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4001,12 +4000,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4016,7 +4015,7 @@
         <v>128933961</v>
       </c>
       <c r="B32" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4125,10 +4124,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128933141</v>
+        <v>128933980</v>
       </c>
       <c r="B33" t="n">
-        <v>79035</v>
+        <v>91547</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4136,41 +4135,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>545088</v>
+        <v>544853</v>
       </c>
       <c r="R33" t="n">
-        <v>7198569</v>
+        <v>7198662</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4194,22 +4189,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Väl nedbruten låga av sälg</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4224,12 +4224,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4239,7 +4239,7 @@
         <v>128933130</v>
       </c>
       <c r="B34" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>128933213</v>
       </c>
       <c r="B35" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>128933156</v>
       </c>
       <c r="B36" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         <v>128934001</v>
       </c>
       <c r="B37" t="n">
-        <v>80176</v>
+        <v>80180</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         <v>128933147</v>
       </c>
       <c r="B38" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>128933212</v>
       </c>
       <c r="B39" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>128933908</v>
       </c>
       <c r="B40" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>128933171</v>
       </c>
       <c r="B41" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5162,10 +5162,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128933124</v>
+        <v>128933978</v>
       </c>
       <c r="B42" t="n">
-        <v>79035</v>
+        <v>91547</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5173,41 +5173,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>545144</v>
+        <v>544893</v>
       </c>
       <c r="R42" t="n">
-        <v>7198368</v>
+        <v>7198604</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5231,22 +5227,27 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På väl nedbruten låga av gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5261,22 +5262,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128933978</v>
+        <v>128933124</v>
       </c>
       <c r="B43" t="n">
-        <v>91540</v>
+        <v>79039</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5284,37 +5285,41 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>544893</v>
+        <v>545144</v>
       </c>
       <c r="R43" t="n">
-        <v>7198604</v>
+        <v>7198368</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5338,27 +5343,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:39</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På väl nedbruten låga av gran</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5373,22 +5373,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128933154</v>
+        <v>128933163</v>
       </c>
       <c r="B44" t="n">
-        <v>91526</v>
+        <v>79039</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5396,21 +5396,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5424,10 +5424,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>544968</v>
+        <v>544832</v>
       </c>
       <c r="R44" t="n">
-        <v>7198730</v>
+        <v>7198667</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5469,12 +5469,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Gran, stor utbredning.</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5501,10 +5496,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128933157</v>
+        <v>128933129</v>
       </c>
       <c r="B45" t="n">
-        <v>80141</v>
+        <v>78796</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5512,21 +5507,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5540,10 +5535,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>544908</v>
+        <v>545158</v>
       </c>
       <c r="R45" t="n">
-        <v>7198602</v>
+        <v>7198403</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5570,27 +5565,27 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Liten kolad stubbe</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5617,10 +5612,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128933163</v>
+        <v>128933157</v>
       </c>
       <c r="B46" t="n">
-        <v>79035</v>
+        <v>80145</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5628,21 +5623,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5656,10 +5651,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>544832</v>
+        <v>544908</v>
       </c>
       <c r="R46" t="n">
-        <v>7198667</v>
+        <v>7198602</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5691,7 +5686,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5701,7 +5696,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5728,10 +5728,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128933129</v>
+        <v>128933154</v>
       </c>
       <c r="B47" t="n">
-        <v>78792</v>
+        <v>91533</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5739,21 +5739,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>545158</v>
+        <v>544968</v>
       </c>
       <c r="R47" t="n">
-        <v>7198403</v>
+        <v>7198730</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5797,27 +5797,27 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Liten kolad stubbe</t>
+          <t>Gran, stor utbredning.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5847,7 +5847,7 @@
         <v>128933139</v>
       </c>
       <c r="B48" t="n">
-        <v>80168</v>
+        <v>80172</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5955,10 +5955,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128933966</v>
+        <v>128933870</v>
       </c>
       <c r="B49" t="n">
-        <v>80141</v>
+        <v>57725</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5966,21 +5966,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5990,13 +5990,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>544905</v>
+        <v>545136</v>
       </c>
       <c r="R49" t="n">
-        <v>7198603</v>
+        <v>7198363</v>
       </c>
       <c r="S49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6020,27 +6020,27 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>Nya ringbarkningar från tretåig hackspett på gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6067,10 +6067,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128933870</v>
+        <v>128933973</v>
       </c>
       <c r="B50" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6102,10 +6102,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>545136</v>
+        <v>544900</v>
       </c>
       <c r="R50" t="n">
-        <v>7198363</v>
+        <v>7198597</v>
       </c>
       <c r="S50" t="n">
         <v>4</v>
@@ -6132,27 +6132,27 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Nya ringbarkningar från tretåig hackspett på gran.</t>
+          <t>Ringhack äldre än 5 år på gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6179,10 +6179,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128933973</v>
+        <v>128933966</v>
       </c>
       <c r="B51" t="n">
-        <v>57723</v>
+        <v>80145</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6190,21 +6190,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6214,13 +6214,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>544900</v>
+        <v>544905</v>
       </c>
       <c r="R51" t="n">
-        <v>7198597</v>
+        <v>7198603</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack äldre än 5 år på gran</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6294,7 +6294,7 @@
         <v>128933984</v>
       </c>
       <c r="B52" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>128933136</v>
       </c>
       <c r="B53" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6514,10 +6514,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128933947</v>
+        <v>128933167</v>
       </c>
       <c r="B54" t="n">
-        <v>91491</v>
+        <v>80048</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6525,37 +6525,41 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5447</v>
+        <v>6456</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>544971</v>
+        <v>544823</v>
       </c>
       <c r="R54" t="n">
-        <v>7198722</v>
+        <v>7198695</v>
       </c>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6584,7 +6588,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6594,7 +6598,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Asp</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6609,22 +6618,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128933167</v>
+        <v>128933947</v>
       </c>
       <c r="B55" t="n">
-        <v>80044</v>
+        <v>91497</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6632,41 +6641,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>544823</v>
+        <v>544971</v>
       </c>
       <c r="R55" t="n">
-        <v>7198695</v>
+        <v>7198722</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6695,7 +6700,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6705,12 +6710,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:14</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Asp</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6725,44 +6725,44 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128933991</v>
+        <v>128934086</v>
       </c>
       <c r="B56" t="n">
-        <v>80044</v>
+        <v>57725</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6772,10 +6772,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>544826</v>
+        <v>544908</v>
       </c>
       <c r="R56" t="n">
-        <v>7198694</v>
+        <v>7198615</v>
       </c>
       <c r="S56" t="n">
         <v>4</v>
@@ -6807,7 +6807,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6849,32 +6849,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128934086</v>
+        <v>128933991</v>
       </c>
       <c r="B57" t="n">
-        <v>57723</v>
+        <v>80048</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6884,10 +6884,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>544908</v>
+        <v>544826</v>
       </c>
       <c r="R57" t="n">
-        <v>7198615</v>
+        <v>7198694</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -6919,7 +6919,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 13030-2025 artfynd.xlsx
+++ b/artfynd/A 13030-2025 artfynd.xlsx
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128933999</v>
+        <v>128933125</v>
       </c>
       <c r="B11" t="n">
-        <v>80144</v>
+        <v>88930</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,37 +1694,41 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544807</v>
+        <v>545148</v>
       </c>
       <c r="R11" t="n">
-        <v>7198677</v>
+        <v>7198360</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1748,27 +1752,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På gammal sälg i sluttning</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1783,64 +1782,60 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128933172</v>
+        <v>128933891</v>
       </c>
       <c r="B12" t="n">
-        <v>80180</v>
+        <v>78796</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6464</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544801</v>
+        <v>545149</v>
       </c>
       <c r="R12" t="n">
-        <v>7198690</v>
+        <v>7198384</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1864,22 +1859,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På död naken gran med brandljud. På kol.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1894,22 +1894,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128933125</v>
+        <v>128933999</v>
       </c>
       <c r="B13" t="n">
-        <v>88930</v>
+        <v>80144</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1917,41 +1917,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545148</v>
+        <v>544807</v>
       </c>
       <c r="R13" t="n">
-        <v>7198360</v>
+        <v>7198677</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1975,22 +1971,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På gammal sälg i sluttning</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2005,60 +2006,64 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128933891</v>
+        <v>128933172</v>
       </c>
       <c r="B14" t="n">
-        <v>78796</v>
+        <v>80180</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545149</v>
+        <v>544801</v>
       </c>
       <c r="R14" t="n">
-        <v>7198384</v>
+        <v>7198690</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2082,27 +2087,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På död naken gran med brandljud. På kol.</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2117,12 +2117,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2460,10 +2460,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128933161</v>
+        <v>128933932</v>
       </c>
       <c r="B18" t="n">
-        <v>91547</v>
+        <v>57725</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2471,41 +2471,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544891</v>
+        <v>545212</v>
       </c>
       <c r="R18" t="n">
-        <v>7198608</v>
+        <v>7198500</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2534,7 +2530,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2544,7 +2540,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre än 5 år på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2559,22 +2560,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128934084</v>
+        <v>128933161</v>
       </c>
       <c r="B19" t="n">
-        <v>91533</v>
+        <v>91547</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2582,37 +2583,41 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544966</v>
+        <v>544891</v>
       </c>
       <c r="R19" t="n">
-        <v>7198729</v>
+        <v>7198608</v>
       </c>
       <c r="S19" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2641,7 +2646,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2651,7 +2656,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2666,22 +2671,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128933896</v>
+        <v>128934084</v>
       </c>
       <c r="B20" t="n">
-        <v>78796</v>
+        <v>91533</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2689,21 +2694,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2713,13 +2718,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545160</v>
+        <v>544966</v>
       </c>
       <c r="R20" t="n">
-        <v>7198394</v>
+        <v>7198729</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2743,27 +2748,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:31</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På stående död gran med brandljud. På kol</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2790,10 +2790,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128933932</v>
+        <v>128933896</v>
       </c>
       <c r="B21" t="n">
-        <v>57725</v>
+        <v>78796</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2801,21 +2801,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545212</v>
+        <v>545160</v>
       </c>
       <c r="R21" t="n">
-        <v>7198500</v>
+        <v>7198394</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -2855,27 +2855,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre än 5 år på tall</t>
+          <t>På stående död gran med brandljud. På kol</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2902,10 +2902,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128933875</v>
+        <v>128933164</v>
       </c>
       <c r="B22" t="n">
-        <v>79039</v>
+        <v>80144</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2913,37 +2913,41 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>545139</v>
+        <v>544839</v>
       </c>
       <c r="R22" t="n">
-        <v>7198365</v>
+        <v>7198665</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2967,27 +2971,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:41</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Mycket god förekomst</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3002,22 +3001,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128933986</v>
+        <v>128933875</v>
       </c>
       <c r="B23" t="n">
-        <v>91547</v>
+        <v>79039</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3025,21 +3024,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3049,13 +3048,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544828</v>
+        <v>545139</v>
       </c>
       <c r="R23" t="n">
-        <v>7198678</v>
+        <v>7198365</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3079,22 +3078,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Mycket god förekomst</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3121,10 +3125,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128933164</v>
+        <v>128933986</v>
       </c>
       <c r="B24" t="n">
-        <v>80144</v>
+        <v>91547</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3132,41 +3136,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544839</v>
+        <v>544828</v>
       </c>
       <c r="R24" t="n">
-        <v>7198665</v>
+        <v>7198678</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3220,22 +3220,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128933989</v>
+        <v>128933166</v>
       </c>
       <c r="B25" t="n">
-        <v>80145</v>
+        <v>80144</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3243,37 +3243,41 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544830</v>
+        <v>544839</v>
       </c>
       <c r="R25" t="n">
-        <v>7198678</v>
+        <v>7198683</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3302,7 +3306,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3312,12 +3316,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På sälglåga</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3332,19 +3331,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128933165</v>
+        <v>128933989</v>
       </c>
       <c r="B26" t="n">
         <v>80145</v>
@@ -3372,24 +3371,20 @@
           <t>(Scop.) DC.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>544837</v>
+        <v>544830</v>
       </c>
       <c r="R26" t="n">
-        <v>7198665</v>
+        <v>7198678</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3418,7 +3413,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3428,7 +3423,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3443,22 +3443,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128933166</v>
+        <v>128933165</v>
       </c>
       <c r="B27" t="n">
-        <v>80144</v>
+        <v>80145</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,21 +3466,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3494,10 +3494,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>544839</v>
+        <v>544837</v>
       </c>
       <c r="R27" t="n">
-        <v>7198683</v>
+        <v>7198665</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3539,7 +3539,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -5051,10 +5051,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128933171</v>
+        <v>128933124</v>
       </c>
       <c r="B41" t="n">
-        <v>80144</v>
+        <v>79039</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5062,21 +5062,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5090,10 +5090,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>544807</v>
+        <v>545144</v>
       </c>
       <c r="R41" t="n">
-        <v>7198685</v>
+        <v>7198368</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5120,22 +5120,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5162,10 +5162,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128933978</v>
+        <v>128933171</v>
       </c>
       <c r="B42" t="n">
-        <v>91547</v>
+        <v>80144</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5173,37 +5173,41 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>544893</v>
+        <v>544807</v>
       </c>
       <c r="R42" t="n">
-        <v>7198604</v>
+        <v>7198685</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5232,7 +5236,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5242,12 +5246,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:39</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På väl nedbruten låga av gran</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5262,22 +5261,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128933124</v>
+        <v>128933978</v>
       </c>
       <c r="B43" t="n">
-        <v>79039</v>
+        <v>91547</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5285,41 +5284,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>545144</v>
+        <v>544893</v>
       </c>
       <c r="R43" t="n">
-        <v>7198368</v>
+        <v>7198604</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5343,22 +5338,27 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På väl nedbruten låga av gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5373,12 +5373,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5955,10 +5955,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128933870</v>
+        <v>128933984</v>
       </c>
       <c r="B49" t="n">
-        <v>57725</v>
+        <v>80144</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5966,21 +5966,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5990,10 +5990,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>545136</v>
+        <v>544836</v>
       </c>
       <c r="R49" t="n">
-        <v>7198363</v>
+        <v>7198663</v>
       </c>
       <c r="S49" t="n">
         <v>4</v>
@@ -6020,27 +6020,27 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Nya ringbarkningar från tretåig hackspett på gran.</t>
+          <t>Högt upp på gammal sälg</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6067,10 +6067,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128933973</v>
+        <v>128933966</v>
       </c>
       <c r="B50" t="n">
-        <v>57725</v>
+        <v>80145</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6078,21 +6078,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6102,13 +6102,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>544900</v>
+        <v>544905</v>
       </c>
       <c r="R50" t="n">
-        <v>7198597</v>
+        <v>7198603</v>
       </c>
       <c r="S50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack äldre än 5 år på gran</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6179,10 +6179,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128933966</v>
+        <v>128933870</v>
       </c>
       <c r="B51" t="n">
-        <v>80145</v>
+        <v>57725</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6190,21 +6190,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6214,13 +6214,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>544905</v>
+        <v>545136</v>
       </c>
       <c r="R51" t="n">
-        <v>7198603</v>
+        <v>7198363</v>
       </c>
       <c r="S51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6244,27 +6244,27 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>Nya ringbarkningar från tretåig hackspett på gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6291,10 +6291,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128933984</v>
+        <v>128933973</v>
       </c>
       <c r="B52" t="n">
-        <v>80144</v>
+        <v>57725</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6302,21 +6302,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6326,10 +6326,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>544836</v>
+        <v>544900</v>
       </c>
       <c r="R52" t="n">
-        <v>7198663</v>
+        <v>7198597</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6361,7 +6361,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Högt upp på gammal sälg</t>
+          <t>Ringhack äldre än 5 år på gran</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 13030-2025 artfynd.xlsx
+++ b/artfynd/A 13030-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128933955</v>
+        <v>128933901</v>
       </c>
       <c r="B2" t="n">
-        <v>92206</v>
+        <v>83005</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>898</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544957</v>
+        <v>545154</v>
       </c>
       <c r="R2" t="n">
-        <v>7198698</v>
+        <v>7198397</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,27 +740,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På bark av gammal gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128933901</v>
+        <v>128933955</v>
       </c>
       <c r="B3" t="n">
-        <v>83015</v>
+        <v>92213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>898</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,13 +822,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545154</v>
+        <v>544957</v>
       </c>
       <c r="R3" t="n">
-        <v>7198397</v>
+        <v>7198698</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,27 +852,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På bark av gammal gran</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1127,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128933155</v>
+        <v>128933902</v>
       </c>
       <c r="B6" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,41 +1138,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544955</v>
+        <v>545147</v>
       </c>
       <c r="R6" t="n">
-        <v>7198720</v>
+        <v>7198430</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1196,22 +1192,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gamla ringbarkningar på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1226,22 +1227,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128933902</v>
+        <v>128933155</v>
       </c>
       <c r="B7" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1249,37 +1250,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545147</v>
+        <v>544955</v>
       </c>
       <c r="R7" t="n">
-        <v>7198430</v>
+        <v>7198720</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,27 +1308,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:51</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Gamla ringbarkningar på tall</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1338,12 +1338,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1353,7 +1353,7 @@
         <v>128933159</v>
       </c>
       <c r="B8" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>128933125</v>
       </c>
       <c r="B11" t="n">
-        <v>88930</v>
+        <v>88937</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,10 +1794,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128933891</v>
+        <v>128933999</v>
       </c>
       <c r="B12" t="n">
-        <v>78796</v>
+        <v>80144</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,21 +1805,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545149</v>
+        <v>544807</v>
       </c>
       <c r="R12" t="n">
-        <v>7198384</v>
+        <v>7198677</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1859,27 +1859,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På död naken gran med brandljud. På kol.</t>
+          <t>På gammal sälg i sluttning</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1906,10 +1906,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128933999</v>
+        <v>128933891</v>
       </c>
       <c r="B13" t="n">
-        <v>80144</v>
+        <v>78796</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1917,21 +1917,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1941,10 +1941,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544807</v>
+        <v>545149</v>
       </c>
       <c r="R13" t="n">
-        <v>7198677</v>
+        <v>7198384</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -1971,27 +1971,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gammal sälg i sluttning</t>
+          <t>På död naken gran med brandljud. På kol.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2132,7 +2132,7 @@
         <v>128933970</v>
       </c>
       <c r="B15" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2460,10 +2460,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128933932</v>
+        <v>128933896</v>
       </c>
       <c r="B18" t="n">
-        <v>57725</v>
+        <v>78796</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2471,21 +2471,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545212</v>
+        <v>545160</v>
       </c>
       <c r="R18" t="n">
-        <v>7198500</v>
+        <v>7198394</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2525,27 +2525,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre än 5 år på tall</t>
+          <t>På stående död gran med brandljud. På kol</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2572,10 +2572,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128933161</v>
+        <v>128933932</v>
       </c>
       <c r="B19" t="n">
-        <v>91547</v>
+        <v>57725</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2583,41 +2583,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544891</v>
+        <v>545212</v>
       </c>
       <c r="R19" t="n">
-        <v>7198608</v>
+        <v>7198500</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2646,7 +2642,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2656,7 +2652,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre än 5 år på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2671,22 +2672,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128934084</v>
+        <v>128933161</v>
       </c>
       <c r="B20" t="n">
-        <v>91533</v>
+        <v>91554</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2694,37 +2695,41 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544966</v>
+        <v>544891</v>
       </c>
       <c r="R20" t="n">
-        <v>7198729</v>
+        <v>7198608</v>
       </c>
       <c r="S20" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2753,7 +2758,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2763,7 +2768,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2778,22 +2783,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128933896</v>
+        <v>128934084</v>
       </c>
       <c r="B21" t="n">
-        <v>78796</v>
+        <v>91540</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2801,21 +2806,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2825,13 +2830,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545160</v>
+        <v>544966</v>
       </c>
       <c r="R21" t="n">
-        <v>7198394</v>
+        <v>7198729</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2855,27 +2860,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:31</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På stående död gran med brandljud. På kol</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2902,10 +2902,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128933164</v>
+        <v>128933986</v>
       </c>
       <c r="B22" t="n">
-        <v>80144</v>
+        <v>91554</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2913,41 +2913,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544839</v>
+        <v>544828</v>
       </c>
       <c r="R22" t="n">
-        <v>7198665</v>
+        <v>7198678</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2976,7 +2972,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2986,7 +2982,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3001,22 +2997,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128933875</v>
+        <v>128933164</v>
       </c>
       <c r="B23" t="n">
-        <v>79039</v>
+        <v>80144</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3024,37 +3020,41 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>545139</v>
+        <v>544839</v>
       </c>
       <c r="R23" t="n">
-        <v>7198365</v>
+        <v>7198665</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3078,27 +3078,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:41</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Mycket god förekomst</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3113,22 +3108,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128933986</v>
+        <v>128933875</v>
       </c>
       <c r="B24" t="n">
-        <v>91547</v>
+        <v>79039</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3136,21 +3131,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3160,13 +3155,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544828</v>
+        <v>545139</v>
       </c>
       <c r="R24" t="n">
-        <v>7198678</v>
+        <v>7198365</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3190,22 +3185,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Mycket god förekomst</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3566,10 +3566,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128933982</v>
+        <v>128933879</v>
       </c>
       <c r="B28" t="n">
-        <v>80145</v>
+        <v>88937</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3577,21 +3577,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>510</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>544845</v>
+        <v>545153</v>
       </c>
       <c r="R28" t="n">
-        <v>7198663</v>
+        <v>7198363</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3631,22 +3631,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På låga av tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3673,10 +3678,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128933879</v>
+        <v>128933982</v>
       </c>
       <c r="B29" t="n">
-        <v>88930</v>
+        <v>80145</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3684,21 +3689,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>510</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3708,10 +3713,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>545153</v>
+        <v>544845</v>
       </c>
       <c r="R29" t="n">
-        <v>7198363</v>
+        <v>7198663</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -3738,27 +3743,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:50</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På låga av tall</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3901,10 +3901,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128933141</v>
+        <v>128933961</v>
       </c>
       <c r="B31" t="n">
-        <v>79039</v>
+        <v>80145</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3912,41 +3912,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>545088</v>
+        <v>544872</v>
       </c>
       <c r="R31" t="n">
-        <v>7198569</v>
+        <v>7198610</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3970,22 +3966,27 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4000,22 +4001,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128933961</v>
+        <v>128933980</v>
       </c>
       <c r="B32" t="n">
-        <v>80145</v>
+        <v>91554</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4023,21 +4024,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4047,13 +4048,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>544872</v>
+        <v>544853</v>
       </c>
       <c r="R32" t="n">
-        <v>7198610</v>
+        <v>7198662</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4082,7 +4083,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4092,12 +4093,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>Väl nedbruten låga av sälg</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4124,10 +4125,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128933980</v>
+        <v>128933141</v>
       </c>
       <c r="B33" t="n">
-        <v>91547</v>
+        <v>79039</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4135,37 +4136,41 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>544853</v>
+        <v>545088</v>
       </c>
       <c r="R33" t="n">
-        <v>7198662</v>
+        <v>7198569</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4189,27 +4194,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Väl nedbruten låga av sälg</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4224,12 +4224,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4707,10 +4707,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128933147</v>
+        <v>128933908</v>
       </c>
       <c r="B38" t="n">
-        <v>57725</v>
+        <v>57885</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4718,46 +4718,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>545204</v>
+        <v>545139</v>
       </c>
       <c r="R38" t="n">
-        <v>7198506</v>
+        <v>7198504</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4781,22 +4772,27 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Två talltitor</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4811,19 +4807,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128933212</v>
+        <v>128933147</v>
       </c>
       <c r="B39" t="n">
         <v>57725</v>
@@ -4867,10 +4863,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>544911</v>
+        <v>545204</v>
       </c>
       <c r="R39" t="n">
-        <v>7198620</v>
+        <v>7198506</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4902,7 +4898,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4912,7 +4908,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4939,10 +4935,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128933908</v>
+        <v>128933212</v>
       </c>
       <c r="B40" t="n">
-        <v>57885</v>
+        <v>57725</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4950,37 +4946,46 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>545139</v>
+        <v>544911</v>
       </c>
       <c r="R40" t="n">
-        <v>7198504</v>
+        <v>7198620</v>
       </c>
       <c r="S40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5004,27 +5009,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Två talltitor</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5039,22 +5039,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128933124</v>
+        <v>128933978</v>
       </c>
       <c r="B41" t="n">
-        <v>79039</v>
+        <v>91554</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5062,41 +5062,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>545144</v>
+        <v>544893</v>
       </c>
       <c r="R41" t="n">
-        <v>7198368</v>
+        <v>7198604</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5120,22 +5116,27 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På väl nedbruten låga av gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5150,22 +5151,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128933171</v>
+        <v>128933124</v>
       </c>
       <c r="B42" t="n">
-        <v>80144</v>
+        <v>79039</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5173,21 +5174,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5201,10 +5202,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>544807</v>
+        <v>545144</v>
       </c>
       <c r="R42" t="n">
-        <v>7198685</v>
+        <v>7198368</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5231,22 +5232,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5273,10 +5274,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128933978</v>
+        <v>128933171</v>
       </c>
       <c r="B43" t="n">
-        <v>91547</v>
+        <v>80144</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5284,37 +5285,41 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>544893</v>
+        <v>544807</v>
       </c>
       <c r="R43" t="n">
-        <v>7198604</v>
+        <v>7198685</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5343,7 +5348,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5353,12 +5358,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:39</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På väl nedbruten låga av gran</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5373,12 +5373,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5496,10 +5496,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128933129</v>
+        <v>128933157</v>
       </c>
       <c r="B45" t="n">
-        <v>78796</v>
+        <v>80145</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5507,21 +5507,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5535,10 +5535,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>545158</v>
+        <v>544908</v>
       </c>
       <c r="R45" t="n">
-        <v>7198403</v>
+        <v>7198602</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5565,27 +5565,27 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Liten kolad stubbe</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5612,10 +5612,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128933157</v>
+        <v>128933154</v>
       </c>
       <c r="B46" t="n">
-        <v>80145</v>
+        <v>91540</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5623,21 +5623,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5651,10 +5651,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>544908</v>
+        <v>544968</v>
       </c>
       <c r="R46" t="n">
-        <v>7198602</v>
+        <v>7198730</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5696,12 +5696,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Gran, stor utbredning.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5728,10 +5728,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128933154</v>
+        <v>128933129</v>
       </c>
       <c r="B47" t="n">
-        <v>91533</v>
+        <v>78796</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5739,21 +5739,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>544968</v>
+        <v>545158</v>
       </c>
       <c r="R47" t="n">
-        <v>7198730</v>
+        <v>7198403</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5797,27 +5797,27 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Gran, stor utbredning.</t>
+          <t>Liten kolad stubbe</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5955,10 +5955,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128933984</v>
+        <v>128933966</v>
       </c>
       <c r="B49" t="n">
-        <v>80144</v>
+        <v>80145</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5966,21 +5966,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5990,13 +5990,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>544836</v>
+        <v>544905</v>
       </c>
       <c r="R49" t="n">
-        <v>7198663</v>
+        <v>7198603</v>
       </c>
       <c r="S49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Högt upp på gammal sälg</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6067,10 +6067,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128933966</v>
+        <v>128933984</v>
       </c>
       <c r="B50" t="n">
-        <v>80145</v>
+        <v>80144</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6078,21 +6078,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6102,13 +6102,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>544905</v>
+        <v>544836</v>
       </c>
       <c r="R50" t="n">
-        <v>7198603</v>
+        <v>7198663</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>Högt upp på gammal sälg</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6179,10 +6179,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128933870</v>
+        <v>128933136</v>
       </c>
       <c r="B51" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6190,37 +6190,41 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>545136</v>
+        <v>545109</v>
       </c>
       <c r="R51" t="n">
-        <v>7198363</v>
+        <v>7198551</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6249,7 +6253,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6259,12 +6263,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Nya ringbarkningar från tretåig hackspett på gran.</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6279,19 +6278,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128933973</v>
+        <v>128933870</v>
       </c>
       <c r="B52" t="n">
         <v>57725</v>
@@ -6326,10 +6325,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>544900</v>
+        <v>545136</v>
       </c>
       <c r="R52" t="n">
-        <v>7198597</v>
+        <v>7198363</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6356,27 +6355,27 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack äldre än 5 år på gran</t>
+          <t>Nya ringbarkningar från tretåig hackspett på gran.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6403,10 +6402,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128933136</v>
+        <v>128933973</v>
       </c>
       <c r="B53" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6414,41 +6413,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>545109</v>
+        <v>544900</v>
       </c>
       <c r="R53" t="n">
-        <v>7198551</v>
+        <v>7198597</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6472,22 +6467,27 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack äldre än 5 år på gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6502,22 +6502,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128933167</v>
+        <v>128933947</v>
       </c>
       <c r="B54" t="n">
-        <v>80048</v>
+        <v>91504</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6525,41 +6525,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>544823</v>
+        <v>544971</v>
       </c>
       <c r="R54" t="n">
-        <v>7198695</v>
+        <v>7198722</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6588,7 +6584,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6598,12 +6594,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:14</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Asp</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6618,22 +6609,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128933947</v>
+        <v>128933167</v>
       </c>
       <c r="B55" t="n">
-        <v>91497</v>
+        <v>80048</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6641,37 +6632,41 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>6456</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>544971</v>
+        <v>544823</v>
       </c>
       <c r="R55" t="n">
-        <v>7198722</v>
+        <v>7198695</v>
       </c>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6700,7 +6695,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6710,7 +6705,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Asp</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6725,12 +6725,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>

--- a/artfynd/A 13030-2025 artfynd.xlsx
+++ b/artfynd/A 13030-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128933901</v>
       </c>
       <c r="B2" t="n">
-        <v>83005</v>
+        <v>83007</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>128933955</v>
       </c>
       <c r="B3" t="n">
-        <v>92213</v>
+        <v>92215</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>128933958</v>
       </c>
       <c r="B4" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>128933126</v>
       </c>
       <c r="B5" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128933902</v>
+        <v>128933155</v>
       </c>
       <c r="B6" t="n">
-        <v>57725</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,37 +1138,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545147</v>
+        <v>544955</v>
       </c>
       <c r="R6" t="n">
-        <v>7198430</v>
+        <v>7198720</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1192,27 +1196,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:51</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gamla ringbarkningar på tall</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1227,22 +1226,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128933155</v>
+        <v>128933902</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1250,41 +1249,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544955</v>
+        <v>545147</v>
       </c>
       <c r="R7" t="n">
-        <v>7198720</v>
+        <v>7198430</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1308,22 +1303,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gamla ringbarkningar på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1338,22 +1338,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128933159</v>
+        <v>128933127</v>
       </c>
       <c r="B8" t="n">
-        <v>91825</v>
+        <v>78798</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1361,21 +1361,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544907</v>
+        <v>545155</v>
       </c>
       <c r="R8" t="n">
-        <v>7198585</v>
+        <v>7198397</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1419,22 +1419,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,10 +1461,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128933127</v>
+        <v>128933159</v>
       </c>
       <c r="B9" t="n">
-        <v>78796</v>
+        <v>91827</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545155</v>
+        <v>544907</v>
       </c>
       <c r="R9" t="n">
-        <v>7198397</v>
+        <v>7198585</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1530,22 +1530,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,7 +1575,7 @@
         <v>128933131</v>
       </c>
       <c r="B10" t="n">
-        <v>80172</v>
+        <v>80174</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128933125</v>
+        <v>128933999</v>
       </c>
       <c r="B11" t="n">
-        <v>88937</v>
+        <v>80146</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,41 +1694,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545148</v>
+        <v>544807</v>
       </c>
       <c r="R11" t="n">
-        <v>7198360</v>
+        <v>7198677</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1752,22 +1748,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På gammal sälg i sluttning</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1782,22 +1783,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128933999</v>
+        <v>128933891</v>
       </c>
       <c r="B12" t="n">
-        <v>80144</v>
+        <v>78798</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,21 +1806,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1829,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544807</v>
+        <v>545149</v>
       </c>
       <c r="R12" t="n">
-        <v>7198677</v>
+        <v>7198384</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1859,27 +1860,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gammal sälg i sluttning</t>
+          <t>På död naken gran med brandljud. På kol.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1906,48 +1907,52 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128933891</v>
+        <v>128933172</v>
       </c>
       <c r="B13" t="n">
-        <v>78796</v>
+        <v>80182</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6464</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545149</v>
+        <v>544801</v>
       </c>
       <c r="R13" t="n">
-        <v>7198384</v>
+        <v>7198690</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1971,27 +1976,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På död naken gran med brandljud. På kol.</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2006,44 +2006,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128933172</v>
+        <v>128933125</v>
       </c>
       <c r="B14" t="n">
-        <v>80180</v>
+        <v>88939</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>510</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2057,10 +2057,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544801</v>
+        <v>545148</v>
       </c>
       <c r="R14" t="n">
-        <v>7198690</v>
+        <v>7198360</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2087,22 +2087,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2129,10 +2129,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128933970</v>
+        <v>128933904</v>
       </c>
       <c r="B15" t="n">
-        <v>91825</v>
+        <v>78444</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2140,21 +2140,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>6437</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2164,13 +2164,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544900</v>
+        <v>545138</v>
       </c>
       <c r="R15" t="n">
-        <v>7198605</v>
+        <v>7198414</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2194,27 +2194,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På gammal granlåga</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2241,10 +2236,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128933904</v>
+        <v>128933970</v>
       </c>
       <c r="B16" t="n">
-        <v>78442</v>
+        <v>91827</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2252,21 +2247,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6437</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2276,13 +2271,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>545138</v>
+        <v>544900</v>
       </c>
       <c r="R16" t="n">
-        <v>7198414</v>
+        <v>7198605</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2306,22 +2301,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2351,7 +2351,7 @@
         <v>128933968</v>
       </c>
       <c r="B17" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         <v>128933896</v>
       </c>
       <c r="B18" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
         <v>128933932</v>
       </c>
       <c r="B19" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>128933161</v>
       </c>
       <c r="B20" t="n">
-        <v>91554</v>
+        <v>91556</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>128934084</v>
       </c>
       <c r="B21" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2902,10 +2902,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128933986</v>
+        <v>128933875</v>
       </c>
       <c r="B22" t="n">
-        <v>91554</v>
+        <v>79041</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2913,21 +2913,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2937,13 +2937,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544828</v>
+        <v>545139</v>
       </c>
       <c r="R22" t="n">
-        <v>7198678</v>
+        <v>7198365</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2967,22 +2967,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Mycket god förekomst</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3009,10 +3014,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128933164</v>
+        <v>128933986</v>
       </c>
       <c r="B23" t="n">
-        <v>80144</v>
+        <v>91556</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3020,41 +3025,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544839</v>
+        <v>544828</v>
       </c>
       <c r="R23" t="n">
-        <v>7198665</v>
+        <v>7198678</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3083,7 +3084,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3093,7 +3094,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3108,22 +3109,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128933875</v>
+        <v>128933164</v>
       </c>
       <c r="B24" t="n">
-        <v>79039</v>
+        <v>80146</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3131,37 +3132,41 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>545139</v>
+        <v>544839</v>
       </c>
       <c r="R24" t="n">
-        <v>7198365</v>
+        <v>7198665</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3185,27 +3190,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:41</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Mycket god förekomst</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3220,22 +3220,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128933166</v>
+        <v>128933989</v>
       </c>
       <c r="B25" t="n">
-        <v>80144</v>
+        <v>80147</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3243,41 +3243,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544839</v>
+        <v>544830</v>
       </c>
       <c r="R25" t="n">
-        <v>7198683</v>
+        <v>7198678</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3306,7 +3302,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3316,7 +3312,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3331,22 +3332,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128933989</v>
+        <v>128933165</v>
       </c>
       <c r="B26" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3371,20 +3372,24 @@
           <t>(Scop.) DC.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>544830</v>
+        <v>544837</v>
       </c>
       <c r="R26" t="n">
-        <v>7198678</v>
+        <v>7198665</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3413,7 +3418,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3423,12 +3428,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På sälglåga</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3443,22 +3443,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128933165</v>
+        <v>128933166</v>
       </c>
       <c r="B27" t="n">
-        <v>80145</v>
+        <v>80146</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,21 +3466,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3494,10 +3494,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>544837</v>
+        <v>544839</v>
       </c>
       <c r="R27" t="n">
-        <v>7198665</v>
+        <v>7198683</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3539,7 +3539,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3566,10 +3566,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128933879</v>
+        <v>128933982</v>
       </c>
       <c r="B28" t="n">
-        <v>88937</v>
+        <v>80147</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3577,21 +3577,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>510</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>545153</v>
+        <v>544845</v>
       </c>
       <c r="R28" t="n">
-        <v>7198363</v>
+        <v>7198663</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3631,27 +3631,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:50</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På låga av tall</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3678,10 +3673,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128933982</v>
+        <v>128933879</v>
       </c>
       <c r="B29" t="n">
-        <v>80145</v>
+        <v>88939</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3689,21 +3684,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>510</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3713,10 +3708,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544845</v>
+        <v>545153</v>
       </c>
       <c r="R29" t="n">
-        <v>7198663</v>
+        <v>7198363</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -3743,22 +3738,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På låga av tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3788,7 +3788,7 @@
         <v>128933158</v>
       </c>
       <c r="B30" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3901,10 +3901,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128933961</v>
+        <v>128933141</v>
       </c>
       <c r="B31" t="n">
-        <v>80145</v>
+        <v>79041</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3912,37 +3912,41 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>544872</v>
+        <v>545088</v>
       </c>
       <c r="R31" t="n">
-        <v>7198610</v>
+        <v>7198569</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3966,27 +3970,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4001,22 +4000,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128933980</v>
+        <v>128933961</v>
       </c>
       <c r="B32" t="n">
-        <v>91554</v>
+        <v>80147</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4024,21 +4023,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1204</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4048,13 +4047,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>544853</v>
+        <v>544872</v>
       </c>
       <c r="R32" t="n">
-        <v>7198662</v>
+        <v>7198610</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4083,7 +4082,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4093,12 +4092,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Väl nedbruten låga av sälg</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4125,10 +4124,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128933141</v>
+        <v>128933980</v>
       </c>
       <c r="B33" t="n">
-        <v>79039</v>
+        <v>91556</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4136,41 +4135,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>545088</v>
+        <v>544853</v>
       </c>
       <c r="R33" t="n">
-        <v>7198569</v>
+        <v>7198662</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4194,22 +4189,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Väl nedbruten låga av sälg</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4224,12 +4224,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4239,7 +4239,7 @@
         <v>128933130</v>
       </c>
       <c r="B34" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>128933213</v>
       </c>
       <c r="B35" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>128933156</v>
       </c>
       <c r="B36" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         <v>128934001</v>
       </c>
       <c r="B37" t="n">
-        <v>80180</v>
+        <v>80182</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         <v>128933908</v>
       </c>
       <c r="B38" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>128933147</v>
       </c>
       <c r="B39" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         <v>128933212</v>
       </c>
       <c r="B40" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5051,10 +5051,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128933978</v>
+        <v>128933171</v>
       </c>
       <c r="B41" t="n">
-        <v>91554</v>
+        <v>80146</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5062,37 +5062,41 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>544893</v>
+        <v>544807</v>
       </c>
       <c r="R41" t="n">
-        <v>7198604</v>
+        <v>7198685</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5121,7 +5125,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5131,12 +5135,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:39</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På väl nedbruten låga av gran</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5151,12 +5150,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5166,7 +5165,7 @@
         <v>128933124</v>
       </c>
       <c r="B42" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5274,10 +5273,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128933171</v>
+        <v>128933978</v>
       </c>
       <c r="B43" t="n">
-        <v>80144</v>
+        <v>91556</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5285,41 +5284,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>544807</v>
+        <v>544893</v>
       </c>
       <c r="R43" t="n">
-        <v>7198685</v>
+        <v>7198604</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5348,7 +5343,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5358,7 +5353,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På väl nedbruten låga av gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5373,12 +5373,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5388,7 +5388,7 @@
         <v>128933163</v>
       </c>
       <c r="B44" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5496,10 +5496,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128933157</v>
+        <v>128933154</v>
       </c>
       <c r="B45" t="n">
-        <v>80145</v>
+        <v>91542</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5507,21 +5507,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5535,10 +5535,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>544908</v>
+        <v>544968</v>
       </c>
       <c r="R45" t="n">
-        <v>7198602</v>
+        <v>7198730</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Gran, stor utbredning.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5612,10 +5612,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128933154</v>
+        <v>128933157</v>
       </c>
       <c r="B46" t="n">
-        <v>91540</v>
+        <v>80147</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5623,21 +5623,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5651,10 +5651,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>544968</v>
+        <v>544908</v>
       </c>
       <c r="R46" t="n">
-        <v>7198730</v>
+        <v>7198602</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5696,12 +5696,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Gran, stor utbredning.</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5731,7 +5731,7 @@
         <v>128933129</v>
       </c>
       <c r="B47" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>128933139</v>
       </c>
       <c r="B48" t="n">
-        <v>80172</v>
+        <v>80174</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5955,10 +5955,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128933966</v>
+        <v>128933136</v>
       </c>
       <c r="B49" t="n">
-        <v>80145</v>
+        <v>79041</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5966,37 +5966,41 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>544905</v>
+        <v>545109</v>
       </c>
       <c r="R49" t="n">
-        <v>7198603</v>
+        <v>7198551</v>
       </c>
       <c r="S49" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6020,27 +6024,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6055,22 +6054,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128933984</v>
+        <v>128933966</v>
       </c>
       <c r="B50" t="n">
-        <v>80144</v>
+        <v>80147</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6078,21 +6077,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6102,13 +6101,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>544836</v>
+        <v>544905</v>
       </c>
       <c r="R50" t="n">
-        <v>7198663</v>
+        <v>7198603</v>
       </c>
       <c r="S50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6137,7 +6136,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6147,12 +6146,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Högt upp på gammal sälg</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6179,10 +6178,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128933136</v>
+        <v>128933984</v>
       </c>
       <c r="B51" t="n">
-        <v>79039</v>
+        <v>80146</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6190,41 +6189,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>545109</v>
+        <v>544836</v>
       </c>
       <c r="R51" t="n">
-        <v>7198551</v>
+        <v>7198663</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6248,22 +6243,27 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Högt upp på gammal sälg</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6278,12 +6278,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6293,7 +6293,7 @@
         <v>128933870</v>
       </c>
       <c r="B52" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
         <v>128933973</v>
       </c>
       <c r="B53" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>128933947</v>
       </c>
       <c r="B54" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>128933167</v>
       </c>
       <c r="B55" t="n">
-        <v>80048</v>
+        <v>80050</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6737,32 +6737,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128934086</v>
+        <v>128933991</v>
       </c>
       <c r="B56" t="n">
-        <v>57725</v>
+        <v>80050</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6772,10 +6772,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>544908</v>
+        <v>544826</v>
       </c>
       <c r="R56" t="n">
-        <v>7198615</v>
+        <v>7198694</v>
       </c>
       <c r="S56" t="n">
         <v>4</v>
@@ -6807,7 +6807,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6849,32 +6849,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128933991</v>
+        <v>128934086</v>
       </c>
       <c r="B57" t="n">
-        <v>80048</v>
+        <v>57727</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6884,10 +6884,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>544826</v>
+        <v>544908</v>
       </c>
       <c r="R57" t="n">
-        <v>7198694</v>
+        <v>7198615</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -6919,7 +6919,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 13030-2025 artfynd.xlsx
+++ b/artfynd/A 13030-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128933901</v>
+        <v>128933955</v>
       </c>
       <c r="B2" t="n">
-        <v>83007</v>
+        <v>92215</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>898</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545154</v>
+        <v>544957</v>
       </c>
       <c r="R2" t="n">
-        <v>7198397</v>
+        <v>7198698</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,27 +740,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På bark av gammal gran</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128933955</v>
+        <v>128933901</v>
       </c>
       <c r="B3" t="n">
-        <v>92215</v>
+        <v>83007</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>898</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,13 +822,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544957</v>
+        <v>545154</v>
       </c>
       <c r="R3" t="n">
-        <v>7198698</v>
+        <v>7198397</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,27 +852,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På bark av gammal gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128933958</v>
+        <v>128933126</v>
       </c>
       <c r="B4" t="n">
-        <v>80146</v>
+        <v>78798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,37 +910,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544871</v>
+        <v>545150</v>
       </c>
       <c r="R4" t="n">
-        <v>7198612</v>
+        <v>7198391</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,27 +968,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>Kolad granved</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,22 +1003,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128933126</v>
+        <v>128933958</v>
       </c>
       <c r="B5" t="n">
-        <v>78798</v>
+        <v>80146</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,41 +1026,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545150</v>
+        <v>544871</v>
       </c>
       <c r="R5" t="n">
-        <v>7198391</v>
+        <v>7198612</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,27 +1080,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Kolad granved</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,22 +1115,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128933155</v>
+        <v>128933902</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,41 +1138,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544955</v>
+        <v>545147</v>
       </c>
       <c r="R6" t="n">
-        <v>7198720</v>
+        <v>7198430</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1196,22 +1192,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gamla ringbarkningar på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1226,22 +1227,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128933902</v>
+        <v>128933155</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1249,37 +1250,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545147</v>
+        <v>544955</v>
       </c>
       <c r="R7" t="n">
-        <v>7198430</v>
+        <v>7198720</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,27 +1308,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:51</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Gamla ringbarkningar på tall</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1338,22 +1338,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128933127</v>
+        <v>128933159</v>
       </c>
       <c r="B8" t="n">
-        <v>78798</v>
+        <v>91827</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1361,21 +1361,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545155</v>
+        <v>544907</v>
       </c>
       <c r="R8" t="n">
-        <v>7198397</v>
+        <v>7198585</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1419,22 +1419,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,10 +1461,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128933159</v>
+        <v>128933127</v>
       </c>
       <c r="B9" t="n">
-        <v>91827</v>
+        <v>78798</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544907</v>
+        <v>545155</v>
       </c>
       <c r="R9" t="n">
-        <v>7198585</v>
+        <v>7198397</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1530,22 +1530,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1683,48 +1683,52 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128933999</v>
+        <v>128933172</v>
       </c>
       <c r="B11" t="n">
-        <v>80146</v>
+        <v>80182</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544807</v>
+        <v>544801</v>
       </c>
       <c r="R11" t="n">
-        <v>7198677</v>
+        <v>7198690</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1753,7 +1757,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,12 +1767,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På gammal sälg i sluttning</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1783,12 +1782,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1907,32 +1906,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128933172</v>
+        <v>128933125</v>
       </c>
       <c r="B13" t="n">
-        <v>80182</v>
+        <v>88939</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6464</v>
+        <v>510</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1946,10 +1945,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544801</v>
+        <v>545148</v>
       </c>
       <c r="R13" t="n">
-        <v>7198690</v>
+        <v>7198360</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1976,22 +1975,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2018,10 +2017,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128933125</v>
+        <v>128933999</v>
       </c>
       <c r="B14" t="n">
-        <v>88939</v>
+        <v>80146</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2029,41 +2028,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545148</v>
+        <v>544807</v>
       </c>
       <c r="R14" t="n">
-        <v>7198360</v>
+        <v>7198677</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2087,22 +2082,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På gammal sälg i sluttning</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2117,22 +2117,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128933904</v>
+        <v>128933970</v>
       </c>
       <c r="B15" t="n">
-        <v>78444</v>
+        <v>91827</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2140,21 +2140,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6437</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2164,13 +2164,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545138</v>
+        <v>544900</v>
       </c>
       <c r="R15" t="n">
-        <v>7198414</v>
+        <v>7198605</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2194,22 +2194,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2236,10 +2241,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128933970</v>
+        <v>128933904</v>
       </c>
       <c r="B16" t="n">
-        <v>91827</v>
+        <v>78444</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2247,21 +2252,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>6437</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2271,13 +2276,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544900</v>
+        <v>545138</v>
       </c>
       <c r="R16" t="n">
-        <v>7198605</v>
+        <v>7198414</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2301,27 +2306,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På gammal granlåga</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2902,10 +2902,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128933875</v>
+        <v>128933986</v>
       </c>
       <c r="B22" t="n">
-        <v>79041</v>
+        <v>91556</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2913,21 +2913,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2937,13 +2937,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>545139</v>
+        <v>544828</v>
       </c>
       <c r="R22" t="n">
-        <v>7198365</v>
+        <v>7198678</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2967,27 +2967,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:41</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Mycket god förekomst</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3014,10 +3009,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128933986</v>
+        <v>128933164</v>
       </c>
       <c r="B23" t="n">
-        <v>91556</v>
+        <v>80146</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3025,37 +3020,41 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544828</v>
+        <v>544839</v>
       </c>
       <c r="R23" t="n">
-        <v>7198678</v>
+        <v>7198665</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3084,7 +3083,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3094,7 +3093,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3109,22 +3108,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128933164</v>
+        <v>128933875</v>
       </c>
       <c r="B24" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3132,41 +3131,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544839</v>
+        <v>545139</v>
       </c>
       <c r="R24" t="n">
-        <v>7198665</v>
+        <v>7198365</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3190,22 +3185,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Mycket god förekomst</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3220,12 +3220,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3566,10 +3566,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128933982</v>
+        <v>128933879</v>
       </c>
       <c r="B28" t="n">
-        <v>80147</v>
+        <v>88939</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3577,21 +3577,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>510</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>544845</v>
+        <v>545153</v>
       </c>
       <c r="R28" t="n">
-        <v>7198663</v>
+        <v>7198363</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3631,22 +3631,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På låga av tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3673,10 +3678,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128933879</v>
+        <v>128933158</v>
       </c>
       <c r="B29" t="n">
-        <v>88939</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3684,37 +3689,46 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>545153</v>
+        <v>544903</v>
       </c>
       <c r="R29" t="n">
-        <v>7198363</v>
+        <v>7198597</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3738,27 +3752,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:50</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På låga av tall</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3773,22 +3782,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128933158</v>
+        <v>128933982</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>80147</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3796,46 +3805,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>544903</v>
+        <v>544845</v>
       </c>
       <c r="R30" t="n">
-        <v>7198597</v>
+        <v>7198663</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3889,12 +3889,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4595,48 +4595,57 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128934001</v>
+        <v>128933147</v>
       </c>
       <c r="B37" t="n">
-        <v>80182</v>
+        <v>57727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>544806</v>
+        <v>545204</v>
       </c>
       <c r="R37" t="n">
-        <v>7198678</v>
+        <v>7198506</v>
       </c>
       <c r="S37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4665,7 +4674,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4675,12 +4684,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:21</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4695,22 +4699,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128933908</v>
+        <v>128933212</v>
       </c>
       <c r="B38" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4718,37 +4722,46 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>545139</v>
+        <v>544911</v>
       </c>
       <c r="R38" t="n">
-        <v>7198504</v>
+        <v>7198620</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4772,27 +4785,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Två talltitor</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4807,22 +4815,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128933147</v>
+        <v>128933908</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4830,46 +4838,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>545204</v>
+        <v>545139</v>
       </c>
       <c r="R39" t="n">
-        <v>7198506</v>
+        <v>7198504</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4893,22 +4892,27 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Två talltitor</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4923,69 +4927,60 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128933212</v>
+        <v>128934001</v>
       </c>
       <c r="B40" t="n">
-        <v>57727</v>
+        <v>80182</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>544911</v>
+        <v>544806</v>
       </c>
       <c r="R40" t="n">
-        <v>7198620</v>
+        <v>7198678</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5014,7 +5009,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5024,7 +5019,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5039,12 +5039,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5385,10 +5385,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128933163</v>
+        <v>128933157</v>
       </c>
       <c r="B44" t="n">
-        <v>79041</v>
+        <v>80147</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5396,21 +5396,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5424,10 +5424,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>544832</v>
+        <v>544908</v>
       </c>
       <c r="R44" t="n">
-        <v>7198667</v>
+        <v>7198602</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5469,7 +5469,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5612,10 +5617,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128933157</v>
+        <v>128933163</v>
       </c>
       <c r="B46" t="n">
-        <v>80147</v>
+        <v>79041</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5623,21 +5628,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5651,10 +5656,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>544908</v>
+        <v>544832</v>
       </c>
       <c r="R46" t="n">
-        <v>7198602</v>
+        <v>7198667</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5686,7 +5691,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5696,12 +5701,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Sälg</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5955,10 +5955,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128933136</v>
+        <v>128933984</v>
       </c>
       <c r="B49" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5966,41 +5966,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>545109</v>
+        <v>544836</v>
       </c>
       <c r="R49" t="n">
-        <v>7198551</v>
+        <v>7198663</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6024,22 +6020,27 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Högt upp på gammal sälg</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6054,22 +6055,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128933966</v>
+        <v>128933136</v>
       </c>
       <c r="B50" t="n">
-        <v>80147</v>
+        <v>79041</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6077,37 +6078,41 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>544905</v>
+        <v>545109</v>
       </c>
       <c r="R50" t="n">
-        <v>7198603</v>
+        <v>7198551</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6131,27 +6136,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6166,22 +6166,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128933984</v>
+        <v>128933870</v>
       </c>
       <c r="B51" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6189,21 +6189,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6213,10 +6213,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>544836</v>
+        <v>545136</v>
       </c>
       <c r="R51" t="n">
-        <v>7198663</v>
+        <v>7198363</v>
       </c>
       <c r="S51" t="n">
         <v>4</v>
@@ -6243,27 +6243,27 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Högt upp på gammal sälg</t>
+          <t>Nya ringbarkningar från tretåig hackspett på gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6290,7 +6290,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128933870</v>
+        <v>128933973</v>
       </c>
       <c r="B52" t="n">
         <v>57727</v>
@@ -6325,10 +6325,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>545136</v>
+        <v>544900</v>
       </c>
       <c r="R52" t="n">
-        <v>7198363</v>
+        <v>7198597</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6355,27 +6355,27 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Nya ringbarkningar från tretåig hackspett på gran.</t>
+          <t>Ringhack äldre än 5 år på gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6402,10 +6402,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128933973</v>
+        <v>128933966</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>80147</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6413,21 +6413,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6437,13 +6437,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>544900</v>
+        <v>544905</v>
       </c>
       <c r="R53" t="n">
-        <v>7198597</v>
+        <v>7198603</v>
       </c>
       <c r="S53" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6482,12 +6482,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack äldre än 5 år på gran</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 13030-2025 artfynd.xlsx
+++ b/artfynd/A 13030-2025 artfynd.xlsx
@@ -1127,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128933902</v>
+        <v>128933155</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,37 +1138,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545147</v>
+        <v>544955</v>
       </c>
       <c r="R6" t="n">
-        <v>7198430</v>
+        <v>7198720</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1192,27 +1196,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:51</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gamla ringbarkningar på tall</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1227,22 +1226,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128933155</v>
+        <v>128933902</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1250,41 +1249,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544955</v>
+        <v>545147</v>
       </c>
       <c r="R7" t="n">
-        <v>7198720</v>
+        <v>7198430</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1308,22 +1303,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gamla ringbarkningar på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1338,12 +1338,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1794,10 +1794,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128933891</v>
+        <v>128933125</v>
       </c>
       <c r="B12" t="n">
-        <v>78798</v>
+        <v>88939</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,37 +1805,41 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>510</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545149</v>
+        <v>545148</v>
       </c>
       <c r="R12" t="n">
-        <v>7198384</v>
+        <v>7198360</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1864,7 +1868,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1874,12 +1878,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På död naken gran med brandljud. På kol.</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1894,22 +1893,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128933125</v>
+        <v>128933999</v>
       </c>
       <c r="B13" t="n">
-        <v>88939</v>
+        <v>80146</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1917,41 +1916,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545148</v>
+        <v>544807</v>
       </c>
       <c r="R13" t="n">
-        <v>7198360</v>
+        <v>7198677</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1975,22 +1970,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På gammal sälg i sluttning</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2005,22 +2005,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128933999</v>
+        <v>128933891</v>
       </c>
       <c r="B14" t="n">
-        <v>80146</v>
+        <v>78798</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2028,21 +2028,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2052,10 +2052,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544807</v>
+        <v>545149</v>
       </c>
       <c r="R14" t="n">
-        <v>7198677</v>
+        <v>7198384</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2082,27 +2082,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gammal sälg i sluttning</t>
+          <t>På död naken gran med brandljud. På kol.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -3678,10 +3678,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128933158</v>
+        <v>128933982</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>80147</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3689,46 +3689,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544903</v>
+        <v>544845</v>
       </c>
       <c r="R29" t="n">
-        <v>7198597</v>
+        <v>7198663</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3757,7 +3748,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3767,7 +3758,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3782,22 +3773,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128933982</v>
+        <v>128933158</v>
       </c>
       <c r="B30" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3805,37 +3796,46 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>544845</v>
+        <v>544903</v>
       </c>
       <c r="R30" t="n">
-        <v>7198663</v>
+        <v>7198597</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3889,12 +3889,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4012,10 +4012,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128933961</v>
+        <v>128933130</v>
       </c>
       <c r="B32" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4023,37 +4023,46 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>544872</v>
+        <v>545144</v>
       </c>
       <c r="R32" t="n">
-        <v>7198610</v>
+        <v>7198419</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4077,27 +4086,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4112,22 +4116,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128933980</v>
+        <v>128933213</v>
       </c>
       <c r="B33" t="n">
-        <v>91556</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4135,37 +4139,49 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>544853</v>
+        <v>544897</v>
       </c>
       <c r="R33" t="n">
-        <v>7198662</v>
+        <v>7198529</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4194,7 +4210,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4204,12 +4220,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Väl nedbruten låga av sälg</t>
+          <t>Innanför gränsen, bild finns.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4224,19 +4240,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128933130</v>
+        <v>128933156</v>
       </c>
       <c r="B34" t="n">
         <v>57727</v>
@@ -4269,21 +4285,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>545144</v>
+        <v>544879</v>
       </c>
       <c r="R34" t="n">
-        <v>7198419</v>
+        <v>7198601</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4310,22 +4329,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4345,17 +4364,17 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128933213</v>
+        <v>128933961</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>80147</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4363,49 +4382,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>544897</v>
+        <v>544872</v>
       </c>
       <c r="R35" t="n">
-        <v>7198529</v>
+        <v>7198610</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4434,7 +4441,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4444,12 +4451,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Innanför gränsen, bild finns.</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4464,22 +4471,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128933156</v>
+        <v>128933980</v>
       </c>
       <c r="B36" t="n">
-        <v>57727</v>
+        <v>91556</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4487,49 +4494,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>544879</v>
+        <v>544853</v>
       </c>
       <c r="R36" t="n">
-        <v>7198601</v>
+        <v>7198662</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4558,7 +4553,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4568,7 +4563,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Väl nedbruten låga av sälg</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4583,12 +4583,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>

--- a/artfynd/A 13030-2025 artfynd.xlsx
+++ b/artfynd/A 13030-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128933955</v>
       </c>
       <c r="B2" t="n">
-        <v>92215</v>
+        <v>92230</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128933126</v>
+        <v>128933958</v>
       </c>
       <c r="B4" t="n">
-        <v>78798</v>
+        <v>80146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,41 +910,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545150</v>
+        <v>544871</v>
       </c>
       <c r="R4" t="n">
-        <v>7198391</v>
+        <v>7198612</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -968,27 +964,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Kolad granved</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,22 +999,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128933958</v>
+        <v>128933126</v>
       </c>
       <c r="B5" t="n">
-        <v>80146</v>
+        <v>78798</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,37 +1022,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544871</v>
+        <v>545150</v>
       </c>
       <c r="R5" t="n">
-        <v>7198612</v>
+        <v>7198391</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,27 +1080,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>Kolad granved</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,12 +1115,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1353,7 +1353,7 @@
         <v>128933159</v>
       </c>
       <c r="B8" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1683,32 +1683,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128933172</v>
+        <v>128933125</v>
       </c>
       <c r="B11" t="n">
-        <v>80182</v>
+        <v>88940</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>510</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544801</v>
+        <v>545148</v>
       </c>
       <c r="R11" t="n">
-        <v>7198690</v>
+        <v>7198360</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1752,22 +1752,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1794,10 +1794,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128933125</v>
+        <v>128933891</v>
       </c>
       <c r="B12" t="n">
-        <v>88939</v>
+        <v>78798</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,41 +1805,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>510</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545148</v>
+        <v>545149</v>
       </c>
       <c r="R12" t="n">
-        <v>7198360</v>
+        <v>7198384</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1868,7 +1864,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1878,7 +1874,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På död naken gran med brandljud. På kol.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1893,12 +1894,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2017,48 +2018,52 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128933891</v>
+        <v>128933172</v>
       </c>
       <c r="B14" t="n">
-        <v>78798</v>
+        <v>80182</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545149</v>
+        <v>544801</v>
       </c>
       <c r="R14" t="n">
-        <v>7198384</v>
+        <v>7198690</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2082,27 +2087,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På död naken gran med brandljud. På kol.</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2117,12 +2117,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2132,7 +2132,7 @@
         <v>128933970</v>
       </c>
       <c r="B15" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2460,10 +2460,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128933896</v>
+        <v>128933161</v>
       </c>
       <c r="B18" t="n">
-        <v>78798</v>
+        <v>91554</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2471,37 +2471,41 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>1204</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545160</v>
+        <v>544891</v>
       </c>
       <c r="R18" t="n">
-        <v>7198394</v>
+        <v>7198608</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2525,27 +2529,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:31</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På stående död gran med brandljud. På kol</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2560,22 +2559,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128933932</v>
+        <v>128934084</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>91540</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2583,21 +2582,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2607,13 +2606,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545212</v>
+        <v>544966</v>
       </c>
       <c r="R19" t="n">
-        <v>7198500</v>
+        <v>7198729</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2642,7 +2641,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2652,12 +2651,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack äldre än 5 år på tall</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2684,10 +2678,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128933161</v>
+        <v>128933896</v>
       </c>
       <c r="B20" t="n">
-        <v>91556</v>
+        <v>78798</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2695,41 +2689,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1204</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544891</v>
+        <v>545160</v>
       </c>
       <c r="R20" t="n">
-        <v>7198608</v>
+        <v>7198394</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2753,22 +2743,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På stående död gran med brandljud. På kol</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2783,22 +2778,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128934084</v>
+        <v>128933932</v>
       </c>
       <c r="B21" t="n">
-        <v>91542</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2806,21 +2801,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2830,13 +2825,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544966</v>
+        <v>545212</v>
       </c>
       <c r="R21" t="n">
-        <v>7198729</v>
+        <v>7198500</v>
       </c>
       <c r="S21" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2865,7 +2860,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2875,7 +2870,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre än 5 år på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2905,7 +2905,7 @@
         <v>128933986</v>
       </c>
       <c r="B22" t="n">
-        <v>91556</v>
+        <v>91554</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128933989</v>
+        <v>128933165</v>
       </c>
       <c r="B25" t="n">
         <v>80147</v>
@@ -3260,20 +3260,24 @@
           <t>(Scop.) DC.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544830</v>
+        <v>544837</v>
       </c>
       <c r="R25" t="n">
-        <v>7198678</v>
+        <v>7198665</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3302,7 +3306,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3312,12 +3316,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På sälglåga</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3332,19 +3331,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128933165</v>
+        <v>128933989</v>
       </c>
       <c r="B26" t="n">
         <v>80147</v>
@@ -3372,24 +3371,20 @@
           <t>(Scop.) DC.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>544837</v>
+        <v>544830</v>
       </c>
       <c r="R26" t="n">
-        <v>7198665</v>
+        <v>7198678</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3418,7 +3413,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3428,7 +3423,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3443,12 +3443,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3569,7 +3569,7 @@
         <v>128933879</v>
       </c>
       <c r="B28" t="n">
-        <v>88939</v>
+        <v>88940</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3678,10 +3678,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128933982</v>
+        <v>128933158</v>
       </c>
       <c r="B29" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3689,37 +3689,46 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544845</v>
+        <v>544903</v>
       </c>
       <c r="R29" t="n">
-        <v>7198663</v>
+        <v>7198597</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3748,7 +3757,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3758,7 +3767,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3773,22 +3782,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128933158</v>
+        <v>128933982</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>80147</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3796,46 +3805,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>544903</v>
+        <v>544845</v>
       </c>
       <c r="R30" t="n">
-        <v>7198597</v>
+        <v>7198663</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3889,22 +3889,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128933141</v>
+        <v>128933961</v>
       </c>
       <c r="B31" t="n">
-        <v>79041</v>
+        <v>80147</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3912,41 +3912,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>545088</v>
+        <v>544872</v>
       </c>
       <c r="R31" t="n">
-        <v>7198569</v>
+        <v>7198610</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3970,22 +3966,27 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4000,12 +4001,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4371,10 +4372,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128933961</v>
+        <v>128933980</v>
       </c>
       <c r="B35" t="n">
-        <v>80147</v>
+        <v>91554</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4382,21 +4383,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4406,13 +4407,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>544872</v>
+        <v>544853</v>
       </c>
       <c r="R35" t="n">
-        <v>7198610</v>
+        <v>7198662</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4441,7 +4442,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4451,12 +4452,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>Väl nedbruten låga av sälg</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4483,10 +4484,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128933980</v>
+        <v>128933141</v>
       </c>
       <c r="B36" t="n">
-        <v>91556</v>
+        <v>79041</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4494,37 +4495,41 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>544853</v>
+        <v>545088</v>
       </c>
       <c r="R36" t="n">
-        <v>7198662</v>
+        <v>7198569</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4548,27 +4553,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Väl nedbruten låga av sälg</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4583,69 +4583,60 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128933147</v>
+        <v>128934001</v>
       </c>
       <c r="B37" t="n">
-        <v>57727</v>
+        <v>80182</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>545204</v>
+        <v>544806</v>
       </c>
       <c r="R37" t="n">
-        <v>7198506</v>
+        <v>7198678</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4674,7 +4665,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4684,7 +4675,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4699,19 +4695,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128933212</v>
+        <v>128933147</v>
       </c>
       <c r="B38" t="n">
         <v>57727</v>
@@ -4755,10 +4751,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>544911</v>
+        <v>545204</v>
       </c>
       <c r="R38" t="n">
-        <v>7198620</v>
+        <v>7198506</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4790,7 +4786,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4800,7 +4796,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4827,10 +4823,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128933908</v>
+        <v>128933212</v>
       </c>
       <c r="B39" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4838,37 +4834,46 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>545139</v>
+        <v>544911</v>
       </c>
       <c r="R39" t="n">
-        <v>7198504</v>
+        <v>7198620</v>
       </c>
       <c r="S39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4892,27 +4897,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Två talltitor</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4927,44 +4927,44 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128934001</v>
+        <v>128933908</v>
       </c>
       <c r="B40" t="n">
-        <v>80182</v>
+        <v>57887</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4974,13 +4974,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>544806</v>
+        <v>545139</v>
       </c>
       <c r="R40" t="n">
-        <v>7198678</v>
+        <v>7198504</v>
       </c>
       <c r="S40" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5004,27 +5004,27 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>Två talltitor</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5051,10 +5051,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128933171</v>
+        <v>128933978</v>
       </c>
       <c r="B41" t="n">
-        <v>80146</v>
+        <v>91554</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5062,41 +5062,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>544807</v>
+        <v>544893</v>
       </c>
       <c r="R41" t="n">
-        <v>7198685</v>
+        <v>7198604</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5125,7 +5121,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5135,7 +5131,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På väl nedbruten låga av gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5150,12 +5151,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5273,10 +5274,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128933978</v>
+        <v>128933171</v>
       </c>
       <c r="B43" t="n">
-        <v>91556</v>
+        <v>80146</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5284,37 +5285,41 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>544893</v>
+        <v>544807</v>
       </c>
       <c r="R43" t="n">
-        <v>7198604</v>
+        <v>7198685</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5343,7 +5348,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5353,12 +5358,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:39</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På väl nedbruten låga av gran</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5373,22 +5373,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128933157</v>
+        <v>128933163</v>
       </c>
       <c r="B44" t="n">
-        <v>80147</v>
+        <v>79041</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5396,21 +5396,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5424,10 +5424,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>544908</v>
+        <v>544832</v>
       </c>
       <c r="R44" t="n">
-        <v>7198602</v>
+        <v>7198667</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5469,12 +5469,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Sälg</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5501,10 +5496,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128933154</v>
+        <v>128933129</v>
       </c>
       <c r="B45" t="n">
-        <v>91542</v>
+        <v>78798</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5512,21 +5507,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5540,10 +5535,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>544968</v>
+        <v>545158</v>
       </c>
       <c r="R45" t="n">
-        <v>7198730</v>
+        <v>7198403</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5570,27 +5565,27 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Gran, stor utbredning.</t>
+          <t>Liten kolad stubbe</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5617,10 +5612,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128933163</v>
+        <v>128933154</v>
       </c>
       <c r="B46" t="n">
-        <v>79041</v>
+        <v>91540</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5628,21 +5623,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5656,10 +5651,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>544832</v>
+        <v>544968</v>
       </c>
       <c r="R46" t="n">
-        <v>7198667</v>
+        <v>7198730</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5691,7 +5686,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5701,7 +5696,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Gran, stor utbredning.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5728,10 +5728,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128933129</v>
+        <v>128933157</v>
       </c>
       <c r="B47" t="n">
-        <v>78798</v>
+        <v>80147</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5739,21 +5739,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>545158</v>
+        <v>544908</v>
       </c>
       <c r="R47" t="n">
-        <v>7198403</v>
+        <v>7198602</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5797,27 +5797,27 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Liten kolad stubbe</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6067,10 +6067,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128933136</v>
+        <v>128933870</v>
       </c>
       <c r="B50" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6078,41 +6078,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>545109</v>
+        <v>545136</v>
       </c>
       <c r="R50" t="n">
-        <v>7198551</v>
+        <v>7198363</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6141,7 +6137,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6151,7 +6147,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Nya ringbarkningar från tretåig hackspett på gran.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6166,19 +6167,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128933870</v>
+        <v>128933973</v>
       </c>
       <c r="B51" t="n">
         <v>57727</v>
@@ -6213,10 +6214,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>545136</v>
+        <v>544900</v>
       </c>
       <c r="R51" t="n">
-        <v>7198363</v>
+        <v>7198597</v>
       </c>
       <c r="S51" t="n">
         <v>4</v>
@@ -6243,27 +6244,27 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Nya ringbarkningar från tretåig hackspett på gran.</t>
+          <t>Ringhack äldre än 5 år på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6290,10 +6291,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128933973</v>
+        <v>128933136</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6301,37 +6302,41 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>544900</v>
+        <v>545109</v>
       </c>
       <c r="R52" t="n">
-        <v>7198597</v>
+        <v>7198551</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6355,27 +6360,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack äldre än 5 år på gran</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6390,12 +6390,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6517,7 +6517,7 @@
         <v>128933947</v>
       </c>
       <c r="B54" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 13030-2025 artfynd.xlsx
+++ b/artfynd/A 13030-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128933955</v>
+        <v>128933901</v>
       </c>
       <c r="B2" t="n">
-        <v>92230</v>
+        <v>83007</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>898</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544957</v>
+        <v>545154</v>
       </c>
       <c r="R2" t="n">
-        <v>7198698</v>
+        <v>7198397</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,27 +740,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På bark av gammal gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128933901</v>
+        <v>128933955</v>
       </c>
       <c r="B3" t="n">
-        <v>83007</v>
+        <v>92231</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>898</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,13 +822,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545154</v>
+        <v>544957</v>
       </c>
       <c r="R3" t="n">
-        <v>7198397</v>
+        <v>7198698</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,27 +852,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På bark av gammal gran</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128933958</v>
+        <v>128933126</v>
       </c>
       <c r="B4" t="n">
-        <v>80146</v>
+        <v>78798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,37 +910,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544871</v>
+        <v>545150</v>
       </c>
       <c r="R4" t="n">
-        <v>7198612</v>
+        <v>7198391</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,27 +968,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>Kolad granved</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,22 +1003,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128933126</v>
+        <v>128933958</v>
       </c>
       <c r="B5" t="n">
-        <v>78798</v>
+        <v>80146</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,41 +1026,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545150</v>
+        <v>544871</v>
       </c>
       <c r="R5" t="n">
-        <v>7198391</v>
+        <v>7198612</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,27 +1080,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Kolad granved</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,22 +1115,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128933155</v>
+        <v>128933902</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,41 +1138,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544955</v>
+        <v>545147</v>
       </c>
       <c r="R6" t="n">
-        <v>7198720</v>
+        <v>7198430</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1196,22 +1192,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gamla ringbarkningar på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1226,22 +1227,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128933902</v>
+        <v>128933155</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1249,37 +1250,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545147</v>
+        <v>544955</v>
       </c>
       <c r="R7" t="n">
-        <v>7198430</v>
+        <v>7198720</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,27 +1308,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:51</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Gamla ringbarkningar på tall</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1338,22 +1338,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128933159</v>
+        <v>128933127</v>
       </c>
       <c r="B8" t="n">
-        <v>91837</v>
+        <v>78798</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1361,21 +1361,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544907</v>
+        <v>545155</v>
       </c>
       <c r="R8" t="n">
-        <v>7198585</v>
+        <v>7198397</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1419,22 +1419,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,10 +1461,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128933127</v>
+        <v>128933159</v>
       </c>
       <c r="B9" t="n">
-        <v>78798</v>
+        <v>91838</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545155</v>
+        <v>544907</v>
       </c>
       <c r="R9" t="n">
-        <v>7198397</v>
+        <v>7198585</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1530,22 +1530,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128933125</v>
+        <v>128933891</v>
       </c>
       <c r="B11" t="n">
-        <v>88940</v>
+        <v>78798</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,41 +1694,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>510</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545148</v>
+        <v>545149</v>
       </c>
       <c r="R11" t="n">
-        <v>7198360</v>
+        <v>7198384</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1757,7 +1753,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1767,7 +1763,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På död naken gran med brandljud. På kol.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1782,22 +1783,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128933891</v>
+        <v>128933125</v>
       </c>
       <c r="B12" t="n">
-        <v>78798</v>
+        <v>88940</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,37 +1806,41 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>510</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545149</v>
+        <v>545148</v>
       </c>
       <c r="R12" t="n">
-        <v>7198384</v>
+        <v>7198360</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1864,7 +1869,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1874,12 +1879,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På död naken gran med brandljud. På kol.</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1894,12 +1894,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2129,10 +2129,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128933970</v>
+        <v>128933904</v>
       </c>
       <c r="B15" t="n">
-        <v>91837</v>
+        <v>78444</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2140,21 +2140,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>6437</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2164,13 +2164,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544900</v>
+        <v>545138</v>
       </c>
       <c r="R15" t="n">
-        <v>7198605</v>
+        <v>7198414</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2194,27 +2194,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På gammal granlåga</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2241,10 +2236,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128933904</v>
+        <v>128933970</v>
       </c>
       <c r="B16" t="n">
-        <v>78444</v>
+        <v>91838</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2252,21 +2247,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6437</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2276,13 +2271,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>545138</v>
+        <v>544900</v>
       </c>
       <c r="R16" t="n">
-        <v>7198414</v>
+        <v>7198605</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2306,22 +2301,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2902,10 +2902,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128933986</v>
+        <v>128933164</v>
       </c>
       <c r="B22" t="n">
-        <v>91554</v>
+        <v>80146</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2913,37 +2913,41 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544828</v>
+        <v>544839</v>
       </c>
       <c r="R22" t="n">
-        <v>7198678</v>
+        <v>7198665</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2972,7 +2976,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2982,7 +2986,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2997,22 +3001,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128933164</v>
+        <v>128933875</v>
       </c>
       <c r="B23" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3020,41 +3024,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544839</v>
+        <v>545139</v>
       </c>
       <c r="R23" t="n">
-        <v>7198665</v>
+        <v>7198365</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3078,22 +3078,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Mycket god förekomst</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3108,22 +3113,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128933875</v>
+        <v>128933986</v>
       </c>
       <c r="B24" t="n">
-        <v>79041</v>
+        <v>91554</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3131,21 +3136,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3155,13 +3160,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>545139</v>
+        <v>544828</v>
       </c>
       <c r="R24" t="n">
-        <v>7198365</v>
+        <v>7198678</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3185,27 +3190,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:41</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Mycket god förekomst</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3232,7 +3232,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128933165</v>
+        <v>128933989</v>
       </c>
       <c r="B25" t="n">
         <v>80147</v>
@@ -3260,24 +3260,20 @@
           <t>(Scop.) DC.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544837</v>
+        <v>544830</v>
       </c>
       <c r="R25" t="n">
-        <v>7198665</v>
+        <v>7198678</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3306,7 +3302,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3316,7 +3312,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3331,19 +3332,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128933989</v>
+        <v>128933165</v>
       </c>
       <c r="B26" t="n">
         <v>80147</v>
@@ -3371,20 +3372,24 @@
           <t>(Scop.) DC.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>544830</v>
+        <v>544837</v>
       </c>
       <c r="R26" t="n">
-        <v>7198678</v>
+        <v>7198665</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3413,7 +3418,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3423,12 +3428,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På sälglåga</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3443,12 +3443,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3566,10 +3566,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128933879</v>
+        <v>128933982</v>
       </c>
       <c r="B28" t="n">
-        <v>88940</v>
+        <v>80147</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3577,21 +3577,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>510</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>545153</v>
+        <v>544845</v>
       </c>
       <c r="R28" t="n">
-        <v>7198363</v>
+        <v>7198663</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3631,27 +3631,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:50</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På låga av tall</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3794,10 +3789,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128933982</v>
+        <v>128933879</v>
       </c>
       <c r="B30" t="n">
-        <v>80147</v>
+        <v>88940</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3805,21 +3800,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>510</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3829,10 +3824,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>544845</v>
+        <v>545153</v>
       </c>
       <c r="R30" t="n">
-        <v>7198663</v>
+        <v>7198363</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -3859,22 +3854,27 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På låga av tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4013,10 +4013,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128933130</v>
+        <v>128933980</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>91554</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4024,46 +4024,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>545144</v>
+        <v>544853</v>
       </c>
       <c r="R32" t="n">
-        <v>7198419</v>
+        <v>7198662</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4087,22 +4078,27 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Väl nedbruten låga av sälg</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4117,19 +4113,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128933213</v>
+        <v>128933130</v>
       </c>
       <c r="B33" t="n">
         <v>57727</v>
@@ -4162,24 +4158,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>544897</v>
+        <v>545144</v>
       </c>
       <c r="R33" t="n">
-        <v>7198529</v>
+        <v>7198419</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4206,27 +4199,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Innanför gränsen, bild finns.</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4246,14 +4234,14 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128933156</v>
+        <v>128933213</v>
       </c>
       <c r="B34" t="n">
         <v>57727</v>
@@ -4300,10 +4288,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>544879</v>
+        <v>544897</v>
       </c>
       <c r="R34" t="n">
-        <v>7198601</v>
+        <v>7198529</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4335,7 +4323,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4345,7 +4333,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Innanför gränsen, bild finns.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4365,17 +4358,17 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128933980</v>
+        <v>128933156</v>
       </c>
       <c r="B35" t="n">
-        <v>91554</v>
+        <v>57727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4383,37 +4376,49 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>544853</v>
+        <v>544879</v>
       </c>
       <c r="R35" t="n">
-        <v>7198662</v>
+        <v>7198601</v>
       </c>
       <c r="S35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4442,7 +4447,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4452,12 +4457,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Väl nedbruten låga av sälg</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4472,12 +4472,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4707,10 +4707,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128933147</v>
+        <v>128933908</v>
       </c>
       <c r="B38" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4718,46 +4718,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>545204</v>
+        <v>545139</v>
       </c>
       <c r="R38" t="n">
-        <v>7198506</v>
+        <v>7198504</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4781,22 +4772,27 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Två talltitor</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4811,19 +4807,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128933212</v>
+        <v>128933147</v>
       </c>
       <c r="B39" t="n">
         <v>57727</v>
@@ -4867,10 +4863,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>544911</v>
+        <v>545204</v>
       </c>
       <c r="R39" t="n">
-        <v>7198620</v>
+        <v>7198506</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4902,7 +4898,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4912,7 +4908,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4939,10 +4935,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128933908</v>
+        <v>128933212</v>
       </c>
       <c r="B40" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4950,37 +4946,46 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>545139</v>
+        <v>544911</v>
       </c>
       <c r="R40" t="n">
-        <v>7198504</v>
+        <v>7198620</v>
       </c>
       <c r="S40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5004,27 +5009,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Två talltitor</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5039,22 +5039,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128933978</v>
+        <v>128933124</v>
       </c>
       <c r="B41" t="n">
-        <v>91554</v>
+        <v>79041</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5062,37 +5062,41 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>544893</v>
+        <v>545144</v>
       </c>
       <c r="R41" t="n">
-        <v>7198604</v>
+        <v>7198368</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5116,27 +5120,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:39</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På väl nedbruten låga av gran</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5151,22 +5150,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128933124</v>
+        <v>128933978</v>
       </c>
       <c r="B42" t="n">
-        <v>79041</v>
+        <v>91554</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5174,41 +5173,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>545144</v>
+        <v>544893</v>
       </c>
       <c r="R42" t="n">
-        <v>7198368</v>
+        <v>7198604</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5232,22 +5227,27 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På väl nedbruten låga av gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5262,12 +5262,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5385,10 +5385,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128933163</v>
+        <v>128933154</v>
       </c>
       <c r="B44" t="n">
-        <v>79041</v>
+        <v>91540</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5396,21 +5396,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5424,10 +5424,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>544832</v>
+        <v>544968</v>
       </c>
       <c r="R44" t="n">
-        <v>7198667</v>
+        <v>7198730</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5469,7 +5469,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Gran, stor utbredning.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5496,10 +5501,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128933129</v>
+        <v>128933163</v>
       </c>
       <c r="B45" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5507,21 +5512,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5535,10 +5540,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>545158</v>
+        <v>544832</v>
       </c>
       <c r="R45" t="n">
-        <v>7198403</v>
+        <v>7198667</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5565,27 +5570,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Liten kolad stubbe</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5612,10 +5612,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128933154</v>
+        <v>128933129</v>
       </c>
       <c r="B46" t="n">
-        <v>91540</v>
+        <v>78798</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5623,21 +5623,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5651,10 +5651,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>544968</v>
+        <v>545158</v>
       </c>
       <c r="R46" t="n">
-        <v>7198730</v>
+        <v>7198403</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5681,27 +5681,27 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Gran, stor utbredning.</t>
+          <t>Liten kolad stubbe</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5955,10 +5955,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128933984</v>
+        <v>128933136</v>
       </c>
       <c r="B49" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5966,37 +5966,41 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>544836</v>
+        <v>545109</v>
       </c>
       <c r="R49" t="n">
-        <v>7198663</v>
+        <v>7198551</v>
       </c>
       <c r="S49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6020,27 +6024,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:56</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Högt upp på gammal sälg</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6055,22 +6054,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128933870</v>
+        <v>128933984</v>
       </c>
       <c r="B50" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6078,21 +6077,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6102,10 +6101,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>545136</v>
+        <v>544836</v>
       </c>
       <c r="R50" t="n">
-        <v>7198363</v>
+        <v>7198663</v>
       </c>
       <c r="S50" t="n">
         <v>4</v>
@@ -6132,27 +6131,27 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Nya ringbarkningar från tretåig hackspett på gran.</t>
+          <t>Högt upp på gammal sälg</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6179,7 +6178,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128933973</v>
+        <v>128933870</v>
       </c>
       <c r="B51" t="n">
         <v>57727</v>
@@ -6214,10 +6213,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>544900</v>
+        <v>545136</v>
       </c>
       <c r="R51" t="n">
-        <v>7198597</v>
+        <v>7198363</v>
       </c>
       <c r="S51" t="n">
         <v>4</v>
@@ -6244,27 +6243,27 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack äldre än 5 år på gran</t>
+          <t>Nya ringbarkningar från tretåig hackspett på gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6291,10 +6290,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128933136</v>
+        <v>128933973</v>
       </c>
       <c r="B52" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6302,41 +6301,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>545109</v>
+        <v>544900</v>
       </c>
       <c r="R52" t="n">
-        <v>7198551</v>
+        <v>7198597</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6360,22 +6355,27 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack äldre än 5 år på gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6390,12 +6390,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>

--- a/artfynd/A 13030-2025 artfynd.xlsx
+++ b/artfynd/A 13030-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128933901</v>
+        <v>128933955</v>
       </c>
       <c r="B2" t="n">
-        <v>83007</v>
+        <v>92231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>898</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545154</v>
+        <v>544957</v>
       </c>
       <c r="R2" t="n">
-        <v>7198397</v>
+        <v>7198698</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,27 +740,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På bark av gammal gran</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128933955</v>
+        <v>128933901</v>
       </c>
       <c r="B3" t="n">
-        <v>92231</v>
+        <v>83007</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>898</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,13 +822,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544957</v>
+        <v>545154</v>
       </c>
       <c r="R3" t="n">
-        <v>7198698</v>
+        <v>7198397</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,27 +852,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På bark av gammal gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128933126</v>
+        <v>128933958</v>
       </c>
       <c r="B4" t="n">
-        <v>78798</v>
+        <v>80146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,41 +910,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545150</v>
+        <v>544871</v>
       </c>
       <c r="R4" t="n">
-        <v>7198391</v>
+        <v>7198612</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -968,27 +964,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Kolad granved</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,22 +999,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128933958</v>
+        <v>128933126</v>
       </c>
       <c r="B5" t="n">
-        <v>80146</v>
+        <v>78798</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,37 +1022,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544871</v>
+        <v>545150</v>
       </c>
       <c r="R5" t="n">
-        <v>7198612</v>
+        <v>7198391</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,27 +1080,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>Kolad granved</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,22 +1115,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128933902</v>
+        <v>128933155</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,37 +1138,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545147</v>
+        <v>544955</v>
       </c>
       <c r="R6" t="n">
-        <v>7198430</v>
+        <v>7198720</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1192,27 +1196,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:51</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gamla ringbarkningar på tall</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1227,22 +1226,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128933155</v>
+        <v>128933902</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1250,41 +1249,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544955</v>
+        <v>545147</v>
       </c>
       <c r="R7" t="n">
-        <v>7198720</v>
+        <v>7198430</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1308,22 +1303,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gamla ringbarkningar på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1338,22 +1338,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128933127</v>
+        <v>128933159</v>
       </c>
       <c r="B8" t="n">
-        <v>78798</v>
+        <v>91838</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1361,21 +1361,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545155</v>
+        <v>544907</v>
       </c>
       <c r="R8" t="n">
-        <v>7198397</v>
+        <v>7198585</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1419,22 +1419,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,10 +1461,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128933159</v>
+        <v>128933127</v>
       </c>
       <c r="B9" t="n">
-        <v>91838</v>
+        <v>78798</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544907</v>
+        <v>545155</v>
       </c>
       <c r="R9" t="n">
-        <v>7198585</v>
+        <v>7198397</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1530,22 +1530,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128933891</v>
+        <v>128933125</v>
       </c>
       <c r="B11" t="n">
-        <v>78798</v>
+        <v>88940</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,37 +1694,41 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>510</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545149</v>
+        <v>545148</v>
       </c>
       <c r="R11" t="n">
-        <v>7198384</v>
+        <v>7198360</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1753,7 +1757,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,12 +1767,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På död naken gran med brandljud. På kol.</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1783,22 +1782,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128933125</v>
+        <v>128933999</v>
       </c>
       <c r="B12" t="n">
-        <v>88940</v>
+        <v>80146</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,41 +1805,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545148</v>
+        <v>544807</v>
       </c>
       <c r="R12" t="n">
-        <v>7198360</v>
+        <v>7198677</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1864,22 +1859,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På gammal sälg i sluttning</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1894,22 +1894,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128933999</v>
+        <v>128933891</v>
       </c>
       <c r="B13" t="n">
-        <v>80146</v>
+        <v>78798</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1917,21 +1917,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1941,10 +1941,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544807</v>
+        <v>545149</v>
       </c>
       <c r="R13" t="n">
-        <v>7198677</v>
+        <v>7198384</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -1971,27 +1971,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gammal sälg i sluttning</t>
+          <t>På död naken gran med brandljud. På kol.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2460,10 +2460,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128933161</v>
+        <v>128933932</v>
       </c>
       <c r="B18" t="n">
-        <v>91554</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2471,41 +2471,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544891</v>
+        <v>545212</v>
       </c>
       <c r="R18" t="n">
-        <v>7198608</v>
+        <v>7198500</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2534,7 +2530,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2544,7 +2540,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre än 5 år på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2559,22 +2560,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128934084</v>
+        <v>128933896</v>
       </c>
       <c r="B19" t="n">
-        <v>91540</v>
+        <v>78798</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2582,21 +2583,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2606,13 +2607,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544966</v>
+        <v>545160</v>
       </c>
       <c r="R19" t="n">
-        <v>7198729</v>
+        <v>7198394</v>
       </c>
       <c r="S19" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2636,22 +2637,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På stående död gran med brandljud. På kol</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2678,10 +2684,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128933896</v>
+        <v>128933161</v>
       </c>
       <c r="B20" t="n">
-        <v>78798</v>
+        <v>91554</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2689,37 +2695,41 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>1204</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545160</v>
+        <v>544891</v>
       </c>
       <c r="R20" t="n">
-        <v>7198394</v>
+        <v>7198608</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2743,27 +2753,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:31</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På stående död gran med brandljud. På kol</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2778,22 +2783,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128933932</v>
+        <v>128934084</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>91540</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2801,21 +2806,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2825,13 +2830,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545212</v>
+        <v>544966</v>
       </c>
       <c r="R21" t="n">
-        <v>7198500</v>
+        <v>7198729</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2860,7 +2865,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2870,12 +2875,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack äldre än 5 år på tall</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3566,10 +3566,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128933982</v>
+        <v>128933879</v>
       </c>
       <c r="B28" t="n">
-        <v>80147</v>
+        <v>88940</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3577,21 +3577,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>510</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>544845</v>
+        <v>545153</v>
       </c>
       <c r="R28" t="n">
-        <v>7198663</v>
+        <v>7198363</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3631,22 +3631,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På låga av tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3673,10 +3678,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128933158</v>
+        <v>128933982</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>80147</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3684,46 +3689,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544903</v>
+        <v>544845</v>
       </c>
       <c r="R29" t="n">
-        <v>7198597</v>
+        <v>7198663</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3752,7 +3748,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3762,7 +3758,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3777,22 +3773,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128933879</v>
+        <v>128933158</v>
       </c>
       <c r="B30" t="n">
-        <v>88940</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3800,37 +3796,46 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>545153</v>
+        <v>544903</v>
       </c>
       <c r="R30" t="n">
-        <v>7198363</v>
+        <v>7198597</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3854,27 +3859,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:50</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På låga av tall</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3889,12 +3889,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4707,10 +4707,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128933908</v>
+        <v>128933147</v>
       </c>
       <c r="B38" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4718,37 +4718,46 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>545139</v>
+        <v>545204</v>
       </c>
       <c r="R38" t="n">
-        <v>7198504</v>
+        <v>7198506</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4772,27 +4781,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Två talltitor</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4807,19 +4811,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128933147</v>
+        <v>128933212</v>
       </c>
       <c r="B39" t="n">
         <v>57727</v>
@@ -4863,10 +4867,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>545204</v>
+        <v>544911</v>
       </c>
       <c r="R39" t="n">
-        <v>7198506</v>
+        <v>7198620</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4898,7 +4902,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4908,7 +4912,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4935,10 +4939,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128933212</v>
+        <v>128933908</v>
       </c>
       <c r="B40" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4946,46 +4950,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>544911</v>
+        <v>545139</v>
       </c>
       <c r="R40" t="n">
-        <v>7198620</v>
+        <v>7198504</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5009,22 +5004,27 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Två talltitor</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5039,12 +5039,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5162,10 +5162,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128933978</v>
+        <v>128933171</v>
       </c>
       <c r="B42" t="n">
-        <v>91554</v>
+        <v>80146</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5173,37 +5173,41 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>544893</v>
+        <v>544807</v>
       </c>
       <c r="R42" t="n">
-        <v>7198604</v>
+        <v>7198685</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5232,7 +5236,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5242,12 +5246,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:39</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På väl nedbruten låga av gran</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5262,22 +5261,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128933171</v>
+        <v>128933978</v>
       </c>
       <c r="B43" t="n">
-        <v>80146</v>
+        <v>91554</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5285,41 +5284,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>544807</v>
+        <v>544893</v>
       </c>
       <c r="R43" t="n">
-        <v>7198685</v>
+        <v>7198604</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5348,7 +5343,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5358,7 +5353,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På väl nedbruten låga av gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5373,22 +5373,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128933154</v>
+        <v>128933163</v>
       </c>
       <c r="B44" t="n">
-        <v>91540</v>
+        <v>79041</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5396,21 +5396,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5424,10 +5424,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>544968</v>
+        <v>544832</v>
       </c>
       <c r="R44" t="n">
-        <v>7198730</v>
+        <v>7198667</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5469,12 +5469,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Gran, stor utbredning.</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5501,10 +5496,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128933163</v>
+        <v>128933129</v>
       </c>
       <c r="B45" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5512,21 +5507,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5540,10 +5535,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>544832</v>
+        <v>545158</v>
       </c>
       <c r="R45" t="n">
-        <v>7198667</v>
+        <v>7198403</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5570,22 +5565,27 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Liten kolad stubbe</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5612,10 +5612,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128933129</v>
+        <v>128933154</v>
       </c>
       <c r="B46" t="n">
-        <v>78798</v>
+        <v>91540</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5623,21 +5623,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5651,10 +5651,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>545158</v>
+        <v>544968</v>
       </c>
       <c r="R46" t="n">
-        <v>7198403</v>
+        <v>7198730</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5681,27 +5681,27 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Liten kolad stubbe</t>
+          <t>Gran, stor utbredning.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5955,10 +5955,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128933136</v>
+        <v>128933966</v>
       </c>
       <c r="B49" t="n">
-        <v>79041</v>
+        <v>80147</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5966,41 +5966,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>545109</v>
+        <v>544905</v>
       </c>
       <c r="R49" t="n">
-        <v>7198551</v>
+        <v>7198603</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6024,22 +6020,27 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6054,12 +6055,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6178,10 +6179,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128933870</v>
+        <v>128933136</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6189,37 +6190,41 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>545136</v>
+        <v>545109</v>
       </c>
       <c r="R51" t="n">
-        <v>7198363</v>
+        <v>7198551</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6248,7 +6253,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6258,12 +6263,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Nya ringbarkningar från tretåig hackspett på gran.</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6278,19 +6278,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128933973</v>
+        <v>128933870</v>
       </c>
       <c r="B52" t="n">
         <v>57727</v>
@@ -6325,10 +6325,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>544900</v>
+        <v>545136</v>
       </c>
       <c r="R52" t="n">
-        <v>7198597</v>
+        <v>7198363</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6355,27 +6355,27 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack äldre än 5 år på gran</t>
+          <t>Nya ringbarkningar från tretåig hackspett på gran.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6402,10 +6402,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128933966</v>
+        <v>128933973</v>
       </c>
       <c r="B53" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6413,21 +6413,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6437,13 +6437,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>544905</v>
+        <v>544900</v>
       </c>
       <c r="R53" t="n">
-        <v>7198603</v>
+        <v>7198597</v>
       </c>
       <c r="S53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6482,12 +6482,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>Ringhack äldre än 5 år på gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6514,10 +6514,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128933947</v>
+        <v>128933167</v>
       </c>
       <c r="B54" t="n">
-        <v>91504</v>
+        <v>80050</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6525,37 +6525,41 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5447</v>
+        <v>6456</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>544971</v>
+        <v>544823</v>
       </c>
       <c r="R54" t="n">
-        <v>7198722</v>
+        <v>7198695</v>
       </c>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6584,7 +6588,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6594,7 +6598,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Asp</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6609,22 +6618,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128933167</v>
+        <v>128933947</v>
       </c>
       <c r="B55" t="n">
-        <v>80050</v>
+        <v>91504</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6632,41 +6641,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>544823</v>
+        <v>544971</v>
       </c>
       <c r="R55" t="n">
-        <v>7198695</v>
+        <v>7198722</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6695,7 +6700,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6705,12 +6710,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:14</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Asp</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6725,12 +6725,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>

--- a/artfynd/A 13030-2025 artfynd.xlsx
+++ b/artfynd/A 13030-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128933955</v>
       </c>
       <c r="B2" t="n">
-        <v>92231</v>
+        <v>92234</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>128933901</v>
       </c>
       <c r="B3" t="n">
-        <v>83007</v>
+        <v>83011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128933958</v>
+        <v>128933126</v>
       </c>
       <c r="B4" t="n">
-        <v>80146</v>
+        <v>78800</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,37 +910,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544871</v>
+        <v>545150</v>
       </c>
       <c r="R4" t="n">
-        <v>7198612</v>
+        <v>7198391</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,27 +968,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>Kolad granved</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,22 +1003,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128933126</v>
+        <v>128933958</v>
       </c>
       <c r="B5" t="n">
-        <v>78798</v>
+        <v>80148</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,41 +1026,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545150</v>
+        <v>544871</v>
       </c>
       <c r="R5" t="n">
-        <v>7198391</v>
+        <v>7198612</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,27 +1080,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Kolad granved</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,12 +1115,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1130,7 +1130,7 @@
         <v>128933155</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>128933159</v>
       </c>
       <c r="B8" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>128933127</v>
       </c>
       <c r="B9" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>128933131</v>
       </c>
       <c r="B10" t="n">
-        <v>80174</v>
+        <v>80176</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>128933125</v>
       </c>
       <c r="B11" t="n">
-        <v>88940</v>
+        <v>88943</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         <v>128933999</v>
       </c>
       <c r="B12" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1906,48 +1906,52 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128933891</v>
+        <v>128933172</v>
       </c>
       <c r="B13" t="n">
-        <v>78798</v>
+        <v>80184</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6464</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545149</v>
+        <v>544801</v>
       </c>
       <c r="R13" t="n">
-        <v>7198384</v>
+        <v>7198690</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1971,27 +1975,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På död naken gran med brandljud. På kol.</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2006,64 +2005,60 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128933172</v>
+        <v>128933891</v>
       </c>
       <c r="B14" t="n">
-        <v>80182</v>
+        <v>78800</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544801</v>
+        <v>545149</v>
       </c>
       <c r="R14" t="n">
-        <v>7198690</v>
+        <v>7198384</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2087,22 +2082,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På död naken gran med brandljud. På kol.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2117,22 +2117,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128933904</v>
+        <v>128933970</v>
       </c>
       <c r="B15" t="n">
-        <v>78444</v>
+        <v>91841</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2140,21 +2140,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6437</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2164,13 +2164,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545138</v>
+        <v>544900</v>
       </c>
       <c r="R15" t="n">
-        <v>7198414</v>
+        <v>7198605</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2194,22 +2194,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2236,10 +2241,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128933970</v>
+        <v>128933904</v>
       </c>
       <c r="B16" t="n">
-        <v>91838</v>
+        <v>78446</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2247,21 +2252,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>6437</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2271,13 +2276,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544900</v>
+        <v>545138</v>
       </c>
       <c r="R16" t="n">
-        <v>7198605</v>
+        <v>7198414</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2301,27 +2306,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På gammal granlåga</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2351,7 +2351,7 @@
         <v>128933968</v>
       </c>
       <c r="B17" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2460,10 +2460,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128933932</v>
+        <v>128933896</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>78800</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2471,21 +2471,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545212</v>
+        <v>545160</v>
       </c>
       <c r="R18" t="n">
-        <v>7198500</v>
+        <v>7198394</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2525,27 +2525,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre än 5 år på tall</t>
+          <t>På stående död gran med brandljud. På kol</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2572,10 +2572,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128933896</v>
+        <v>128933161</v>
       </c>
       <c r="B19" t="n">
-        <v>78798</v>
+        <v>91557</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2583,37 +2583,41 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>1204</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545160</v>
+        <v>544891</v>
       </c>
       <c r="R19" t="n">
-        <v>7198394</v>
+        <v>7198608</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2637,27 +2641,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:31</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På stående död gran med brandljud. På kol</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2672,22 +2671,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128933161</v>
+        <v>128934084</v>
       </c>
       <c r="B20" t="n">
-        <v>91554</v>
+        <v>91543</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2695,41 +2694,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544891</v>
+        <v>544966</v>
       </c>
       <c r="R20" t="n">
-        <v>7198608</v>
+        <v>7198729</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2758,7 +2753,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2768,7 +2763,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2783,22 +2778,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128934084</v>
+        <v>128933932</v>
       </c>
       <c r="B21" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2806,21 +2801,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2830,13 +2825,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544966</v>
+        <v>545212</v>
       </c>
       <c r="R21" t="n">
-        <v>7198729</v>
+        <v>7198500</v>
       </c>
       <c r="S21" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2865,7 +2860,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2875,7 +2870,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre än 5 år på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2902,10 +2902,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128933164</v>
+        <v>128933986</v>
       </c>
       <c r="B22" t="n">
-        <v>80146</v>
+        <v>91557</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2913,41 +2913,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544839</v>
+        <v>544828</v>
       </c>
       <c r="R22" t="n">
-        <v>7198665</v>
+        <v>7198678</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2976,7 +2972,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2986,7 +2982,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3001,12 +2997,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3016,7 +3012,7 @@
         <v>128933875</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3125,10 +3121,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128933986</v>
+        <v>128933164</v>
       </c>
       <c r="B24" t="n">
-        <v>91554</v>
+        <v>80148</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3136,37 +3132,41 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544828</v>
+        <v>544839</v>
       </c>
       <c r="R24" t="n">
-        <v>7198678</v>
+        <v>7198665</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3220,12 +3220,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3235,7 +3235,7 @@
         <v>128933989</v>
       </c>
       <c r="B25" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v>128933165</v>
       </c>
       <c r="B26" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>128933166</v>
       </c>
       <c r="B27" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>128933879</v>
       </c>
       <c r="B28" t="n">
-        <v>88940</v>
+        <v>88943</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
         <v>128933982</v>
       </c>
       <c r="B29" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3901,10 +3901,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128933961</v>
+        <v>128933980</v>
       </c>
       <c r="B31" t="n">
-        <v>80147</v>
+        <v>91557</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3912,21 +3912,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3936,13 +3936,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>544872</v>
+        <v>544853</v>
       </c>
       <c r="R31" t="n">
-        <v>7198610</v>
+        <v>7198662</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>Väl nedbruten låga av sälg</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4013,10 +4013,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128933980</v>
+        <v>128933961</v>
       </c>
       <c r="B32" t="n">
-        <v>91554</v>
+        <v>80149</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4024,21 +4024,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1204</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4048,13 +4048,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>544853</v>
+        <v>544872</v>
       </c>
       <c r="R32" t="n">
-        <v>7198662</v>
+        <v>7198610</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Väl nedbruten låga av sälg</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4125,10 +4125,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128933130</v>
+        <v>128933141</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4136,21 +4136,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4158,21 +4158,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>545144</v>
+        <v>545088</v>
       </c>
       <c r="R33" t="n">
-        <v>7198419</v>
+        <v>7198569</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4204,7 +4199,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4214,7 +4209,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4241,7 +4236,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128933213</v>
+        <v>128933130</v>
       </c>
       <c r="B34" t="n">
         <v>57727</v>
@@ -4274,24 +4269,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>544897</v>
+        <v>545144</v>
       </c>
       <c r="R34" t="n">
-        <v>7198529</v>
+        <v>7198419</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4318,27 +4310,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Innanför gränsen, bild finns.</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4358,14 +4345,14 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128933156</v>
+        <v>128933213</v>
       </c>
       <c r="B35" t="n">
         <v>57727</v>
@@ -4412,10 +4399,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>544879</v>
+        <v>544897</v>
       </c>
       <c r="R35" t="n">
-        <v>7198601</v>
+        <v>7198529</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4447,7 +4434,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4457,7 +4444,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Innanför gränsen, bild finns.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4484,10 +4476,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128933141</v>
+        <v>128933156</v>
       </c>
       <c r="B36" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4495,21 +4487,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4517,16 +4509,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>545088</v>
+        <v>544879</v>
       </c>
       <c r="R36" t="n">
-        <v>7198569</v>
+        <v>7198601</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4553,22 +4553,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4588,55 +4588,64 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128934001</v>
+        <v>128933147</v>
       </c>
       <c r="B37" t="n">
-        <v>80182</v>
+        <v>57727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>544806</v>
+        <v>545204</v>
       </c>
       <c r="R37" t="n">
-        <v>7198678</v>
+        <v>7198506</v>
       </c>
       <c r="S37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4665,7 +4674,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4675,12 +4684,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:21</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4695,19 +4699,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128933147</v>
+        <v>128933212</v>
       </c>
       <c r="B38" t="n">
         <v>57727</v>
@@ -4751,10 +4755,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>545204</v>
+        <v>544911</v>
       </c>
       <c r="R38" t="n">
-        <v>7198506</v>
+        <v>7198620</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4786,7 +4790,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4796,7 +4800,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4823,10 +4827,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128933212</v>
+        <v>128933908</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4834,46 +4838,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>544911</v>
+        <v>545139</v>
       </c>
       <c r="R39" t="n">
-        <v>7198620</v>
+        <v>7198504</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4897,22 +4892,27 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Två talltitor</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4927,44 +4927,44 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128933908</v>
+        <v>128934001</v>
       </c>
       <c r="B40" t="n">
-        <v>57887</v>
+        <v>80184</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4974,13 +4974,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>545139</v>
+        <v>544806</v>
       </c>
       <c r="R40" t="n">
-        <v>7198504</v>
+        <v>7198678</v>
       </c>
       <c r="S40" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5004,27 +5004,27 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Två talltitor</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5051,10 +5051,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128933124</v>
+        <v>128933978</v>
       </c>
       <c r="B41" t="n">
-        <v>79041</v>
+        <v>91557</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5062,41 +5062,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>545144</v>
+        <v>544893</v>
       </c>
       <c r="R41" t="n">
-        <v>7198368</v>
+        <v>7198604</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5120,22 +5116,27 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På väl nedbruten låga av gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5150,22 +5151,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128933171</v>
+        <v>128933124</v>
       </c>
       <c r="B42" t="n">
-        <v>80146</v>
+        <v>79043</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5173,21 +5174,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5201,10 +5202,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>544807</v>
+        <v>545144</v>
       </c>
       <c r="R42" t="n">
-        <v>7198685</v>
+        <v>7198368</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5231,22 +5232,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5273,10 +5274,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128933978</v>
+        <v>128933171</v>
       </c>
       <c r="B43" t="n">
-        <v>91554</v>
+        <v>80148</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5284,37 +5285,41 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>544893</v>
+        <v>544807</v>
       </c>
       <c r="R43" t="n">
-        <v>7198604</v>
+        <v>7198685</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5343,7 +5348,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5353,12 +5358,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:39</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På väl nedbruten låga av gran</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5373,22 +5373,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128933163</v>
+        <v>128933154</v>
       </c>
       <c r="B44" t="n">
-        <v>79041</v>
+        <v>91543</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5396,21 +5396,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5424,10 +5424,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>544832</v>
+        <v>544968</v>
       </c>
       <c r="R44" t="n">
-        <v>7198667</v>
+        <v>7198730</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5469,7 +5469,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Gran, stor utbredning.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5496,10 +5501,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128933129</v>
+        <v>128933157</v>
       </c>
       <c r="B45" t="n">
-        <v>78798</v>
+        <v>80149</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5507,21 +5512,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5535,10 +5540,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>545158</v>
+        <v>544908</v>
       </c>
       <c r="R45" t="n">
-        <v>7198403</v>
+        <v>7198602</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5565,27 +5570,27 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Liten kolad stubbe</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5612,10 +5617,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128933154</v>
+        <v>128933129</v>
       </c>
       <c r="B46" t="n">
-        <v>91540</v>
+        <v>78800</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5623,21 +5628,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5651,10 +5656,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>544968</v>
+        <v>545158</v>
       </c>
       <c r="R46" t="n">
-        <v>7198730</v>
+        <v>7198403</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5681,27 +5686,27 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Gran, stor utbredning.</t>
+          <t>Liten kolad stubbe</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5728,10 +5733,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128933157</v>
+        <v>128933163</v>
       </c>
       <c r="B47" t="n">
-        <v>80147</v>
+        <v>79043</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5739,21 +5744,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5767,10 +5772,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>544908</v>
+        <v>544832</v>
       </c>
       <c r="R47" t="n">
-        <v>7198602</v>
+        <v>7198667</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5802,7 +5807,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5812,12 +5817,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Sälg</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5847,7 +5847,7 @@
         <v>128933139</v>
       </c>
       <c r="B48" t="n">
-        <v>80174</v>
+        <v>80176</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5955,10 +5955,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128933966</v>
+        <v>128933973</v>
       </c>
       <c r="B49" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5966,21 +5966,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5990,13 +5990,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>544905</v>
+        <v>544900</v>
       </c>
       <c r="R49" t="n">
-        <v>7198603</v>
+        <v>7198597</v>
       </c>
       <c r="S49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>Ringhack äldre än 5 år på gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6067,10 +6067,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128933984</v>
+        <v>128933966</v>
       </c>
       <c r="B50" t="n">
-        <v>80146</v>
+        <v>80149</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6078,21 +6078,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6102,13 +6102,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>544836</v>
+        <v>544905</v>
       </c>
       <c r="R50" t="n">
-        <v>7198663</v>
+        <v>7198603</v>
       </c>
       <c r="S50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Högt upp på gammal sälg</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6182,7 +6182,7 @@
         <v>128933136</v>
       </c>
       <c r="B51" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6290,10 +6290,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128933870</v>
+        <v>128933984</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>80148</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6301,21 +6301,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6325,10 +6325,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>545136</v>
+        <v>544836</v>
       </c>
       <c r="R52" t="n">
-        <v>7198363</v>
+        <v>7198663</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6355,27 +6355,27 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Nya ringbarkningar från tretåig hackspett på gran.</t>
+          <t>Högt upp på gammal sälg</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6402,7 +6402,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128933973</v>
+        <v>128933870</v>
       </c>
       <c r="B53" t="n">
         <v>57727</v>
@@ -6437,10 +6437,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>544900</v>
+        <v>545136</v>
       </c>
       <c r="R53" t="n">
-        <v>7198597</v>
+        <v>7198363</v>
       </c>
       <c r="S53" t="n">
         <v>4</v>
@@ -6467,27 +6467,27 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack äldre än 5 år på gran</t>
+          <t>Nya ringbarkningar från tretåig hackspett på gran.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6514,10 +6514,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128933167</v>
+        <v>128933947</v>
       </c>
       <c r="B54" t="n">
-        <v>80050</v>
+        <v>91507</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6525,41 +6525,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>544823</v>
+        <v>544971</v>
       </c>
       <c r="R54" t="n">
-        <v>7198695</v>
+        <v>7198722</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6588,7 +6584,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6598,12 +6594,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:14</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Asp</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6618,22 +6609,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128933947</v>
+        <v>128933167</v>
       </c>
       <c r="B55" t="n">
-        <v>91504</v>
+        <v>80052</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6641,37 +6632,41 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>6456</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>544971</v>
+        <v>544823</v>
       </c>
       <c r="R55" t="n">
-        <v>7198722</v>
+        <v>7198695</v>
       </c>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6700,7 +6695,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6710,7 +6705,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Asp</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6725,12 +6725,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6740,7 +6740,7 @@
         <v>128933991</v>
       </c>
       <c r="B56" t="n">
-        <v>80050</v>
+        <v>80052</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 13030-2025 artfynd.xlsx
+++ b/artfynd/A 13030-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128933955</v>
       </c>
       <c r="B2" t="n">
-        <v>92234</v>
+        <v>92236</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>128933901</v>
       </c>
       <c r="B3" t="n">
-        <v>83011</v>
+        <v>83012</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128933126</v>
+        <v>128933958</v>
       </c>
       <c r="B4" t="n">
-        <v>78800</v>
+        <v>80149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,41 +910,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545150</v>
+        <v>544871</v>
       </c>
       <c r="R4" t="n">
-        <v>7198391</v>
+        <v>7198612</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -968,27 +964,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Kolad granved</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,22 +999,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128933958</v>
+        <v>128933126</v>
       </c>
       <c r="B5" t="n">
-        <v>80148</v>
+        <v>78801</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,37 +1022,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544871</v>
+        <v>545150</v>
       </c>
       <c r="R5" t="n">
-        <v>7198612</v>
+        <v>7198391</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,27 +1080,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>Kolad granved</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,12 +1115,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1130,7 +1130,7 @@
         <v>128933155</v>
       </c>
       <c r="B6" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1350,10 +1350,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128933159</v>
+        <v>128933127</v>
       </c>
       <c r="B8" t="n">
-        <v>91841</v>
+        <v>78801</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1361,21 +1361,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544907</v>
+        <v>545155</v>
       </c>
       <c r="R8" t="n">
-        <v>7198585</v>
+        <v>7198397</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1419,22 +1419,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,10 +1461,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128933127</v>
+        <v>128933159</v>
       </c>
       <c r="B9" t="n">
-        <v>78800</v>
+        <v>91843</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545155</v>
+        <v>544907</v>
       </c>
       <c r="R9" t="n">
-        <v>7198397</v>
+        <v>7198585</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1530,22 +1530,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,7 +1575,7 @@
         <v>128933131</v>
       </c>
       <c r="B10" t="n">
-        <v>80176</v>
+        <v>80177</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>128933125</v>
       </c>
       <c r="B11" t="n">
-        <v>88943</v>
+        <v>88945</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         <v>128933999</v>
       </c>
       <c r="B12" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1906,52 +1906,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128933172</v>
+        <v>128933891</v>
       </c>
       <c r="B13" t="n">
-        <v>80184</v>
+        <v>78801</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6464</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544801</v>
+        <v>545149</v>
       </c>
       <c r="R13" t="n">
-        <v>7198690</v>
+        <v>7198384</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1975,22 +1971,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På död naken gran med brandljud. På kol.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2005,60 +2006,64 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128933891</v>
+        <v>128933172</v>
       </c>
       <c r="B14" t="n">
-        <v>78800</v>
+        <v>80185</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545149</v>
+        <v>544801</v>
       </c>
       <c r="R14" t="n">
-        <v>7198384</v>
+        <v>7198690</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2082,27 +2087,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På död naken gran med brandljud. På kol.</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2117,12 +2117,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2132,7 +2132,7 @@
         <v>128933970</v>
       </c>
       <c r="B15" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>128933904</v>
       </c>
       <c r="B16" t="n">
-        <v>78446</v>
+        <v>78447</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>128933968</v>
       </c>
       <c r="B17" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2460,10 +2460,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128933896</v>
+        <v>128933161</v>
       </c>
       <c r="B18" t="n">
-        <v>78800</v>
+        <v>91559</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2471,37 +2471,41 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>1204</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545160</v>
+        <v>544891</v>
       </c>
       <c r="R18" t="n">
-        <v>7198394</v>
+        <v>7198608</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2525,27 +2529,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:31</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På stående död gran med brandljud. På kol</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2560,22 +2559,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128933161</v>
+        <v>128934084</v>
       </c>
       <c r="B19" t="n">
-        <v>91557</v>
+        <v>91545</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2583,41 +2582,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544891</v>
+        <v>544966</v>
       </c>
       <c r="R19" t="n">
-        <v>7198608</v>
+        <v>7198729</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2646,7 +2641,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2656,7 +2651,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2671,22 +2666,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128934084</v>
+        <v>128933896</v>
       </c>
       <c r="B20" t="n">
-        <v>91543</v>
+        <v>78801</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2694,21 +2689,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2718,13 +2713,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544966</v>
+        <v>545160</v>
       </c>
       <c r="R20" t="n">
-        <v>7198729</v>
+        <v>7198394</v>
       </c>
       <c r="S20" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2748,22 +2743,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På stående död gran med brandljud. På kol</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2905,7 +2905,7 @@
         <v>128933986</v>
       </c>
       <c r="B22" t="n">
-        <v>91557</v>
+        <v>91559</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>128933875</v>
       </c>
       <c r="B23" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>128933164</v>
       </c>
       <c r="B24" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>128933989</v>
       </c>
       <c r="B25" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v>128933165</v>
       </c>
       <c r="B26" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>128933166</v>
       </c>
       <c r="B27" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3566,10 +3566,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128933879</v>
+        <v>128933158</v>
       </c>
       <c r="B28" t="n">
-        <v>88943</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3577,37 +3577,46 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>545153</v>
+        <v>544903</v>
       </c>
       <c r="R28" t="n">
-        <v>7198363</v>
+        <v>7198597</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3631,27 +3640,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:50</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På låga av tall</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3666,12 +3670,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3681,7 +3685,7 @@
         <v>128933982</v>
       </c>
       <c r="B29" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3785,10 +3789,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128933158</v>
+        <v>128933879</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>88945</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3796,46 +3800,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>544903</v>
+        <v>545153</v>
       </c>
       <c r="R30" t="n">
-        <v>7198597</v>
+        <v>7198363</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3859,22 +3854,27 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På låga av tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3889,22 +3889,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128933980</v>
+        <v>128933141</v>
       </c>
       <c r="B31" t="n">
-        <v>91557</v>
+        <v>79044</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3912,37 +3912,41 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>544853</v>
+        <v>545088</v>
       </c>
       <c r="R31" t="n">
-        <v>7198662</v>
+        <v>7198569</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3966,27 +3970,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Väl nedbruten låga av sälg</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4001,12 +4000,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4016,7 +4015,7 @@
         <v>128933961</v>
       </c>
       <c r="B32" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4125,10 +4124,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128933141</v>
+        <v>128933980</v>
       </c>
       <c r="B33" t="n">
-        <v>79043</v>
+        <v>91559</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4136,41 +4135,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>545088</v>
+        <v>544853</v>
       </c>
       <c r="R33" t="n">
-        <v>7198569</v>
+        <v>7198662</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4194,22 +4189,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Väl nedbruten låga av sälg</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4224,19 +4224,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128933130</v>
+        <v>128933156</v>
       </c>
       <c r="B34" t="n">
         <v>57727</v>
@@ -4269,21 +4269,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>545144</v>
+        <v>544879</v>
       </c>
       <c r="R34" t="n">
-        <v>7198419</v>
+        <v>7198601</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4310,22 +4313,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4345,14 +4348,14 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128933213</v>
+        <v>128933130</v>
       </c>
       <c r="B35" t="n">
         <v>57727</v>
@@ -4385,24 +4388,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>544897</v>
+        <v>545144</v>
       </c>
       <c r="R35" t="n">
-        <v>7198529</v>
+        <v>7198419</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4429,27 +4429,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Innanför gränsen, bild finns.</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4469,14 +4464,14 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128933156</v>
+        <v>128933213</v>
       </c>
       <c r="B36" t="n">
         <v>57727</v>
@@ -4523,10 +4518,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>544879</v>
+        <v>544897</v>
       </c>
       <c r="R36" t="n">
-        <v>7198601</v>
+        <v>7198529</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4558,7 +4553,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4568,7 +4563,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Innanför gränsen, bild finns.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4595,57 +4595,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128933147</v>
+        <v>128934001</v>
       </c>
       <c r="B37" t="n">
-        <v>57727</v>
+        <v>80185</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>545204</v>
+        <v>544806</v>
       </c>
       <c r="R37" t="n">
-        <v>7198506</v>
+        <v>7198678</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4674,7 +4665,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4684,7 +4675,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4699,12 +4695,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4827,10 +4823,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128933908</v>
+        <v>128933147</v>
       </c>
       <c r="B39" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4838,37 +4834,46 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>545139</v>
+        <v>545204</v>
       </c>
       <c r="R39" t="n">
-        <v>7198504</v>
+        <v>7198506</v>
       </c>
       <c r="S39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4892,27 +4897,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Två talltitor</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4927,44 +4927,44 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128934001</v>
+        <v>128933908</v>
       </c>
       <c r="B40" t="n">
-        <v>80184</v>
+        <v>57887</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4974,13 +4974,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>544806</v>
+        <v>545139</v>
       </c>
       <c r="R40" t="n">
-        <v>7198678</v>
+        <v>7198504</v>
       </c>
       <c r="S40" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5004,27 +5004,27 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>Två talltitor</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5051,10 +5051,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128933978</v>
+        <v>128933171</v>
       </c>
       <c r="B41" t="n">
-        <v>91557</v>
+        <v>80149</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5062,37 +5062,41 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>544893</v>
+        <v>544807</v>
       </c>
       <c r="R41" t="n">
-        <v>7198604</v>
+        <v>7198685</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5121,7 +5125,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5131,12 +5135,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:39</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På väl nedbruten låga av gran</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5151,22 +5150,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128933124</v>
+        <v>128933978</v>
       </c>
       <c r="B42" t="n">
-        <v>79043</v>
+        <v>91559</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5174,41 +5173,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>545144</v>
+        <v>544893</v>
       </c>
       <c r="R42" t="n">
-        <v>7198368</v>
+        <v>7198604</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5232,22 +5227,27 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På väl nedbruten låga av gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5262,22 +5262,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128933171</v>
+        <v>128933124</v>
       </c>
       <c r="B43" t="n">
-        <v>80148</v>
+        <v>79044</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5285,21 +5285,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5313,10 +5313,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>544807</v>
+        <v>545144</v>
       </c>
       <c r="R43" t="n">
-        <v>7198685</v>
+        <v>7198368</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5343,22 +5343,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5385,10 +5385,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128933154</v>
+        <v>128933163</v>
       </c>
       <c r="B44" t="n">
-        <v>91543</v>
+        <v>79044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5396,21 +5396,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5424,10 +5424,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>544968</v>
+        <v>544832</v>
       </c>
       <c r="R44" t="n">
-        <v>7198730</v>
+        <v>7198667</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5469,12 +5469,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Gran, stor utbredning.</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5501,10 +5496,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128933157</v>
+        <v>128933129</v>
       </c>
       <c r="B45" t="n">
-        <v>80149</v>
+        <v>78801</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5512,21 +5507,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5540,10 +5535,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>544908</v>
+        <v>545158</v>
       </c>
       <c r="R45" t="n">
-        <v>7198602</v>
+        <v>7198403</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5570,27 +5565,27 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Liten kolad stubbe</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5617,10 +5612,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128933129</v>
+        <v>128933157</v>
       </c>
       <c r="B46" t="n">
-        <v>78800</v>
+        <v>80150</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5628,21 +5623,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5656,10 +5651,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>545158</v>
+        <v>544908</v>
       </c>
       <c r="R46" t="n">
-        <v>7198403</v>
+        <v>7198602</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5686,27 +5681,27 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Liten kolad stubbe</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5733,10 +5728,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128933163</v>
+        <v>128933154</v>
       </c>
       <c r="B47" t="n">
-        <v>79043</v>
+        <v>91545</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5744,21 +5739,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5772,10 +5767,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>544832</v>
+        <v>544968</v>
       </c>
       <c r="R47" t="n">
-        <v>7198667</v>
+        <v>7198730</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5807,7 +5802,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5817,7 +5812,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Gran, stor utbredning.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5847,7 +5847,7 @@
         <v>128933139</v>
       </c>
       <c r="B48" t="n">
-        <v>80176</v>
+        <v>80177</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5955,10 +5955,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128933973</v>
+        <v>128933136</v>
       </c>
       <c r="B49" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5966,37 +5966,41 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>544900</v>
+        <v>545109</v>
       </c>
       <c r="R49" t="n">
-        <v>7198597</v>
+        <v>7198551</v>
       </c>
       <c r="S49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6020,27 +6024,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack äldre än 5 år på gran</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6055,12 +6054,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6070,7 +6069,7 @@
         <v>128933966</v>
       </c>
       <c r="B50" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6179,10 +6178,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128933136</v>
+        <v>128933984</v>
       </c>
       <c r="B51" t="n">
-        <v>79043</v>
+        <v>80149</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6190,41 +6189,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>545109</v>
+        <v>544836</v>
       </c>
       <c r="R51" t="n">
-        <v>7198551</v>
+        <v>7198663</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6248,22 +6243,27 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Högt upp på gammal sälg</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6278,22 +6278,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128933984</v>
+        <v>128933973</v>
       </c>
       <c r="B52" t="n">
-        <v>80148</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6301,21 +6301,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6325,10 +6325,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>544836</v>
+        <v>544900</v>
       </c>
       <c r="R52" t="n">
-        <v>7198663</v>
+        <v>7198597</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6370,12 +6370,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Högt upp på gammal sälg</t>
+          <t>Ringhack äldre än 5 år på gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6517,7 +6517,7 @@
         <v>128933947</v>
       </c>
       <c r="B54" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>128933167</v>
       </c>
       <c r="B55" t="n">
-        <v>80052</v>
+        <v>80053</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>128933991</v>
       </c>
       <c r="B56" t="n">
-        <v>80052</v>
+        <v>80053</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 13030-2025 artfynd.xlsx
+++ b/artfynd/A 13030-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128933955</v>
       </c>
       <c r="B2" t="n">
-        <v>92236</v>
+        <v>92240</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1127,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128933155</v>
+        <v>128933902</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,41 +1138,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544955</v>
+        <v>545147</v>
       </c>
       <c r="R6" t="n">
-        <v>7198720</v>
+        <v>7198430</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1196,22 +1192,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gamla ringbarkningar på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1226,22 +1227,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128933902</v>
+        <v>128933155</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1249,37 +1250,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545147</v>
+        <v>544955</v>
       </c>
       <c r="R7" t="n">
-        <v>7198430</v>
+        <v>7198720</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,27 +1308,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:51</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Gamla ringbarkningar på tall</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1338,22 +1338,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128933127</v>
+        <v>128933159</v>
       </c>
       <c r="B8" t="n">
-        <v>78801</v>
+        <v>91847</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1361,21 +1361,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545155</v>
+        <v>544907</v>
       </c>
       <c r="R8" t="n">
-        <v>7198397</v>
+        <v>7198585</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1419,22 +1419,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,10 +1461,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128933159</v>
+        <v>128933127</v>
       </c>
       <c r="B9" t="n">
-        <v>91843</v>
+        <v>78801</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544907</v>
+        <v>545155</v>
       </c>
       <c r="R9" t="n">
-        <v>7198585</v>
+        <v>7198397</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1530,22 +1530,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1686,7 +1686,7 @@
         <v>128933125</v>
       </c>
       <c r="B11" t="n">
-        <v>88945</v>
+        <v>88949</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,48 +1794,52 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128933999</v>
+        <v>128933172</v>
       </c>
       <c r="B12" t="n">
-        <v>80149</v>
+        <v>80185</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544807</v>
+        <v>544801</v>
       </c>
       <c r="R12" t="n">
-        <v>7198677</v>
+        <v>7198690</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1864,7 +1868,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1874,12 +1878,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På gammal sälg i sluttning</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1894,22 +1893,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128933891</v>
+        <v>128933999</v>
       </c>
       <c r="B13" t="n">
-        <v>78801</v>
+        <v>80149</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1917,21 +1916,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1941,10 +1940,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545149</v>
+        <v>544807</v>
       </c>
       <c r="R13" t="n">
-        <v>7198384</v>
+        <v>7198677</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -1971,27 +1970,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På död naken gran med brandljud. På kol.</t>
+          <t>På gammal sälg i sluttning</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2018,52 +2017,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128933172</v>
+        <v>128933891</v>
       </c>
       <c r="B14" t="n">
-        <v>80185</v>
+        <v>78801</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544801</v>
+        <v>545149</v>
       </c>
       <c r="R14" t="n">
-        <v>7198690</v>
+        <v>7198384</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2087,22 +2082,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På död naken gran med brandljud. På kol.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2117,12 +2117,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2132,7 +2132,7 @@
         <v>128933970</v>
       </c>
       <c r="B15" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         <v>128933161</v>
       </c>
       <c r="B18" t="n">
-        <v>91559</v>
+        <v>91563</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         <v>128934084</v>
       </c>
       <c r="B19" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2678,10 +2678,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128933896</v>
+        <v>128933932</v>
       </c>
       <c r="B20" t="n">
-        <v>78801</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2689,21 +2689,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545160</v>
+        <v>545212</v>
       </c>
       <c r="R20" t="n">
-        <v>7198394</v>
+        <v>7198500</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2743,27 +2743,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På stående död gran med brandljud. På kol</t>
+          <t>Ringhack äldre än 5 år på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2790,10 +2790,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128933932</v>
+        <v>128933896</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>78801</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2801,21 +2801,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545212</v>
+        <v>545160</v>
       </c>
       <c r="R21" t="n">
-        <v>7198500</v>
+        <v>7198394</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -2855,27 +2855,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre än 5 år på tall</t>
+          <t>På stående död gran med brandljud. På kol</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2902,10 +2902,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128933986</v>
+        <v>128933164</v>
       </c>
       <c r="B22" t="n">
-        <v>91559</v>
+        <v>80149</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2913,37 +2913,41 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544828</v>
+        <v>544839</v>
       </c>
       <c r="R22" t="n">
-        <v>7198678</v>
+        <v>7198665</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2972,7 +2976,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2982,7 +2986,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2997,12 +3001,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3121,10 +3125,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128933164</v>
+        <v>128933986</v>
       </c>
       <c r="B24" t="n">
-        <v>80149</v>
+        <v>91563</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3132,41 +3136,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544839</v>
+        <v>544828</v>
       </c>
       <c r="R24" t="n">
-        <v>7198665</v>
+        <v>7198678</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3220,12 +3220,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3566,10 +3566,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128933158</v>
+        <v>128933879</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>88949</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3577,46 +3577,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>544903</v>
+        <v>545153</v>
       </c>
       <c r="R28" t="n">
-        <v>7198597</v>
+        <v>7198363</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3640,22 +3631,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På låga av tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3670,12 +3666,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3789,10 +3785,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128933879</v>
+        <v>128933158</v>
       </c>
       <c r="B30" t="n">
-        <v>88945</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3800,37 +3796,46 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>545153</v>
+        <v>544903</v>
       </c>
       <c r="R30" t="n">
-        <v>7198363</v>
+        <v>7198597</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3854,27 +3859,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:50</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På låga av tall</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3889,22 +3889,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128933141</v>
+        <v>128933961</v>
       </c>
       <c r="B31" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3912,41 +3912,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>545088</v>
+        <v>544872</v>
       </c>
       <c r="R31" t="n">
-        <v>7198569</v>
+        <v>7198610</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3970,22 +3966,27 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4000,22 +4001,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128933961</v>
+        <v>128933980</v>
       </c>
       <c r="B32" t="n">
-        <v>80150</v>
+        <v>91563</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4023,21 +4024,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4047,13 +4048,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>544872</v>
+        <v>544853</v>
       </c>
       <c r="R32" t="n">
-        <v>7198610</v>
+        <v>7198662</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4082,7 +4083,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4092,12 +4093,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>Väl nedbruten låga av sälg</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4124,10 +4125,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128933980</v>
+        <v>128933130</v>
       </c>
       <c r="B33" t="n">
-        <v>91559</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4135,37 +4136,46 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>544853</v>
+        <v>545144</v>
       </c>
       <c r="R33" t="n">
-        <v>7198662</v>
+        <v>7198419</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4189,27 +4199,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Väl nedbruten låga av sälg</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4224,19 +4229,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128933156</v>
+        <v>128933213</v>
       </c>
       <c r="B34" t="n">
         <v>57727</v>
@@ -4283,10 +4288,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>544879</v>
+        <v>544897</v>
       </c>
       <c r="R34" t="n">
-        <v>7198601</v>
+        <v>7198529</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4318,7 +4323,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4328,7 +4333,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Innanför gränsen, bild finns.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4355,7 +4365,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128933130</v>
+        <v>128933156</v>
       </c>
       <c r="B35" t="n">
         <v>57727</v>
@@ -4388,21 +4398,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>545144</v>
+        <v>544879</v>
       </c>
       <c r="R35" t="n">
-        <v>7198419</v>
+        <v>7198601</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4429,22 +4442,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4464,17 +4477,17 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128933213</v>
+        <v>128933141</v>
       </c>
       <c r="B36" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4482,21 +4495,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4504,24 +4517,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>544897</v>
+        <v>545088</v>
       </c>
       <c r="R36" t="n">
-        <v>7198529</v>
+        <v>7198569</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4548,27 +4553,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Innanför gränsen, bild finns.</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4707,7 +4707,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128933212</v>
+        <v>128933147</v>
       </c>
       <c r="B38" t="n">
         <v>57727</v>
@@ -4751,10 +4751,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>544911</v>
+        <v>545204</v>
       </c>
       <c r="R38" t="n">
-        <v>7198620</v>
+        <v>7198506</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4823,7 +4823,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128933147</v>
+        <v>128933212</v>
       </c>
       <c r="B39" t="n">
         <v>57727</v>
@@ -4867,10 +4867,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>545204</v>
+        <v>544911</v>
       </c>
       <c r="R39" t="n">
-        <v>7198506</v>
+        <v>7198620</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4912,7 +4912,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5051,10 +5051,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128933171</v>
+        <v>128933978</v>
       </c>
       <c r="B41" t="n">
-        <v>80149</v>
+        <v>91563</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5062,41 +5062,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>544807</v>
+        <v>544893</v>
       </c>
       <c r="R41" t="n">
-        <v>7198685</v>
+        <v>7198604</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5125,7 +5121,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5135,7 +5131,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På väl nedbruten låga av gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5150,22 +5151,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128933978</v>
+        <v>128933124</v>
       </c>
       <c r="B42" t="n">
-        <v>91559</v>
+        <v>79044</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5173,37 +5174,41 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>544893</v>
+        <v>545144</v>
       </c>
       <c r="R42" t="n">
-        <v>7198604</v>
+        <v>7198368</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5227,27 +5232,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:39</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På väl nedbruten låga av gran</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5262,22 +5262,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128933124</v>
+        <v>128933171</v>
       </c>
       <c r="B43" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5285,21 +5285,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5313,10 +5313,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>545144</v>
+        <v>544807</v>
       </c>
       <c r="R43" t="n">
-        <v>7198368</v>
+        <v>7198685</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5343,22 +5343,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5385,10 +5385,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128933163</v>
+        <v>128933157</v>
       </c>
       <c r="B44" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5396,21 +5396,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5424,10 +5424,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>544832</v>
+        <v>544908</v>
       </c>
       <c r="R44" t="n">
-        <v>7198667</v>
+        <v>7198602</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5469,7 +5469,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5496,10 +5501,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128933129</v>
+        <v>128933154</v>
       </c>
       <c r="B45" t="n">
-        <v>78801</v>
+        <v>91549</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5507,21 +5512,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5535,10 +5540,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>545158</v>
+        <v>544968</v>
       </c>
       <c r="R45" t="n">
-        <v>7198403</v>
+        <v>7198730</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5565,27 +5570,27 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Liten kolad stubbe</t>
+          <t>Gran, stor utbredning.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5612,10 +5617,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128933157</v>
+        <v>128933163</v>
       </c>
       <c r="B46" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5623,21 +5628,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5651,10 +5656,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>544908</v>
+        <v>544832</v>
       </c>
       <c r="R46" t="n">
-        <v>7198602</v>
+        <v>7198667</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5686,7 +5691,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5696,12 +5701,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Sälg</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5728,10 +5728,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128933154</v>
+        <v>128933129</v>
       </c>
       <c r="B47" t="n">
-        <v>91545</v>
+        <v>78801</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5739,21 +5739,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>544968</v>
+        <v>545158</v>
       </c>
       <c r="R47" t="n">
-        <v>7198730</v>
+        <v>7198403</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5797,27 +5797,27 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Gran, stor utbredning.</t>
+          <t>Liten kolad stubbe</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5955,10 +5955,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128933136</v>
+        <v>128933984</v>
       </c>
       <c r="B49" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5966,41 +5966,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>545109</v>
+        <v>544836</v>
       </c>
       <c r="R49" t="n">
-        <v>7198551</v>
+        <v>7198663</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6024,22 +6020,27 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Högt upp på gammal sälg</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6054,22 +6055,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128933966</v>
+        <v>128933136</v>
       </c>
       <c r="B50" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6077,37 +6078,41 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>544905</v>
+        <v>545109</v>
       </c>
       <c r="R50" t="n">
-        <v>7198603</v>
+        <v>7198551</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6131,27 +6136,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6166,22 +6166,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128933984</v>
+        <v>128933870</v>
       </c>
       <c r="B51" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6189,21 +6189,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6213,10 +6213,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>544836</v>
+        <v>545136</v>
       </c>
       <c r="R51" t="n">
-        <v>7198663</v>
+        <v>7198363</v>
       </c>
       <c r="S51" t="n">
         <v>4</v>
@@ -6243,27 +6243,27 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Högt upp på gammal sälg</t>
+          <t>Nya ringbarkningar från tretåig hackspett på gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6402,10 +6402,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128933870</v>
+        <v>128933966</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6413,21 +6413,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6437,13 +6437,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>545136</v>
+        <v>544905</v>
       </c>
       <c r="R53" t="n">
-        <v>7198363</v>
+        <v>7198603</v>
       </c>
       <c r="S53" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6467,27 +6467,27 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Nya ringbarkningar från tretåig hackspett på gran.</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6514,10 +6514,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128933947</v>
+        <v>128933167</v>
       </c>
       <c r="B54" t="n">
-        <v>91509</v>
+        <v>80053</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6525,37 +6525,41 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5447</v>
+        <v>6456</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>544971</v>
+        <v>544823</v>
       </c>
       <c r="R54" t="n">
-        <v>7198722</v>
+        <v>7198695</v>
       </c>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6584,7 +6588,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6594,7 +6598,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Asp</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6609,22 +6618,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128933167</v>
+        <v>128933947</v>
       </c>
       <c r="B55" t="n">
-        <v>80053</v>
+        <v>91513</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6632,41 +6641,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>544823</v>
+        <v>544971</v>
       </c>
       <c r="R55" t="n">
-        <v>7198695</v>
+        <v>7198722</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6695,7 +6700,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6705,12 +6710,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:14</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Asp</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6725,12 +6725,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>

--- a/artfynd/A 13030-2025 artfynd.xlsx
+++ b/artfynd/A 13030-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128933955</v>
       </c>
       <c r="B2" t="n">
-        <v>92240</v>
+        <v>92241</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1127,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128933902</v>
+        <v>128933155</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,37 +1138,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545147</v>
+        <v>544955</v>
       </c>
       <c r="R6" t="n">
-        <v>7198430</v>
+        <v>7198720</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1192,27 +1196,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:51</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gamla ringbarkningar på tall</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1227,22 +1226,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128933155</v>
+        <v>128933902</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1250,41 +1249,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544955</v>
+        <v>545147</v>
       </c>
       <c r="R7" t="n">
-        <v>7198720</v>
+        <v>7198430</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1308,22 +1303,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gamla ringbarkningar på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1338,22 +1338,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128933159</v>
+        <v>128933127</v>
       </c>
       <c r="B8" t="n">
-        <v>91847</v>
+        <v>78801</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1361,21 +1361,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544907</v>
+        <v>545155</v>
       </c>
       <c r="R8" t="n">
-        <v>7198585</v>
+        <v>7198397</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1419,22 +1419,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,10 +1461,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128933127</v>
+        <v>128933159</v>
       </c>
       <c r="B9" t="n">
-        <v>78801</v>
+        <v>91848</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545155</v>
+        <v>544907</v>
       </c>
       <c r="R9" t="n">
-        <v>7198397</v>
+        <v>7198585</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1530,22 +1530,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1686,7 +1686,7 @@
         <v>128933125</v>
       </c>
       <c r="B11" t="n">
-        <v>88949</v>
+        <v>88950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,52 +1794,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128933172</v>
+        <v>128933999</v>
       </c>
       <c r="B12" t="n">
-        <v>80185</v>
+        <v>80149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544801</v>
+        <v>544807</v>
       </c>
       <c r="R12" t="n">
-        <v>7198690</v>
+        <v>7198677</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1868,7 +1864,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1878,7 +1874,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På gammal sälg i sluttning</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1893,22 +1894,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128933999</v>
+        <v>128933891</v>
       </c>
       <c r="B13" t="n">
-        <v>80149</v>
+        <v>78801</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1916,21 +1917,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1940,10 +1941,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544807</v>
+        <v>545149</v>
       </c>
       <c r="R13" t="n">
-        <v>7198677</v>
+        <v>7198384</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -1970,27 +1971,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gammal sälg i sluttning</t>
+          <t>På död naken gran med brandljud. På kol.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2017,48 +2018,52 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128933891</v>
+        <v>128933172</v>
       </c>
       <c r="B14" t="n">
-        <v>78801</v>
+        <v>80185</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545149</v>
+        <v>544801</v>
       </c>
       <c r="R14" t="n">
-        <v>7198384</v>
+        <v>7198690</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2082,27 +2087,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På död naken gran med brandljud. På kol.</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2117,12 +2117,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2132,7 +2132,7 @@
         <v>128933970</v>
       </c>
       <c r="B15" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2460,10 +2460,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128933161</v>
+        <v>128933932</v>
       </c>
       <c r="B18" t="n">
-        <v>91563</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2471,41 +2471,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544891</v>
+        <v>545212</v>
       </c>
       <c r="R18" t="n">
-        <v>7198608</v>
+        <v>7198500</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2534,7 +2530,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2544,7 +2540,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre än 5 år på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2559,22 +2560,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128934084</v>
+        <v>128933161</v>
       </c>
       <c r="B19" t="n">
-        <v>91549</v>
+        <v>91564</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2582,37 +2583,41 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544966</v>
+        <v>544891</v>
       </c>
       <c r="R19" t="n">
-        <v>7198729</v>
+        <v>7198608</v>
       </c>
       <c r="S19" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2641,7 +2646,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2651,7 +2656,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2666,22 +2671,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128933932</v>
+        <v>128934084</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>91550</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2689,21 +2694,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2713,13 +2718,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545212</v>
+        <v>544966</v>
       </c>
       <c r="R20" t="n">
-        <v>7198500</v>
+        <v>7198729</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2748,7 +2753,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2758,12 +2763,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack äldre än 5 år på tall</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3128,7 +3128,7 @@
         <v>128933986</v>
       </c>
       <c r="B24" t="n">
-        <v>91563</v>
+        <v>91564</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3337,7 +3337,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3566,10 +3566,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128933879</v>
+        <v>128933158</v>
       </c>
       <c r="B28" t="n">
-        <v>88949</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3577,37 +3577,46 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>545153</v>
+        <v>544903</v>
       </c>
       <c r="R28" t="n">
-        <v>7198363</v>
+        <v>7198597</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3631,27 +3640,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:50</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På låga av tall</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3666,12 +3670,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3778,17 +3782,17 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128933158</v>
+        <v>128933879</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>88950</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3796,46 +3800,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>544903</v>
+        <v>545153</v>
       </c>
       <c r="R30" t="n">
-        <v>7198597</v>
+        <v>7198363</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3859,22 +3854,27 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På låga av tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3889,12 +3889,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4016,7 +4016,7 @@
         <v>128933980</v>
       </c>
       <c r="B32" t="n">
-        <v>91563</v>
+        <v>91564</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4595,32 +4595,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128934001</v>
+        <v>128933908</v>
       </c>
       <c r="B37" t="n">
-        <v>80185</v>
+        <v>57887</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4630,13 +4630,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>544806</v>
+        <v>545139</v>
       </c>
       <c r="R37" t="n">
-        <v>7198678</v>
+        <v>7198504</v>
       </c>
       <c r="S37" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4660,27 +4660,27 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>Två talltitor</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4707,57 +4707,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128933147</v>
+        <v>128934001</v>
       </c>
       <c r="B38" t="n">
-        <v>57727</v>
+        <v>80185</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>545204</v>
+        <v>544806</v>
       </c>
       <c r="R38" t="n">
-        <v>7198506</v>
+        <v>7198678</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4786,7 +4777,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4796,7 +4787,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4811,19 +4807,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128933212</v>
+        <v>128933147</v>
       </c>
       <c r="B39" t="n">
         <v>57727</v>
@@ -4867,10 +4863,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>544911</v>
+        <v>545204</v>
       </c>
       <c r="R39" t="n">
-        <v>7198620</v>
+        <v>7198506</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4902,7 +4898,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4912,7 +4908,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4939,10 +4935,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128933908</v>
+        <v>128933212</v>
       </c>
       <c r="B40" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4950,37 +4946,46 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>545139</v>
+        <v>544911</v>
       </c>
       <c r="R40" t="n">
-        <v>7198504</v>
+        <v>7198620</v>
       </c>
       <c r="S40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5004,27 +5009,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Två talltitor</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5039,12 +5039,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5054,7 +5054,7 @@
         <v>128933978</v>
       </c>
       <c r="B41" t="n">
-        <v>91563</v>
+        <v>91564</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5504,7 +5504,7 @@
         <v>128933154</v>
       </c>
       <c r="B45" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5955,10 +5955,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128933984</v>
+        <v>128933136</v>
       </c>
       <c r="B49" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5966,37 +5966,41 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>544836</v>
+        <v>545109</v>
       </c>
       <c r="R49" t="n">
-        <v>7198663</v>
+        <v>7198551</v>
       </c>
       <c r="S49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6020,27 +6024,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:56</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Högt upp på gammal sälg</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6055,22 +6054,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128933136</v>
+        <v>128933966</v>
       </c>
       <c r="B50" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6078,41 +6077,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>545109</v>
+        <v>544905</v>
       </c>
       <c r="R50" t="n">
-        <v>7198551</v>
+        <v>7198603</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6136,22 +6131,27 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6166,22 +6166,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128933870</v>
+        <v>128933984</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6189,21 +6189,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6213,10 +6213,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>545136</v>
+        <v>544836</v>
       </c>
       <c r="R51" t="n">
-        <v>7198363</v>
+        <v>7198663</v>
       </c>
       <c r="S51" t="n">
         <v>4</v>
@@ -6243,27 +6243,27 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Nya ringbarkningar från tretåig hackspett på gran.</t>
+          <t>Högt upp på gammal sälg</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6283,14 +6283,14 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128933973</v>
+        <v>128933870</v>
       </c>
       <c r="B52" t="n">
         <v>57727</v>
@@ -6325,10 +6325,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>544900</v>
+        <v>545136</v>
       </c>
       <c r="R52" t="n">
-        <v>7198597</v>
+        <v>7198363</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6355,27 +6355,27 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack äldre än 5 år på gran</t>
+          <t>Nya ringbarkningar från tretåig hackspett på gran.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6402,10 +6402,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128933966</v>
+        <v>128933973</v>
       </c>
       <c r="B53" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6413,21 +6413,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6437,13 +6437,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>544905</v>
+        <v>544900</v>
       </c>
       <c r="R53" t="n">
-        <v>7198603</v>
+        <v>7198597</v>
       </c>
       <c r="S53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6482,12 +6482,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>Ringhack äldre än 5 år på gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6507,17 +6507,17 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128933167</v>
+        <v>128933947</v>
       </c>
       <c r="B54" t="n">
-        <v>80053</v>
+        <v>91514</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6525,41 +6525,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>544823</v>
+        <v>544971</v>
       </c>
       <c r="R54" t="n">
-        <v>7198695</v>
+        <v>7198722</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6588,7 +6584,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6598,12 +6594,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:14</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Asp</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6618,22 +6609,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128933947</v>
+        <v>128933167</v>
       </c>
       <c r="B55" t="n">
-        <v>91513</v>
+        <v>80053</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6641,37 +6632,41 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>6456</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>544971</v>
+        <v>544823</v>
       </c>
       <c r="R55" t="n">
-        <v>7198722</v>
+        <v>7198695</v>
       </c>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6700,7 +6695,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6710,7 +6705,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Asp</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6725,12 +6725,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>

--- a/artfynd/A 13030-2025 artfynd.xlsx
+++ b/artfynd/A 13030-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AY69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128933955</v>
+        <v>128933125</v>
       </c>
       <c r="B2" t="n">
-        <v>92241</v>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>898</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544957</v>
+        <v>545148</v>
       </c>
       <c r="R2" t="n">
-        <v>7198698</v>
+        <v>7198360</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,27 +744,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:44</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +774,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128933901</v>
+        <v>128933879</v>
       </c>
       <c r="B3" t="n">
-        <v>83012</v>
+        <v>89292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545154</v>
+        <v>545153</v>
       </c>
       <c r="R3" t="n">
-        <v>7198397</v>
+        <v>7198363</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -857,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +866,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På bark av gammal gran</t>
+          <t>På låga av tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128933958</v>
+        <v>128933159</v>
       </c>
       <c r="B4" t="n">
-        <v>80149</v>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,37 +909,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544871</v>
+        <v>544907</v>
       </c>
       <c r="R4" t="n">
-        <v>7198612</v>
+        <v>7198585</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,7 +972,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,12 +982,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,22 +997,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128933126</v>
+        <v>128933970</v>
       </c>
       <c r="B5" t="n">
-        <v>78801</v>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,41 +1020,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545150</v>
+        <v>544900</v>
       </c>
       <c r="R5" t="n">
-        <v>7198391</v>
+        <v>7198605</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,27 +1074,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Kolad granved</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,64 +1109,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128933155</v>
+        <v>128933955</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>92605</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>898</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544955</v>
+        <v>544957</v>
       </c>
       <c r="R6" t="n">
-        <v>7198720</v>
+        <v>7198698</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1201,7 +1191,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1211,7 +1201,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1226,22 +1221,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128933902</v>
+        <v>128933154</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1249,37 +1244,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545147</v>
+        <v>544968</v>
       </c>
       <c r="R7" t="n">
-        <v>7198430</v>
+        <v>7198730</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,27 +1302,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Gamla ringbarkningar på tall</t>
+          <t>Gran, stor utbredning.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1338,22 +1337,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128933127</v>
+        <v>128934084</v>
       </c>
       <c r="B8" t="n">
-        <v>78801</v>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1361,41 +1360,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545155</v>
+        <v>544966</v>
       </c>
       <c r="R8" t="n">
-        <v>7198397</v>
+        <v>7198729</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1419,22 +1414,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,44 +1444,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128933159</v>
+        <v>128933161</v>
       </c>
       <c r="B9" t="n">
-        <v>91848</v>
+        <v>91923</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1500,10 +1495,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544907</v>
+        <v>544891</v>
       </c>
       <c r="R9" t="n">
-        <v>7198585</v>
+        <v>7198608</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1535,7 +1530,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1545,7 +1540,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1572,52 +1567,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128933131</v>
+        <v>128933978</v>
       </c>
       <c r="B10" t="n">
-        <v>80177</v>
+        <v>91923</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6461</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545111</v>
+        <v>544893</v>
       </c>
       <c r="R10" t="n">
-        <v>7198467</v>
+        <v>7198604</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1641,22 +1632,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På väl nedbruten låga av gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,64 +1667,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128933125</v>
+        <v>128933980</v>
       </c>
       <c r="B11" t="n">
-        <v>88950</v>
+        <v>91923</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>510</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545148</v>
+        <v>544853</v>
       </c>
       <c r="R11" t="n">
-        <v>7198360</v>
+        <v>7198662</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1752,22 +1744,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Väl nedbruten låga av sälg</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1782,44 +1779,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128933999</v>
+        <v>128933986</v>
       </c>
       <c r="B12" t="n">
-        <v>80149</v>
+        <v>91923</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1829,13 +1826,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544807</v>
+        <v>544828</v>
       </c>
       <c r="R12" t="n">
-        <v>7198677</v>
+        <v>7198678</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1864,7 +1861,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1874,12 +1871,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På gammal sälg i sluttning</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1899,17 +1891,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128933891</v>
+        <v>128933134</v>
       </c>
       <c r="B13" t="n">
-        <v>78801</v>
+        <v>83173</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1917,37 +1909,41 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545149</v>
+        <v>545072</v>
       </c>
       <c r="R13" t="n">
-        <v>7198384</v>
+        <v>7198517</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1976,7 +1972,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1986,12 +1982,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På död naken gran med brandljud. På kol.</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2006,64 +1997,60 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128933172</v>
+        <v>128933910</v>
       </c>
       <c r="B14" t="n">
-        <v>80185</v>
+        <v>83173</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544801</v>
+        <v>545073</v>
       </c>
       <c r="R14" t="n">
-        <v>7198690</v>
+        <v>7198519</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2087,22 +2074,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2117,22 +2109,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128933970</v>
+        <v>128934012</v>
       </c>
       <c r="B15" t="n">
-        <v>91848</v>
+        <v>83173</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2140,21 +2132,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2164,13 +2156,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544900</v>
+        <v>544799</v>
       </c>
       <c r="R15" t="n">
-        <v>7198605</v>
+        <v>7198726</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2199,7 +2191,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2209,12 +2201,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På gammal granlåga</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2241,10 +2228,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128933904</v>
+        <v>128933157</v>
       </c>
       <c r="B16" t="n">
-        <v>78447</v>
+        <v>80433</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2252,37 +2239,41 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6437</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>545138</v>
+        <v>544908</v>
       </c>
       <c r="R16" t="n">
-        <v>7198414</v>
+        <v>7198602</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2306,22 +2297,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2336,22 +2332,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128933968</v>
+        <v>128933165</v>
       </c>
       <c r="B17" t="n">
-        <v>80149</v>
+        <v>80433</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2359,37 +2355,41 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544899</v>
+        <v>544837</v>
       </c>
       <c r="R17" t="n">
-        <v>7198606</v>
+        <v>7198665</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2428,12 +2428,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:27</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Högt upp på gammal sälg</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2448,22 +2443,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128933932</v>
+        <v>128933961</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>80433</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2471,21 +2466,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2495,13 +2490,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545212</v>
+        <v>544872</v>
       </c>
       <c r="R18" t="n">
-        <v>7198500</v>
+        <v>7198610</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2530,7 +2525,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2540,12 +2535,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre än 5 år på tall</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2572,10 +2567,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128933161</v>
+        <v>128933966</v>
       </c>
       <c r="B19" t="n">
-        <v>91564</v>
+        <v>80433</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2583,41 +2578,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1204</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544891</v>
+        <v>544905</v>
       </c>
       <c r="R19" t="n">
-        <v>7198608</v>
+        <v>7198603</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2646,7 +2637,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2656,7 +2647,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2671,22 +2667,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128934084</v>
+        <v>128933982</v>
       </c>
       <c r="B20" t="n">
-        <v>91550</v>
+        <v>80433</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2694,21 +2690,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2718,13 +2714,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544966</v>
+        <v>544845</v>
       </c>
       <c r="R20" t="n">
-        <v>7198729</v>
+        <v>7198663</v>
       </c>
       <c r="S20" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2753,7 +2749,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2763,7 +2759,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2783,17 +2779,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128933896</v>
+        <v>128933989</v>
       </c>
       <c r="B21" t="n">
-        <v>78801</v>
+        <v>80433</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2801,21 +2797,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2825,10 +2821,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545160</v>
+        <v>544830</v>
       </c>
       <c r="R21" t="n">
-        <v>7198394</v>
+        <v>7198678</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -2855,27 +2851,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På stående död gran med brandljud. På kol</t>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2902,10 +2898,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128933164</v>
+        <v>128934090</v>
       </c>
       <c r="B22" t="n">
-        <v>80149</v>
+        <v>80433</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2913,41 +2909,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544839</v>
+        <v>544877</v>
       </c>
       <c r="R22" t="n">
-        <v>7198665</v>
+        <v>7198514</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2976,7 +2968,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2986,7 +2978,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3001,44 +2993,44 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128933875</v>
+        <v>128933947</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>91872</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3048,13 +3040,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>545139</v>
+        <v>544971</v>
       </c>
       <c r="R23" t="n">
-        <v>7198365</v>
+        <v>7198722</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3078,27 +3070,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:41</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Mycket god förekomst</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3125,48 +3112,52 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128933986</v>
+        <v>128933124</v>
       </c>
       <c r="B24" t="n">
-        <v>91564</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544828</v>
+        <v>545144</v>
       </c>
       <c r="R24" t="n">
-        <v>7198678</v>
+        <v>7198368</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3190,22 +3181,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3220,60 +3211,64 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128933989</v>
+        <v>128933136</v>
       </c>
       <c r="B25" t="n">
-        <v>80150</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544830</v>
+        <v>545109</v>
       </c>
       <c r="R25" t="n">
-        <v>7198678</v>
+        <v>7198551</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3297,27 +3292,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På sälglåga</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3332,44 +3322,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128933165</v>
+        <v>128933141</v>
       </c>
       <c r="B26" t="n">
-        <v>80150</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3383,10 +3373,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>544837</v>
+        <v>545088</v>
       </c>
       <c r="R26" t="n">
-        <v>7198665</v>
+        <v>7198569</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3413,22 +3403,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3455,32 +3445,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128933166</v>
+        <v>128933155</v>
       </c>
       <c r="B27" t="n">
-        <v>80149</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3494,10 +3484,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>544839</v>
+        <v>544955</v>
       </c>
       <c r="R27" t="n">
-        <v>7198683</v>
+        <v>7198720</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3529,7 +3519,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3539,7 +3529,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3566,32 +3556,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128933158</v>
+        <v>128933163</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3599,21 +3589,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>544903</v>
+        <v>544832</v>
       </c>
       <c r="R28" t="n">
-        <v>7198597</v>
+        <v>7198667</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3645,7 +3630,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3655,7 +3640,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3682,48 +3667,52 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128933982</v>
+        <v>128933175</v>
       </c>
       <c r="B29" t="n">
-        <v>80150</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544845</v>
+        <v>544805</v>
       </c>
       <c r="R29" t="n">
-        <v>7198663</v>
+        <v>7198727</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3752,7 +3741,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3762,7 +3751,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3777,44 +3766,44 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128933879</v>
+        <v>128933875</v>
       </c>
       <c r="B30" t="n">
-        <v>88950</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3824,10 +3813,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>545153</v>
+        <v>545139</v>
       </c>
       <c r="R30" t="n">
-        <v>7198363</v>
+        <v>7198365</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -3859,7 +3848,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3869,12 +3858,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På låga av tall</t>
+          <t>Mycket god förekomst</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3901,32 +3890,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128933961</v>
+        <v>128934010</v>
       </c>
       <c r="B31" t="n">
-        <v>80150</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3936,13 +3925,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>544872</v>
+        <v>544797</v>
       </c>
       <c r="R31" t="n">
-        <v>7198610</v>
+        <v>7198723</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3971,7 +3960,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3981,12 +3970,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4013,10 +3997,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128933980</v>
+        <v>128933173</v>
       </c>
       <c r="B32" t="n">
-        <v>91564</v>
+        <v>78730</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4024,37 +4008,41 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1204</v>
+        <v>6437</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>544853</v>
+        <v>544801</v>
       </c>
       <c r="R32" t="n">
-        <v>7198662</v>
+        <v>7198738</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4083,7 +4071,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4093,12 +4081,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Väl nedbruten låga av sälg</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4113,22 +4096,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128933130</v>
+        <v>128933904</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>78730</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4136,46 +4119,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>545144</v>
+        <v>545138</v>
       </c>
       <c r="R33" t="n">
-        <v>7198419</v>
+        <v>7198414</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4204,7 +4178,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4214,7 +4188,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4229,22 +4203,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128933213</v>
+        <v>128934004</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>78730</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4252,49 +4226,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>544897</v>
+        <v>544803</v>
       </c>
       <c r="R34" t="n">
-        <v>7198529</v>
+        <v>7198728</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4323,7 +4285,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4333,12 +4295,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Innanför gränsen, bild finns.</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4353,7 +4310,7 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
@@ -4365,10 +4322,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128933156</v>
+        <v>128933901</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>83307</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4376,49 +4333,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>544879</v>
+        <v>545154</v>
       </c>
       <c r="R35" t="n">
-        <v>7198601</v>
+        <v>7198397</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4442,22 +4387,27 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På bark av gammal gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4472,7 +4422,7 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
@@ -4484,10 +4434,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128933141</v>
+        <v>128933126</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>79084</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4495,21 +4445,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4523,10 +4473,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>545088</v>
+        <v>545150</v>
       </c>
       <c r="R36" t="n">
-        <v>7198569</v>
+        <v>7198391</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4558,7 +4508,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4568,7 +4518,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Kolad granved</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4595,10 +4550,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128933908</v>
+        <v>128933127</v>
       </c>
       <c r="B37" t="n">
-        <v>57887</v>
+        <v>79084</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4606,37 +4561,41 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>545139</v>
+        <v>545155</v>
       </c>
       <c r="R37" t="n">
-        <v>7198504</v>
+        <v>7198397</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4665,7 +4624,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4675,12 +4634,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Två talltitor</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4695,60 +4649,64 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128934001</v>
+        <v>128933129</v>
       </c>
       <c r="B38" t="n">
-        <v>80185</v>
+        <v>79084</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6464</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>544806</v>
+        <v>545158</v>
       </c>
       <c r="R38" t="n">
-        <v>7198678</v>
+        <v>7198403</v>
       </c>
       <c r="S38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4772,27 +4730,27 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>Liten kolad stubbe</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4807,22 +4765,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128933147</v>
+        <v>128933174</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>79084</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4830,21 +4788,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4852,21 +4810,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>545204</v>
+        <v>544798</v>
       </c>
       <c r="R39" t="n">
-        <v>7198506</v>
+        <v>7198737</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4898,7 +4851,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4908,7 +4861,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4935,10 +4888,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128933212</v>
+        <v>128933891</v>
       </c>
       <c r="B40" t="n">
-        <v>57727</v>
+        <v>79084</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4946,46 +4899,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>544911</v>
+        <v>545149</v>
       </c>
       <c r="R40" t="n">
-        <v>7198620</v>
+        <v>7198384</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5009,22 +4953,27 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På död naken gran med brandljud. På kol.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5039,22 +4988,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128933978</v>
+        <v>128933896</v>
       </c>
       <c r="B41" t="n">
-        <v>91564</v>
+        <v>79084</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5062,21 +5011,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1204</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5086,10 +5035,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>544893</v>
+        <v>545160</v>
       </c>
       <c r="R41" t="n">
-        <v>7198604</v>
+        <v>7198394</v>
       </c>
       <c r="S41" t="n">
         <v>4</v>
@@ -5116,27 +5065,27 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På väl nedbruten låga av gran</t>
+          <t>På stående död gran med brandljud. På kol</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5156,17 +5105,17 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128933124</v>
+        <v>128934007</v>
       </c>
       <c r="B42" t="n">
-        <v>79044</v>
+        <v>79084</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5174,41 +5123,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>545144</v>
+        <v>544803</v>
       </c>
       <c r="R42" t="n">
-        <v>7198368</v>
+        <v>7198728</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5232,22 +5177,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5262,44 +5207,44 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128933171</v>
+        <v>128933167</v>
       </c>
       <c r="B43" t="n">
-        <v>80149</v>
+        <v>80336</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5313,10 +5258,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>544807</v>
+        <v>544823</v>
       </c>
       <c r="R43" t="n">
-        <v>7198685</v>
+        <v>7198695</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5348,7 +5293,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5358,7 +5303,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Asp</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5385,52 +5335,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128933157</v>
+        <v>128933991</v>
       </c>
       <c r="B44" t="n">
-        <v>80150</v>
+        <v>80336</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>544908</v>
+        <v>544826</v>
       </c>
       <c r="R44" t="n">
-        <v>7198602</v>
+        <v>7198694</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5459,7 +5405,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5469,12 +5415,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5489,22 +5435,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128933154</v>
+        <v>128933164</v>
       </c>
       <c r="B45" t="n">
-        <v>91550</v>
+        <v>80432</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5512,21 +5458,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5540,10 +5486,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>544968</v>
+        <v>544839</v>
       </c>
       <c r="R45" t="n">
-        <v>7198730</v>
+        <v>7198665</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5575,7 +5521,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5585,12 +5531,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Gran, stor utbredning.</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5617,10 +5558,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128933163</v>
+        <v>128933166</v>
       </c>
       <c r="B46" t="n">
-        <v>79044</v>
+        <v>80432</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5628,21 +5569,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5656,10 +5597,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>544832</v>
+        <v>544839</v>
       </c>
       <c r="R46" t="n">
-        <v>7198667</v>
+        <v>7198683</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5691,7 +5632,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5701,7 +5642,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5728,10 +5669,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128933129</v>
+        <v>128933171</v>
       </c>
       <c r="B47" t="n">
-        <v>78801</v>
+        <v>80432</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5739,21 +5680,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5767,10 +5708,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>545158</v>
+        <v>544807</v>
       </c>
       <c r="R47" t="n">
-        <v>7198403</v>
+        <v>7198685</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5797,27 +5738,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Liten kolad stubbe</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5844,52 +5780,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128933139</v>
+        <v>128933958</v>
       </c>
       <c r="B48" t="n">
-        <v>80177</v>
+        <v>80432</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>545089</v>
+        <v>544871</v>
       </c>
       <c r="R48" t="n">
-        <v>7198569</v>
+        <v>7198612</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5913,22 +5845,27 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5943,22 +5880,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128933136</v>
+        <v>128933968</v>
       </c>
       <c r="B49" t="n">
-        <v>79044</v>
+        <v>80432</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5966,41 +5903,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>545109</v>
+        <v>544899</v>
       </c>
       <c r="R49" t="n">
-        <v>7198551</v>
+        <v>7198606</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6024,22 +5957,27 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Högt upp på gammal sälg</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6054,22 +5992,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Edvin Strandberg</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128933966</v>
+        <v>128933984</v>
       </c>
       <c r="B50" t="n">
-        <v>80150</v>
+        <v>80432</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6077,21 +6015,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6101,13 +6039,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>544905</v>
+        <v>544836</v>
       </c>
       <c r="R50" t="n">
-        <v>7198603</v>
+        <v>7198663</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6136,7 +6074,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6146,12 +6084,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>Högt upp på gammal sälg</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6178,10 +6116,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128933984</v>
+        <v>128933999</v>
       </c>
       <c r="B51" t="n">
-        <v>80149</v>
+        <v>80432</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6213,10 +6151,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>544836</v>
+        <v>544807</v>
       </c>
       <c r="R51" t="n">
-        <v>7198663</v>
+        <v>7198677</v>
       </c>
       <c r="S51" t="n">
         <v>4</v>
@@ -6248,7 +6186,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6258,12 +6196,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Högt upp på gammal sälg</t>
+          <t>På gammal sälg i sluttning</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6283,17 +6221,17 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128933870</v>
+        <v>128934092</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>80432</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6301,21 +6239,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6325,10 +6263,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>545136</v>
+        <v>544877</v>
       </c>
       <c r="R52" t="n">
-        <v>7198363</v>
+        <v>7198514</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6355,27 +6293,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Nya ringbarkningar från tretåig hackspett på gran.</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6402,48 +6335,52 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128933973</v>
+        <v>128933131</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>80460</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>544900</v>
+        <v>545111</v>
       </c>
       <c r="R53" t="n">
-        <v>7198597</v>
+        <v>7198467</v>
       </c>
       <c r="S53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6467,27 +6404,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack äldre än 5 år på gran</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6502,22 +6434,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128933947</v>
+        <v>128933139</v>
       </c>
       <c r="B54" t="n">
-        <v>91514</v>
+        <v>80460</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6525,37 +6457,41 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5447</v>
+        <v>6461</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>544971</v>
+        <v>545089</v>
       </c>
       <c r="R54" t="n">
-        <v>7198722</v>
+        <v>7198569</v>
       </c>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6579,22 +6515,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6609,22 +6545,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>David Kenger</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+          <t>Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128933167</v>
+        <v>128933172</v>
       </c>
       <c r="B55" t="n">
-        <v>80053</v>
+        <v>80468</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6632,21 +6568,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6456</v>
+        <v>6464</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6660,10 +6596,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>544823</v>
+        <v>544801</v>
       </c>
       <c r="R55" t="n">
-        <v>7198695</v>
+        <v>7198690</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6695,7 +6631,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6705,12 +6641,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:14</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Asp</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6737,10 +6668,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128933991</v>
+        <v>128934001</v>
       </c>
       <c r="B56" t="n">
-        <v>80053</v>
+        <v>80468</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6748,21 +6679,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6456</v>
+        <v>6464</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6772,13 +6703,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>544826</v>
+        <v>544806</v>
       </c>
       <c r="R56" t="n">
-        <v>7198694</v>
+        <v>7198678</v>
       </c>
       <c r="S56" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6807,7 +6738,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6817,12 +6748,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6842,17 +6773,17 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128934086</v>
+        <v>128933123</v>
       </c>
       <c r="B57" t="n">
-        <v>57727</v>
+        <v>57953</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6877,20 +6808,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Stalonbyn, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>544908</v>
+        <v>545136</v>
       </c>
       <c r="R57" t="n">
-        <v>7198615</v>
+        <v>7198361</v>
       </c>
       <c r="S57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6914,27 +6854,27 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Tretåhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6949,15 +6889,1394 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
+          <t>Edvin Strandberg</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Edvin Strandberg</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>128933130</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Stalonbyn, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>545144</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7198419</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Edvin Strandberg</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Edvin Strandberg</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>128933147</v>
+      </c>
+      <c r="B59" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Stalonbyn, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>545204</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7198506</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>08:58</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>08:58</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Edvin Strandberg</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Edvin Strandberg</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>128933156</v>
+      </c>
+      <c r="B60" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Stalonbyn, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>544879</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7198601</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Edvin Strandberg</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>128933158</v>
+      </c>
+      <c r="B61" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Stalonbyn, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>544903</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7198597</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Edvin Strandberg</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Edvin Strandberg</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>128933212</v>
+      </c>
+      <c r="B62" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Stalonbyn, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>544911</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7198620</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Edvin Strandberg</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Edvin Strandberg</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>128933213</v>
+      </c>
+      <c r="B63" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Stalonbyn, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>544897</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7198529</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Innanför gränsen, bild finns.</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Edvin Strandberg</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>128933870</v>
+      </c>
+      <c r="B64" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Stalonbyn, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>545136</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7198363</v>
+      </c>
+      <c r="S64" t="n">
+        <v>4</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Nya ringbarkningar från tretåig hackspett på gran.</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
           <t>David Kenger</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>David Kenger, Edvin Strandberg, Petter Lindwall</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>128933902</v>
+      </c>
+      <c r="B65" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Stalonbyn, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>545147</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7198430</v>
+      </c>
+      <c r="S65" t="n">
+        <v>4</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Gamla ringbarkningar på tall</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>David Kenger</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>128933932</v>
+      </c>
+      <c r="B66" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Stalonbyn, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>545212</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7198500</v>
+      </c>
+      <c r="S66" t="n">
+        <v>4</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack äldre än 5 år på tall</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>David Kenger</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>128933973</v>
+      </c>
+      <c r="B67" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Stalonbyn, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>544900</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7198597</v>
+      </c>
+      <c r="S67" t="n">
+        <v>4</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack äldre än 5 år på gran</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>David Kenger</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>128934086</v>
+      </c>
+      <c r="B68" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Stalonbyn, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>544908</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7198615</v>
+      </c>
+      <c r="S68" t="n">
+        <v>4</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>David Kenger</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>128933908</v>
+      </c>
+      <c r="B69" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Stalonbyn, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>545139</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7198504</v>
+      </c>
+      <c r="S69" t="n">
+        <v>4</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Två talltitor</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>David Kenger</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>David Kenger, Petter Lindwall, Edvin Strandberg</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
